--- a/resources/openvas/openvas_artifactory-oss_5.11.0.xlsx
+++ b/resources/openvas/openvas_artifactory-oss_5.11.0.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S117"/>
+  <dimension ref="A1:P117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,21 +497,6 @@
           <t>log_method</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>plugin</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>plugin_details</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>instances</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -530,7 +515,6 @@
 For other products using Tomcat please contact the vendor for more information on fixed versions</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>['cve: CVE-2020-1938', 'url: https://lists.apache.org/thread/bnys5lvg1875dsslkkx2vmwxv833l35x', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.31', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.51', 'url: https://tomcat.apache.org/security-7.html#Fixed_in_Apache_Tomcat_7.0.100', 'url: https://web.archive.org/web/20250114042903/https://www.chaitin.cn/en/ghostcat', 'url: https://www.cnvd.org.cn/flaw/show/CNVD-2020-10487', 'url: https://github.com/YDHCUI/CNVD-2020-10487-Tomcat-Ajp-lfi', 'url: https://securityboulevard.com/2020/02/patch-your-tomcat-and-jboss-instances-to-protect-from-ghostcat-vulnerability-cve-2020-1938-and/', 'url: https://www.cisa.gov/known-exploited-vulnerabilities-catalog cisa: Known Exploited Vulnerability (KEV) catalog', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2023-2480', 'cert-bund: CB-K20/0711', 'cert-bund: CB-K20/0705', 'cert-bund: CB-K20/0693', 'cert-bund: CB-K20/0555', 'cert-bund: CB-K20/0543', 'cert-bund: CB-K20/0154', 'dfn-cert: DFN-CERT-2021-1736', 'dfn-cert: DFN-CERT-2020-1508', 'dfn-cert: DFN-CERT-2020-1413', 'dfn-cert: DFN-CERT-2020-1276', 'dfn-cert: DFN-CERT-2020-1134', 'dfn-cert: DFN-CERT-2020-0850', 'dfn-cert: DFN-CERT-2020-0835', 'dfn-cert: DFN-CERT-2020-0821', 'dfn-cert: DFN-CERT-2020-0569', 'dfn-cert: DFN-CERT-2020-0557', 'dfn-cert: DFN-CERT-2020-0501', 'dfn-cert: DFN-CERT-2020-0381']</t>
@@ -541,7 +525,6 @@
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>8019</v>
       </c>
@@ -580,18 +563,6 @@
           <t>The 'Apache Tomcat' version on the remote host has reached the end of life.</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -624,7 +595,6 @@
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>8040</v>
       </c>
@@ -641,7 +611,6 @@
       <c r="K3" t="n">
         <v>10</v>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>The "Apache Tomcat" version on the remote host has reached the end of life.
@@ -668,18 +637,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -715,7 +672,6 @@
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>8040</v>
       </c>
@@ -756,18 +712,6 @@
 ,→7652)</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -785,7 +729,6 @@
           <t>Update to version 9.0.99, 10.1.35, 11.0.3 or later.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>['cve: CVE-2025-24813', 'cisa: Known Exploited Vulnerability (KEV) catalog', 'url: https://www.cisa.gov/known-exploited-vulnerabilities-catalog', 'url: https://lists.apache.org/thread/j5fkjv2k477os90nczf2v9l61fb0kkgq', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.3', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.35', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.99', 'url: https://github.com/iSee857/CVE-2025-24813-PoC', 'url: https://lab.wallarm.com/one-put-request-to-own-tomcat-cve-2025-24813-rce-is-in-the-wild/', 'url: https://www.openwall.com/lists/oss-security/2025/03/10/5', 'url: https://scrapco.de/blog/analysis-of-cve-2025-24813-apache-tomcat-path-equivalence-rce.html', 'url: https://bishopfox.com/blog/tomcat-cve-2025-24813-what-you-need-to-know-blog', 'cert-bund: WID-SEC-2025-1564', 'cert-bund: WID-SEC-2025-1439 cert-bund: WID-SEC-2025-0825', 'cert-bund: WID-SEC-2025-0824', 'cert-bund: WID-SEC-2025-0823', 'cert-bund: WID-SEC-2025-0511', 'dfn-cert: DFN-CERT-2025-2098', 'dfn-cert: DFN-CERT-2025-0993', 'dfn-cert: DFN-CERT-2025-0890', 'dfn-cert: DFN-CERT-2025-0888', 'dfn-cert: DFN-CERT-2025-0766', 'dfn-cert: DFN-CERT-2025-0622']</t>
@@ -796,7 +739,6 @@
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>8040</v>
       </c>
@@ -842,18 +784,6 @@
 ,→7652)</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -872,7 +802,6 @@
 Update to version 7.0.100, 8.5.51, 9.0.31 or later.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>['cve: CVE-2020-1935', 'cve: CVE-2020-1938', 'cisa: Known Exploited Vulnerability (KEV) catalog', 'url: https://www.cisa.gov/known-exploited-vulnerabilities-catalog', 'url: https://lists.apache.org/thread.html/r127f76181aceffea2bd4711b03c595d0f115f', ',→63e020348fe925a916c%40%3Cannounce.tomcat.apache.org%3E', 'url: https://lists.apache.org/thread.html/r7c6f492fbd39af34a68681dbbba0468490ff1', ',→a97a1bd79c6a53610ef%40%3Cannounce.tomcat.apache.org%3E', 'url: https://www.chaitin.cn/en/ghostcat', 'url: https://www.cnvd.org.cn/flaw/show/CNVD-2020-10487', 'url: https://github.com/YDHCUI/CNVD-2020-10487-Tomcat-Ajp-lfi', 'url: https://tomcat.apache.org/tomcat-7.0-doc/changelog.html', 'url: https://tomcat.apache.org/tomcat-8.5-doc/changelog.html', 'url: https://tomcat.apache.org/tomcat-9.0-doc/changelog.html', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2023-2480', 'cert-bund: WID-SEC-2023-2130', 'cert-bund: CB-K20/0711', 'cert-bund: CB-K20/0705', 'cert-bund: CB-K20/0693', 'cert-bund: CB-K20/0555', 'cert-bund: CB-K20/0543', 'cert-bund: CB-K20/0165', 'cert-bund: CB-K20/0154', 'dfn-cert: DFN-CERT-2021-1736', 'dfn-cert: DFN-CERT-2021-0575', 'dfn-cert: DFN-CERT-2020-2482', 'dfn-cert: DFN-CERT-2020-1707', 'dfn-cert: DFN-CERT-2020-1706', 'dfn-cert: DFN-CERT-2020-1508', 'dfn-cert: DFN-CERT-2020-1413', 'dfn-cert: DFN-CERT-2020-1276', 'dfn-cert: DFN-CERT-2020-1134', 'dfn-cert: DFN-CERT-2020-0850', 'dfn-cert: DFN-CERT-2020-0835 dfn-cert: DFN-CERT-2020-0821', 'dfn-cert: DFN-CERT-2020-0569', 'dfn-cert: DFN-CERT-2020-0557', 'dfn-cert: DFN-CERT-2020-0501', 'dfn-cert: DFN-CERT-2020-0381']</t>
@@ -883,7 +812,6 @@
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>8040</v>
       </c>
@@ -914,25 +842,12 @@
 Installation path / port: 8040/tcp</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
           <t>cpe:/a:apache:tomcat:8.5.23
 Detected by Apache Tomcat Detection Consolidation (OID: 1.3.6.1.4.1.25623.1.0.10-&gt;7652)</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -951,7 +866,6 @@
           <t>Update to version 9.0.104, 10.1.40, 11.0.6 or later.</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>['cve: CVE-2025-31651', 'url: https://lists.apache.org/thread/cpklvqwvdrp4k9hmd2l3q33j0gzy4fox', 'cert-bund: WID-SEC-2025-2372', 'cert-bund: WID-SEC-2025-1850', 'cert-bund: WID-SEC-2025-1572', 'cert-bund: WID-SEC-2025-1565', 'cert-bund: WID-SEC-2025-1563', 'cert-bund: WID-SEC-2025-1439', 'cert-bund: WID-SEC-2025-1365', 'cert-bund: WID-SEC-2025-0895', 'dfn-cert: DFN-CERT-2025-3462', 'dfn-cert: DFN-CERT-2025-3454', 'dfn-cert: DFN-CERT-2025-3431', 'dfn-cert: DFN-CERT-2025-3113', 'dfn-cert: DFN-CERT-2025-2285', 'dfn-cert: DFN-CERT-2025-2098', 'dfn-cert: DFN-CERT-2025-1991', 'dfn-cert: DFN-CERT-2025-1905', 'dfn-cert: DFN-CERT-2025-1898', 'dfn-cert: DFN-CERT-2025-1557', 'dfn-cert: DFN-CERT-2025-1081']</t>
@@ -962,7 +876,6 @@
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>8040</v>
       </c>
@@ -1003,18 +916,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1048,7 +949,6 @@
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>8081</v>
       </c>
@@ -1065,7 +965,6 @@
       <c r="K8" t="n">
         <v>10</v>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>The "Apache Tomcat" version on the remote host has reached the end of life.
@@ -1091,18 +990,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1135,7 +1022,6 @@
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>8081</v>
       </c>
@@ -1175,18 +1061,6 @@
 Method: Apache Tomcat Detection Consolidation OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1204,7 +1078,6 @@
           <t>Update to version 7.0.100, 8.5.51, 9.0.31 or later.</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>['cve: CVE-2020-1935', 'cve: CVE-2020-1938', 'cisa: Known Exploited Vulnerability (KEV) catalog', 'url: https://www.cisa.gov/known-exploited-vulnerabilities-catalog', 'url: https://lists.apache.org/thread.html/r127f76181aceffea2bd4711b03c595d0f115f63e020348fe925a916c%40%3Cannounce.tomcat.apache.org%3E', 'url: https://lists.apache.org/thread.html/r7c6f492fbd39af34a68681dbbba0468490ffa97a1bd79c6a53610ef%40%3Cannounce.tomcat.apache.org%3E', 'url: https://www.chaitin.cn/en/ghostcat', 'url: https://www.cnvd.org.cn/flaw/show/CNVD-2020-10487', 'url: https://github.com/YDHCUI/CNVD-2020-10487-Tomcat-Ajp-lfi', 'url: https://tomcat.apache.org/tomcat-7.0-doc/changelog.html', 'url: https://tomcat.apache.org/tomcat-8.5-doc/changelog.html', 'url: https://tomcat.apache.org/tomcat-9.0-doc/changelog.html', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2023-2480', 'cert-bund: WID-SEC-2023-2130', 'cert-bund: CB-K20/0711', 'cert-bund: CB-K20/0705']</t>
@@ -1215,7 +1088,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>8081</v>
       </c>
@@ -1261,18 +1133,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1290,7 +1150,6 @@
           <t>Update to version 9.0.104, 10.1.40, 11.0.6 or later.</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>['cve: CVE-2025-31651', 'url: https://lists.apache.org/thread/cpklvqwvdrp4k9hmd2l3q33j0gzy4fox', 'cert-bund: WID-SEC-2025-2372', 'cert-bund: WID-SEC-2025-1850', 'cert-bund: WID-SEC-2025-1572', 'cert-bund: WID-SEC-2025-1565', 'cert-bund: WID-SEC-2025-1563', 'cert-bund: WID-SEC-2025-1439', 'cert-bund: WID-SEC-2025-1365', 'cert-bund: WID-SEC-2025-0895', 'dfn-cert: DFN-CERT-2025-3462', 'dfn-cert: DFN-CERT-2025-3454', 'dfn-cert: DFN-CERT-2025-3431', 'dfn-cert: DFN-CERT-2025-3113', 'dfn-cert: DFN-CERT-2025-2285', 'dfn-cert: DFN-CERT-2025-2098', 'dfn-cert: DFN-CERT-2025-1991', 'dfn-cert: DFN-CERT-2025-1905', 'dfn-cert: DFN-CERT-2025-1898', 'dfn-cert: DFN-CERT-2025-1557', 'dfn-cert: DFN-CERT-2025-1081']</t>
@@ -1301,7 +1160,6 @@
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>8081</v>
       </c>
@@ -1345,18 +1203,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1374,7 +1220,6 @@
           <t>Update to version 9.0.99, 10.1.35, 11.0.3 or later.</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>['cve: CVE-2025-24813', 'cisa: Known Exploited Vulnerability (KEV) catalog', 'url: https://www.cisa.gov/known-exploited-vulnerabilities-catalog', 'url: https://lists.apache.org/thread/j5fkjv2k477os90nczf2v9l61fb0kkgq', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.3', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.35', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.99', 'url: https://github.com/iSee857/CVE-2025-24813-PoC', 'url: https://lab.wallarm.com/one-put-request-to-own-tomcat-cve-2025-24813-rce-is-in-the-wild/', 'url: https://www.openwall.com/lists/oss-security/2025/03/10/5', 'url: https://scrapco.de/blog/analysis-of-cve-2025-24813-apache-tomcat-path-equivalence-rce.html', 'url: https://bishopfox.com/blog/tomcat-cve-2025-24813-what-you-need-to-know-blog', 'cert-bund: WID-SEC-2025-1564', 'cert-bund: WID-SEC-2025-1439', 'cert-bund: WID-SEC-2025-0825', 'cert-bund: WID-SEC-2025-0824', 'cert-bund: WID-SEC-2025-0823', 'cert-bund: WID-SEC-2025-0511', 'dfn-cert: DFN-CERT-2025-2098', 'dfn-cert: DFN-CERT-2025-0993', 'dfn-cert: DFN-CERT-2025-0890', 'dfn-cert: DFN-CERT-2025-0888', 'dfn-cert: DFN-CERT-2025-0766', 'dfn-cert: DFN-CERT-2025-0622']</t>
@@ -1385,7 +1230,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>8081</v>
       </c>
@@ -1444,18 +1288,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1473,7 +1305,6 @@
           <t>Update to version 8.5.76, 9.0.21 or later.</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>['cve: CVE-2022-25762', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.21', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.76', 'url: https://lists.apache.org/thread/tkmozotlgcrpvhx5vt6kw0pxtfx11k67', 'cert-bund: WID-SEC-2022-1335', 'cert-bund: WID-SEC-2022-1228', 'cert-bund: WID-SEC-2022-0899', 'cert-bund: WID-SEC-2022-0740', 'cert-bund: CB-K22/0600', 'dfn-cert: DFN-CERT-2024-0762', 'dfn-cert: DFN-CERT-2022-1605']</t>
@@ -1484,7 +1315,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>8040</v>
       </c>
@@ -1506,7 +1336,6 @@
           <t>The error handling triggered in this case could cause the a pooled object to be placed in the pool twice. This could result in subsequent connections using the same object concurrently which could result in data being returned to the wrong user and/or other errors.</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>Checks if a vulnerable version is present on the target host.
@@ -1522,18 +1351,6 @@
 ,→7652)</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1551,7 +1368,6 @@
           <t>Update to version 9.0.106, 10.1.42, 11.0.8 or later.</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>['cve: CVE-2022-25762', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.21', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.76', 'url: https://lists.apache.org/thread/tkmozotlgcrpvhx5vt6kw0pxtfx11k67', 'cert-bund: WID-SEC-2022-1335', 'cert-bund: WID-SEC-2022-1228', 'cert-bund: WID-SEC-2022-0899', 'cert-bund: WID-SEC-2022-0740', 'cert-bund: CB-K22/0600', 'dfn-cert: DFN-CERT-2024-0762', 'dfn-cert: DFN-CERT-2022-1605']</t>
@@ -1562,7 +1378,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>8040</v>
       </c>
@@ -1608,18 +1423,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1637,7 +1440,6 @@
           <t>Update to version 9.0.90, 10.1.25, 11.0.0-M21 or later.</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>['cve: CVE-2024-34750', 'url: https://lists.apache.org/thread/4kqf0bc9gxymjc2x7v3p7dvplnl77y8l', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.0-M2', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.25', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.90', 'cert-bund: WID-SEC-2025-0163', 'cert-bund: WID-SEC-2025-0161', 'cert-bund: WID-SEC-2025-0148', 'cert-bund: WID-SEC-2025-0144', 'cert-bund: WID-SEC-2025-0143', 'cert-bund: WID-SEC-2024-3197', 'cert-bund: WID-SEC-2024-3195', 'cert-bund: WID-SEC-2024-2100', 'cert-bund: WID-SEC-2024-1905', 'cert-bund: WID-SEC-2024-1522', 'dfn-cert: DFN-CERT-2025-2098', 'dfn-cert: DFN-CERT-2025-1991', 'dfn-cert: DFN-CERT-2025-1517', 'dfn-cert: DFN-CERT-2025-0170', 'dfn-cert: DFN-CERT-2025-0146', 'dfn-cert: DFN-CERT-2024-2192', 'dfn-cert: DFN-CERT-2024-2031 dfn-cert: DFN-CERT-2024-1723']</t>
@@ -1648,7 +1450,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>8040</v>
       </c>
@@ -1692,18 +1493,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1721,7 +1510,6 @@
           <t>Update to version 9.0.107 or later.</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>['cve: CVE-2025-52434', 'url: https://lists.apache.org/thread/gxgh65004f25y8519coth6w7vchww030', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.107', 'cert-bund: WID-SEC-2026-0177', 'cert-bund: WID-SEC-2025-1905', 'cert-bund: WID-SEC-2025-1468', 'dfn-cert: DFN-CERT-2025-2957', 'dfn-cert: DFN-CERT-2025-2390', 'dfn-cert: DFN-CERT-2025-2299', 'dfn-cert: DFN-CERT-2025-2056', 'dfn-cert: DFN-CERT-2025-1991', 'dfn-cert: DFN-CERT-2025-1789']</t>
@@ -1732,7 +1520,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>8040</v>
       </c>
@@ -1773,18 +1560,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1803,7 +1578,6 @@
           <t>Update to version 9.0.108, 10.1.44, 11.0.10 or later.</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>['cve: CVE-2025-8671', 'cve: CVE-2025-48989', 'url: https://lists.apache.org/thread/9ydfg0xr0tchmglcprhxgwhj0hfwxlyf', 'url: https://lists.apache.org/thread/p09775q0rd185m6zz98krg0fp45j8kr0', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.108', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.44', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.10', 'url: https://galbarnahum.com/posts/made-you-reset-intro', 'url: https://deepness-lab.org/publications/madeyoureset/', 'url: https://kb.cert.org/vuls/id/767506', 'url: https://thehackernews.com/2025/08/new-http2-madeyoureset-vulnerability.html', 'cert-bund: WID-SEC-2026-0177', 'cert-bund: WID-SEC-2026-0175', 'cert-bund: WID-SEC-2026-0173', 'cert-bund: WID-SEC-2026-0165', 'cert-bund: WID-SEC-2025-2853', 'cert-bund: WID-SEC-2025-2373', 'cert-bund: WID-SEC-2025-2361', 'cert-bund: WID-SEC-2025-2360 cert-bund: WID-SEC-2025-2356', 'cert-bund: WID-SEC-2025-1830', 'dfn-cert: DFN-CERT-2025-3431', 'dfn-cert: DFN-CERT-2025-2957', 'dfn-cert: DFN-CERT-2025-2390', 'dfn-cert: DFN-CERT-2025-2299', 'dfn-cert: DFN-CERT-2025-2224', 'dfn-cert: DFN-CERT-2025-2219']</t>
@@ -1814,7 +1588,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>8040</v>
       </c>
@@ -1859,18 +1632,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1888,7 +1649,6 @@
           <t>Update to version 9.0.106, 10.1.42, 11.0.8 or later.</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>['cve: CVE-2025-48976', 'cve: CVE-2025-48988', 'cve: CVE-2025-49125', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.8', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.42', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.106', 'url: https://lists.apache.org/thread/nzkqsok8t42qofgqfmck536mtyzygp18', 'url: https://lists.apache.org/thread/m66cytbfrty9k7dc4cg6tl1czhsnbywk', 'url: https://www.openwall.com/lists/oss-security/2025/06/16/1', 'url: https://www.openwall.com/lists/oss-security/2025/06/16/2', 'url: https://github.com/Samb102/POC-CVE-2025-48988-CVE-2025-48976', 'cert-bund: WID-SEC-2026-0177', 'cert-bund: WID-SEC-2026-0175', 'cert-bund: WID-SEC-2026-0165', 'cert-bund: WID-SEC-2026-0163', 'cert-bund: WID-SEC-2026-0162', 'cert-bund: WID-SEC-2026-0153', 'cert-bund: WID-SEC-2025-2853', 'cert-bund: WID-SEC-2025-2768', 'cert-bund: WID-SEC-2025-2373', 'cert-bund: WID-SEC-2025-2372', 'cert-bund: WID-SEC-2025-2371', 'cert-bund: WID-SEC-2025-2369', 'cert-bund: WID-SEC-2025-2366', 'cert-bund: WID-SEC-2025-2362', 'cert-bund: WID-SEC-2025-2361', 'cert-bund: WID-SEC-2025-2360', 'cert-bund: WID-SEC-2025-2359', 'cert-bund: WID-SEC-2025-2357', 'cert-bund: WID-SEC-2025-2356', 'cert-bund: WID-SEC-2025-2355', 'cert-bund: WID-SEC-2025-2353', 'cert-bund: WID-SEC-2025-2351 cert-bund: WID-SEC-2025-1562', 'cert-bund: WID-SEC-2025-1560', 'cert-bund: WID-SEC-2025-1559', 'cert-bund: WID-SEC-2025-1335', 'cert-bund: WID-SEC-2025-1334', 'dfn-cert: DFN-CERT-2026-0205', 'dfn-cert: DFN-CERT-2025-3541', 'dfn-cert: DFN-CERT-2025-3168', 'dfn-cert: DFN-CERT-2025-2941', 'dfn-cert: DFN-CERT-2025-2939', 'dfn-cert: DFN-CERT-2025-2390', 'dfn-cert: DFN-CERT-2025-2335', 'dfn-cert: DFN-CERT-2025-2299', 'dfn-cert: DFN-CERT-2025-2291', 'dfn-cert: DFN-CERT-2025-2098', 'dfn-cert: DFN-CERT-2025-2088', 'dfn-cert: DFN-CERT-2025-2056', 'dfn-cert: DFN-CERT-2025-1992', 'dfn-cert: DFN-CERT-2025-1991', 'dfn-cert: DFN-CERT-2025-1780', 'dfn-cert: DFN-CERT-2025-1739', 'dfn-cert: DFN-CERT-2025-1588']</t>
@@ -1899,7 +1659,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>8040</v>
       </c>
@@ -1945,18 +1704,6 @@
 Detected by Apache Tomcat Detection Consolidation (OID: 1.3.6.1.4.1.25623.1.0.10 -&gt;7652)</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1975,7 +1722,6 @@
 Update to version 9.0.107, 10.1.43, 11.0.9 or later.</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>['cve: CVE-2025-52520', 'cve: CVE-2025-53506', 'url: https://lists.apache.org/thread/trqq01bbxw6c92zx69kx2mw2qgmfy0o5', 'url: https://lists.apache.org/thread/p09775q0rd185m6zz98krg0fp45j8kr0', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.107', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.43', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.9', 'cert-bund: WID-SEC-2025-1905', 'cert-bund: WID-SEC-2025-1468', 'dfn-cert: DFN-CERT-2025-2390', 'dfn-cert: DFN-CERT-2025-2335', 'dfn-cert: DFN-CERT-2025-2299', 'dfn-cert: DFN-CERT-2025-2219', 'dfn-cert: DFN-CERT-2025-2168', 'dfn-cert: DFN-CERT-2025-2088', 'dfn-cert: DFN-CERT-2025-2056', 'dfn-cert: DFN-CERT-2025-1991', 'dfn-cert: DFN-CERT-2025-1789']</t>
@@ -1986,7 +1732,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>8040</v>
       </c>
@@ -2033,18 +1778,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2062,7 +1795,6 @@
           <t>Update to version 8.5.64, 9.0.44, 10.0.4 or later.</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>['cve: CVE-2021-41079', 'url: https://lists.apache.org/thread.html/rccdef0349fdf4fb73a4e4403095446d7fe6264e0a58e2df5c6799434%40%3Cannounce.tomcat.apache.org%3E', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-0673', 'cert-bund: WID-SEC-2022-0615', 'cert-bund: WID-SEC-2022-0607', 'cert-bund: CB-K21/0983', 'dfn-cert: DFN-CERT-2024-1989', 'dfn-cert: DFN-CERT-2024-0762', 'dfn-cert: DFN-CERT-2022-1530', 'dfn-cert: DFN-CERT-2022-0826', 'dfn-cert: DFN-CERT-2022-0733', 'dfn-cert: DFN-CERT-2021-2297', 'dfn-cert: DFN-CERT-2021-2169', 'dfn-cert: DFN-CERT-2021-1990']</t>
@@ -2073,7 +1805,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>8040</v>
       </c>
@@ -2119,18 +1850,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2148,7 +1867,6 @@
           <t>Update to version 8.5.94, 9.0.81, 10.1.14, 11.0.0-M12 or later.</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>['cve: CVE-2023-42795', 'cve: CVE-2023-44487', 'cve: CVE-2023-45648', 'url: https://lists.apache.org/thread/065jfyo583490r9j2v73nhpyxdob56lw', 'url: https://lists.apache.org/thread/3m81kt8c2gtg4nkjfwt2hvt5l9ycx6vl', 'url: https://lists.apache.org/thread/2pv8yz1pyp088tsxfb7ogltk9msk0jdp', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.0-M1', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.14', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.81', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.94', 'url: https://cloud.google.com/blog/products/identity-security/how-it-works-the-n', 'url: https://blog.cloudflare.com/technical-breakdown-http2-rapid-reset-ddos-atta', 'url: https://aws.amazon.com/blogs/security/how-aws-protects-customers-from-ddosurl: https://www.openwall.com/lists/oss-security/2023/10/10/6', 'url: https://www.cisa.gov/news-events/alerts/2023/10/10/http2-rapid-reset-vulner', 'url: https://www.cisa.gov/known-exploited-vulnerabilities-catalog', 'cisa: Known Exploited Vulnerability (KEV) catalog', 'cert-bund: WID-SEC-2025-0225', 'cert-bund: WID-SEC-2024-3684', 'cert-bund: WID-SEC-2024-1652 cert-bund: WID-SEC-2024-1643', 'cert-bund: WID-SEC-2024-1642', 'cert-bund: WID-SEC-2024-1307', 'cert-bund: WID-SEC-2024-1248', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-1228', 'cert-bund: WID-SEC-2024-0899', 'cert-bund: WID-SEC-2024-0894', 'cert-bund: WID-SEC-2024-0887', 'cert-bund: WID-SEC-2024-0874', 'cert-bund: WID-SEC-2024-0873', 'cert-bund: WID-SEC-2024-0870', 'cert-bund: WID-SEC-2024-0869', 'cert-bund: WID-SEC-2024-0794', 'cert-bund: WID-SEC-2024-0597', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2024-0521', 'cert-bund: WID-SEC-2024-0519', 'cert-bund: WID-SEC-2024-0123', 'cert-bund: WID-SEC-2024-0121', 'cert-bund: WID-SEC-2024-0118', 'cert-bund: WID-SEC-2024-0117', 'cert-bund: WID-SEC-2024-0116', 'cert-bund: WID-SEC-2024-0115', 'cert-bund: WID-SEC-2024-0108', 'cert-bund: WID-SEC-2024-0107', 'cert-bund: WID-SEC-2024-0106', 'cert-bund: WID-SEC-2024-0025', 'cert-bund: WID-SEC-2023-3146', 'cert-bund: WID-SEC-2023-2993', 'cert-bund: WID-SEC-2023-2963', 'cert-bund: WID-SEC-2023-2788', 'cert-bund: WID-SEC-2023-2723', 'cert-bund: WID-SEC-2023-2655', 'cert-bund: WID-SEC-2023-2628', 'cert-bund: WID-SEC-2023-2627', 'cert-bund: WID-SEC-2023-2618', 'cert-bund: WID-SEC-2023-2611', 'cert-bund: WID-SEC-2023-2606', 'dfn-cert: DFN-CERT-2025-2658', 'dfn-cert: DFN-CERT-2025-2038', 'dfn-cert: DFN-CERT-2025-1517', 'dfn-cert: DFN-CERT-2025-0267', 'dfn-cert: DFN-CERT-2024-3078', 'dfn-cert: DFN-CERT-2024-2706', 'dfn-cert: DFN-CERT-2024-2681', 'dfn-cert: DFN-CERT-2024-2487 dfn-cert: DFN-CERT-2024-2348', 'dfn-cert: DFN-CERT-2024-2290', 'dfn-cert: DFN-CERT-2024-1105', 'dfn-cert: DFN-CERT-2024-1016', 'dfn-cert: DFN-CERT-2024-1002', 'dfn-cert: DFN-CERT-2024-1000', 'dfn-cert: DFN-CERT-2024-0830', 'dfn-cert: DFN-CERT-2024-0819', 'dfn-cert: DFN-CERT-2024-0760', 'dfn-cert: DFN-CERT-2024-0526', 'dfn-cert: DFN-CERT-2024-0522', 'dfn-cert: DFN-CERT-2024-0491', 'dfn-cert: DFN-CERT-2024-0464', 'dfn-cert: DFN-CERT-2024-0411', 'dfn-cert: DFN-CERT-2024-0398', 'dfn-cert: DFN-CERT-2024-0367', 'dfn-cert: DFN-CERT-2024-0337', 'dfn-cert: DFN-CERT-2024-0149', 'dfn-cert: DFN-CERT-2024-0134', 'dfn-cert: DFN-CERT-2024-0133', 'dfn-cert: DFN-CERT-2024-0129', 'dfn-cert: DFN-CERT-2024-0081', 'dfn-cert: DFN-CERT-2024-0076', 'dfn-cert: DFN-CERT-2024-0048', 'dfn-cert: DFN-CERT-2023-3167', 'dfn-cert: DFN-CERT-2023-3124', 'dfn-cert: DFN-CERT-2023-3119', 'dfn-cert: DFN-CERT-2023-3073', 'dfn-cert: DFN-CERT-2023-3059', 'dfn-cert: DFN-CERT-2023-3035', 'dfn-cert: DFN-CERT-2023-3007', 'dfn-cert: DFN-CERT-2023-2996', 'dfn-cert: DFN-CERT-2023-2991', 'dfn-cert: DFN-CERT-2023-2971', 'dfn-cert: DFN-CERT-2023-2959', 'dfn-cert: DFN-CERT-2023-2912', 'dfn-cert: DFN-CERT-2023-2892', 'dfn-cert: DFN-CERT-2023-2882', 'dfn-cert: DFN-CERT-2023-2876', 'dfn-cert: DFN-CERT-2023-2864', 'dfn-cert: DFN-CERT-2023-2851', 'dfn-cert: DFN-CERT-2023-2849', 'dfn-cert: DFN-CERT-2023-2803', 'dfn-cert: DFN-CERT-2023-2787', 'dfn-cert: DFN-CERT-2023-2785', 'dfn-cert: DFN-CERT-2023-2730', 'dfn-cert: DFN-CERT-2023-2729 dfn-cert: DFN-CERT-2023-2708', 'dfn-cert: DFN-CERT-2023-2701', 'dfn-cert: DFN-CERT-2023-2696', 'dfn-cert: DFN-CERT-2023-2695', 'dfn-cert: DFN-CERT-2023-2680', 'dfn-cert: DFN-CERT-2023-2677', 'dfn-cert: DFN-CERT-2023-2675', 'dfn-cert: DFN-CERT-2023-2670', 'dfn-cert: DFN-CERT-2023-2666', 'dfn-cert: DFN-CERT-2023-2646', 'dfn-cert: DFN-CERT-2023-2637', 'dfn-cert: DFN-CERT-2023-2636', 'dfn-cert: DFN-CERT-2023-2635', 'dfn-cert: DFN-CERT-2023-2623', 'dfn-cert: DFN-CERT-2023-2603', 'dfn-cert: DFN-CERT-2023-2600', 'dfn-cert: DFN-CERT-2023-2599', 'dfn-cert: DFN-CERT-2023-2597', 'dfn-cert: DFN-CERT-2023-2596', 'dfn-cert: DFN-CERT-2023-2595', 'dfn-cert: DFN-CERT-2023-2590', 'dfn-cert: DFN-CERT-2023-2589', 'dfn-cert: DFN-CERT-2023-2586', 'dfn-cert: DFN-CERT-2023-2585', 'dfn-cert: DFN-CERT-2023-2572', 'dfn-cert: DFN-CERT-2023-2571', 'dfn-cert: DFN-CERT-2023-2568', 'dfn-cert: DFN-CERT-2023-2564', 'dfn-cert: DFN-CERT-2023-2556', 'dfn-cert: DFN-CERT-2023-2555', 'dfn-cert: DFN-CERT-2023-2552', 'dfn-cert: DFN-CERT-2023-2549', 'dfn-cert: DFN-CERT-2023-2547', 'dfn-cert: DFN-CERT-2023-2528', 'dfn-cert: DFN-CERT-2023-2522', 'dfn-cert: DFN-CERT-2023-2512', 'dfn-cert: DFN-CERT-2023-2504', 'dfn-cert: DFN-CERT-2023-2501', 'dfn-cert: DFN-CERT-2023-2487', 'dfn-cert: DFN-CERT-2023-2469', 'dfn-cert: DFN-CERT-2023-2468', 'dfn-cert: DFN-CERT-2023-2459', 'dfn-cert: DFN-CERT-2023-2457', 'dfn-cert: DFN-CERT-2023-2453', 'dfn-cert: DFN-CERT-2023-2450', 'dfn-cert: DFN-CERT-2023-2449', 'dfn-cert: DFN-CERT-2023-2439']</t>
@@ -2159,7 +1877,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>8040</v>
       </c>
@@ -2203,18 +1920,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2232,7 +1937,6 @@
           <t>Update to version 8.5.60, 9.0.40, 10.0.0-M10 or later.</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>['cve: CVE-2020-17527', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.0.0-M1', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.40', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.60', 'url: https://lists.apache.org/thread.html/rce5ac9a40173651d540babce59f6f3825f12c6d4e886ba00823b11e5%40%3Cannounce.tomcat.apache.org%3E', 'cert-bund: WID-SEC-2023-2466', 'cert-bund: WID-SEC-2023-0065', 'cert-bund: WID-SEC-2022-0624', 'cert-bund: CB-K21/0421', 'cert-bund: CB-K21/0418', 'cert-bund: CB-K20/1195', 'dfn-cert: DFN-CERT-2022-0733', 'dfn-cert: DFN-CERT-2021-2620', 'dfn-cert: DFN-CERT-2021-0821', 'dfn-cert: DFN-CERT-2021-0820', 'dfn-cert: DFN-CERT-2021-0338', 'dfn-cert: DFN-CERT-2021-0134', 'dfn-cert: DFN-CERT-2021-0034', 'dfn-cert: DFN-CERT-2020-2646']</t>
@@ -2243,7 +1947,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>8040</v>
       </c>
@@ -2289,18 +1992,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2318,7 +2009,6 @@
           <t>Update to version 8.5.63, 9.0.43, 10.0.2 or later.</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>['cve: CVE-2021-25122', 'url: https://lists.apache.org/thread.html/r7b95bc248603360501f18c8eb03bb6001ec0e', ',→e3296205b34b07105b7@%3Cannounce.tomcat.apache.org%3E', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.0.2', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.43', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.63', 'cert-bund: WID-SEC-2022-1375', 'cert-bund: WID-SEC-2022-1099', 'cert-bund: WID-SEC-2022-0624', 'cert-bund: WID-SEC-2022-0607', 'cert-bund: CB-K21/1094', 'cert-bund: CB-K21/1081', 'cert-bund: CB-K21/0770', 'cert-bund: CB-K21/0222', 'dfn-cert: DFN-CERT-2024-1989', 'dfn-cert: DFN-CERT-2022-1530', 'dfn-cert: DFN-CERT-2022-0733', 'dfn-cert: DFN-CERT-2021-2191', 'dfn-cert: DFN-CERT-2021-1904', 'dfn-cert: DFN-CERT-2021-1537', 'dfn-cert: DFN-CERT-2021-1536', 'dfn-cert: DFN-CERT-2021-1403', 'dfn-cert: DFN-CERT-2021-0810', 'dfn-cert: DFN-CERT-2021-0807', 'dfn-cert: DFN-CERT-2021-0544', 'dfn-cert: DFN-CERT-2021-0445']</t>
@@ -2329,7 +2019,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>8040</v>
       </c>
@@ -2346,7 +2035,6 @@
       <c r="K23" t="n">
         <v>7.5</v>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Installed version: 8.5.23
@@ -2369,18 +2057,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2398,7 +2074,6 @@
           <t>Update to version 7.0.99, 8.5.50, 9.0.30 or later.</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>['cve: CVE-2019-17563', 'url: https://lists.apache.org/thread.html/8b4c1db8300117b28a0f3f743c0b9e3f964687a690cdf9662a884bbd%40%3Cannounce.tomcat.apache.org%3E', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2023-1229', 'cert-bund: WID-SEC-2023-1049', 'cert-bund: CB-K21/0071', 'cert-bund: CB-K20/1030', 'cert-bund: CB-K20/0318', 'cert-bund: CB-K20/0309', 'cert-bund: CB-K19/1102', 'dfn-cert: DFN-CERT-2021-0575', 'dfn-cert: DFN-CERT-2020-2132', 'dfn-cert: DFN-CERT-2020-1134', 'dfn-cert: DFN-CERT-2020-1129', 'dfn-cert: DFN-CERT-2020-0821', 'dfn-cert: DFN-CERT-2020-0780', 'dfn-cert: DFN-CERT-2020-0775', 'dfn-cert: DFN-CERT-2020-0557', 'dfn-cert: DFN-CERT-2020-0501', 'dfn-cert: DFN-CERT-2020-0345', 'dfn-cert: DFN-CERT-2020-0027', 'dfn-cert: DFN-CERT-2019-2710', 'dfn-cert: DFN-CERT-2019-2673']</t>
@@ -2409,7 +2084,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>8040</v>
       </c>
@@ -2455,18 +2129,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2484,7 +2146,6 @@
           <t>Update to version 8.5.41, 9.0.20 or later.</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>['cve: CVE-2019-10072', 'url: https://lists.apache.org/thread.html/df1a2c1b87c8a6c500ecdbbaf134c7f1491c8d79d98b48c6b9f0fa6a@%3Cannounce.tomcat.apache.org%3E', 'url: http://www.securityfocus.com/bid/108874', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: CB-K20/1008', 'cert-bund: CB-K20/0029', 'cert-bund: CB-K19/0915', 'cert-bund: CB-K19/0523', 'dfn-cert: DFN-CERT-2020-0501', 'dfn-cert: DFN-CERT-2020-0088', 'dfn-cert: DFN-CERT-2020-0027', 'dfn-cert: DFN-CERT-2019-2457', 'dfn-cert: DFN-CERT-2019-2149', 'dfn-cert: DFN-CERT-2019-1895', 'dfn-cert: DFN-CERT-2019-1472', 'dfn-cert: DFN-CERT-2019-1268']</t>
@@ -2495,7 +2156,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>8040</v>
       </c>
@@ -2536,18 +2196,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2565,7 +2213,6 @@
           <t>Update to version 8.5.41, 9.0.20 or later.</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>['cve: CVE-2019-10072', 'url: http://tomcat.apache.org/security-9.html', 'url: http://tomcat.apache.org/security-8.html', 'cert-bund: WID-SEC-2024-0528 cert-bund: CB-K20/1008', 'cert-bund: CB-K20/0029', 'cert-bund: CB-K19/0915', 'cert-bund: CB-K19/0523', 'dfn-cert: DFN-CERT-2020-0501', 'dfn-cert: DFN-CERT-2020-0088', 'dfn-cert: DFN-CERT-2020-0027', 'dfn-cert: DFN-CERT-2019-2457', 'dfn-cert: DFN-CERT-2019-2149', 'dfn-cert: DFN-CERT-2019-1895', 'dfn-cert: DFN-CERT-2019-1472', 'dfn-cert: DFN-CERT-2019-1268']</t>
@@ -2576,7 +2223,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>8040</v>
       </c>
@@ -2621,18 +2267,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2650,7 +2284,6 @@
           <t>Update to version 8.5.38, 9.0.16 or later.</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>['cve: CVE-2019-0199', 'url: http://tomcat.apache.org/security-9.html', 'url: http://tomcat.apache.org/security-8.html', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: CB-K20/0543', 'cert-bund: CB-K20/0029', 'cert-bund: CB-K19/0235', 'dfn-cert: DFN-CERT-2019-2710', 'dfn-cert: DFN-CERT-2019-1895', 'dfn-cert: DFN-CERT-2019-1755', 'dfn-cert: DFN-CERT-2019-1472', 'dfn-cert: DFN-CERT-2019-1231', 'dfn-cert: DFN-CERT-2019-1095', 'dfn-cert: DFN-CERT-2019-0594']</t>
@@ -2661,7 +2294,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>8040</v>
       </c>
@@ -2706,18 +2338,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2736,7 +2356,6 @@
 Update to version 8.5.56, 9.0.36, 10.0.0-M6 or later.</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>['cve: CVE-2020-11996', 'url: https://lists.apache.org/thread.html/r5541ef6b6b68b49f76fc4c45695940116da2b', ',→cbe0312ef204a00a2e0%40%3Cannounce.tomcat.apache.org%3E', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2022-1375', 'cert-bund: CB-K20/1017', 'cert-bund: CB-K20/0637', 'cert-bund: CB-K20/0636', 'dfn-cert: DFN-CERT-2021-1736', 'dfn-cert: DFN-CERT-2021-0043', 'dfn-cert: DFN-CERT-2020-2006', 'dfn-cert: DFN-CERT-2020-1575', 'dfn-cert: DFN-CERT-2020-1490', 'dfn-cert: DFN-CERT-2020-1358']</t>
@@ -2747,9 +2366,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>OPENVAS</t>
@@ -2758,7 +2374,6 @@
       <c r="K28" t="n">
         <v>7.5</v>
       </c>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>Installed version: 8.5.23
@@ -2778,18 +2393,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2807,7 +2410,6 @@
           <t>Update to version 8.5.57, 9.0.37, 10.0.0-M7 or later.</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>['cve: CVE-2020-13934', 'cve: CVE-2020-13935', 'url: https://lists.apache.org/thread.html/r61f411cf82488d6ec213063fc15feeeb88e31-&gt;b0ca9c29652ee4f962e%40%3Cannounce.tomcat.apache.org%3E', 'url: https://lists.apache.org/thread.html/rd48c72bd3255bda87564d4da3791517c074d9-&gt;4f8a701f93b85752651%40%3Cannounce.tomcat.apache.org%3E', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.0.0-M7', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.37', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.57', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2023-1048', 'cert-bund: WID-SEC-2022-1375', 'cert-bund: WID-SEC-2022-0519', 'cert-bund: CB-K20/1030', 'cert-bund: CB-K20/1021', 'cert-bund: CB-K20/1017', 'cert-bund: CB-K20/0717', 'dfn-cert: DFN-CERT-2022-1472', 'dfn-cert: DFN-CERT-2021-1736', 'dfn-cert: DFN-CERT-2021-0714', 'dfn-cert: DFN-CERT-2021-0132', 'dfn-cert: DFN-CERT-2020-2295', 'dfn-cert: DFN-CERT-2020-2287', 'dfn-cert: DFN-CERT-2020-2132', 'dfn-cert: DFN-CERT-2020-2006', 'dfn-cert: DFN-CERT-2020-1761', 'dfn-cert: DFN-CERT-2020-1707', 'dfn-cert: DFN-CERT-2020-1706', 'dfn-cert: DFN-CERT-2020-1575', 'dfn-cert: DFN-CERT-2020-1511']</t>
@@ -2818,7 +2420,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>8040</v>
       </c>
@@ -2842,7 +2443,6 @@
 - WebSocket Denial of Service (CVE-2020-13935) </t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>Checks if a vulnerable version is present on the target host.
@@ -2858,18 +2458,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2882,8 +2470,6 @@
           <t>Apache Tomcat is prone to a request smuggling vulnerability.</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>['url: https://lists.apache.org/thread.html/r61f411cf82488d6ec213063fc15feeeb88e31-&gt;b0ca9c29652ee4f962e%40%3Cannounce.tomcat.apache.org%3E', 'url: https://lists.apache.org/thread.html/rd48c72bd3255bda87564d4da3791517c074d9-&gt;4f8a701f93b85752651%40%3Cannounce.tomcat.apache.org%3E', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.0.0-M7', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.37', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.57', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2023-1048', 'cert-bund: WID-SEC-2022-1375', 'cert-bund: WID-SEC-2022-0519', 'cert-bund: CB-K20/1030', 'cert-bund: CB-K20/1021', 'cert-bund: CB-K20/1017', 'cert-bund: CB-K20/0717', 'dfn-cert: DFN-CERT-2022-1472', 'dfn-cert: DFN-CERT-2021-1736', 'dfn-cert: DFN-CERT-2021-0714', 'dfn-cert: DFN-CERT-2021-0132', 'dfn-cert: DFN-CERT-2020-2295', 'dfn-cert: DFN-CERT-2020-2287', 'dfn-cert: DFN-CERT-2020-2132', 'dfn-cert: DFN-CERT-2020-2006', 'dfn-cert: DFN-CERT-2020-1761', 'dfn-cert: DFN-CERT-2020-1707', 'dfn-cert: DFN-CERT-2020-1706', 'dfn-cert: DFN-CERT-2020-1575', 'dfn-cert: DFN-CERT-2020-1511']</t>
@@ -2894,7 +2480,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>8040</v>
       </c>
@@ -2911,30 +2496,16 @@
       <c r="K30" t="n">
         <v>7.5</v>
       </c>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>Installed version: 8.5.23
 Fixed version: 8.5.83</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
           <t>Product: cpe:/a:apache:tomcat:8.5.23
 Method: Apache Tomcat Detection Consolidation</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>[]</t>
         </is>
       </c>
     </row>
@@ -2969,7 +2540,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>8040</v>
       </c>
@@ -2991,7 +2561,6 @@
           <t>The flaw exists due to a missing host name verification when using TLS with the WebSocket client.</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>Checks if a vulnerable version is present on the target host.
@@ -3006,18 +2575,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3035,7 +2592,6 @@
           <t>Update to version 8.5.96, 9.0.83, 10.1.16, 11.0.0-M11 or later.</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>['cve: CVE-2023-46589', 'url: https://lists.apache.org/thread/0rqq6ktozqc42ro8hhxdmmdjm1k1tpxr', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.0-M1', ',→1', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.16', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.83', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.96', 'cert-bund: WID-SEC-2025-0810', 'cert-bund: WID-SEC-2024-1653 cert-bund: WID-SEC-2024-1652', 'cert-bund: WID-SEC-2024-1642', 'cert-bund: WID-SEC-2024-1248', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-0899', 'cert-bund: WID-SEC-2024-0890', 'cert-bund: WID-SEC-2024-0873', 'cert-bund: WID-SEC-2024-0869', 'cert-bund: WID-SEC-2024-0769', 'cert-bund: WID-SEC-2024-0119', 'cert-bund: WID-SEC-2024-0108', 'cert-bund: WID-SEC-2024-0106', 'cert-bund: WID-SEC-2024-0101', 'cert-bund: WID-SEC-2024-0094', 'cert-bund: WID-SEC-2023-3020', 'dfn-cert: DFN-CERT-2024-1404', 'dfn-cert: DFN-CERT-2024-1036', 'dfn-cert: DFN-CERT-2024-1000', 'dfn-cert: DFN-CERT-2024-0723', 'dfn-cert: DFN-CERT-2024-0722', 'dfn-cert: DFN-CERT-2024-0506', 'dfn-cert: DFN-CERT-2024-0411', 'dfn-cert: DFN-CERT-2024-0174', 'dfn-cert: DFN-CERT-2024-0127', 'dfn-cert: DFN-CERT-2023-2977']</t>
@@ -3046,7 +2602,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>8040</v>
       </c>
@@ -3090,18 +2645,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3134,7 +2677,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>8040</v>
       </c>
@@ -3178,18 +2720,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3208,7 +2738,6 @@
 Update Apache Tomcat to version 10.1.0-M15, 10.0.21, 9.0.63, 8.5.79 or later to receive the corrected / updated documentation</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>['cve: CVE-2022-29885', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.0-M1', ',→5', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.0.21', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.63', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.79', 'url: https://lists.apache.org/thread/548bnqoxvp0rqqq2yyj90l0xvwhq087d', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2022-1780', 'cert-bund: WID-SEC-2022-1767', 'cert-bund: WID-SEC-2022-0799', 'cert-bund: WID-SEC-2022-0467', 'cert-bund: CB-K22/0597', 'dfn-cert: DFN-CERT-2024-1989', 'dfn-cert: DFN-CERT-2024-0762', 'dfn-cert: DFN-CERT-2022-2392', 'dfn-cert: DFN-CERT-2022-2323', 'dfn-cert: DFN-CERT-2022-1070']</t>
@@ -3219,7 +2748,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>8040</v>
       </c>
@@ -3241,7 +2769,6 @@
           <t>The documentation for the EncryptInterceptor incorrectly stated it enabled Tomcat clustering to run over an untrusted network. This was not correct. While the EncryptInterceptor does provide confidentiality and integrity protection, it does not protect against all risks associated with running over any untrusted network, particularly DoS risks.</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>Checks if a vulnerable version is present on the target host. Details: Apache Tomcat Clustering DoS Vulnerability (May 2022)
@@ -3256,18 +2783,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3280,8 +2795,6 @@
           <t>Apache Tomcat is prone to a denial of service (DoS) vulnerability.</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>['cve: CVE-2023-24998', 'url: https://lists.apache.org/thread/g16kv0xpp272htz107molwbbgdrqrdk1', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.0-M3', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.5', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.71', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.85', 'url: https://lists.apache.org/thread/4xl4l09mhwg4vgsk7dxqogcjrobrrdoy', 'cert-bund: WID-SEC-2025-0810', 'cert-bund: WID-SEC-2024-1652', 'cert-bund: WID-SEC-2024-1642', 'cert-bund: WID-SEC-2024-1637', 'cert-bund: WID-SEC-2024-1622', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-0890']</t>
@@ -3292,7 +2805,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>8040</v>
       </c>
@@ -3309,7 +2821,6 @@
       <c r="K35" t="n">
         <v>7.5</v>
       </c>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
           <t>Installed version: 8.5.23 Fixed version: 8.5.85
@@ -3332,18 +2843,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3378,7 +2877,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>8040</v>
       </c>
@@ -3422,18 +2920,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3451,7 +2937,6 @@
           <t>Update to version 7.0.108, 8.5.63, 9.0.43, 10.0.2 or later.</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>['cve: CVE-2019-12418', 'url: https://lists.apache.org/thread.html/43530b91506e2e0c11cfbe691173f5df8c48f5-&gt;1b98262426d7493b67%40%3Cannounce.tomcat.apache.org%3E', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2023-1229', 'cert-bund: CB-K20/0309', 'cert-bund: CB-K19/1102', 'dfn-cert: DFN-CERT-2020-1129', 'dfn-cert: DFN-CERT-2020-1094', 'dfn-cert: DFN-CERT-2020-0821', 'dfn-cert: DFN-CERT-2020-0604', 'dfn-cert: DFN-CERT-2020-0557', 'dfn-cert: DFN-CERT-2020-0501', 'dfn-cert: DFN-CERT-2020-0345', 'dfn-cert: DFN-CERT-2020-0027', 'dfn-cert: DFN-CERT-2019-2710', 'dfn-cert: DFN-CERT-2019-2673']</t>
@@ -3462,7 +2947,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>8040</v>
       </c>
@@ -3502,18 +2986,6 @@
 Method: Apache Tomcat Detection Consolidation</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3531,7 +3003,6 @@
           <t>Update to version 7.0.104, 8.5.55, 9.0.35, 10.0.0-M5 or later.</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>['cve: CVE-2020-9484', 'url: https://lists.apache.org/thread.html/r77eae567ed829da9012cadb29af17f2df8fa2', ',→3bf66faf88229857bb1%40%3Cannounce.tomcat.apache.org%3E', 'cert-bund: WID-SEC-2022-1870', 'cert-bund: WID-SEC-2022-0607', 'cert-bund: WID-SEC-2022-0432', 'cert-bund: WID-SEC-2022-0302', 'cert-bund: CB-K21/1094', 'cert-bund: CB-K21/0069', 'cert-bund: CB-K20/1017', 'cert-bund: CB-K20/0494', 'dfn-cert: DFN-CERT-2024-1989', 'dfn-cert: DFN-CERT-2024-1926', 'dfn-cert: DFN-CERT-2022-1530', 'dfn-cert: DFN-CERT-2022-0733', 'dfn-cert: DFN-CERT-2021-1736', 'dfn-cert: DFN-CERT-2020-2286', 'dfn-cert: DFN-CERT-2020-1706', 'dfn-cert: DFN-CERT-2020-1635', 'dfn-cert: DFN-CERT-2020-1575', 'dfn-cert: DFN-CERT-2020-1490', 'dfn-cert: DFN-CERT-2020-1289', 'dfn-cert: DFN-CERT-2020-1134', 'dfn-cert: DFN-CERT-2020-1129', 'dfn-cert: DFN-CERT-2020-1094 dfn-cert: DFN-CERT-2020-1086']</t>
@@ -3542,7 +3013,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
         <v>8040</v>
       </c>
@@ -3586,18 +3056,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3630,7 +3088,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>8081</v>
       </c>
@@ -3668,18 +3125,6 @@
 Method: Apache Tomcat Detection Consolidation</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3697,7 +3142,6 @@
           <t>Update to version 8.5.76, 9.0.21 or later.</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>['cve: CVE-2022-25762', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.21', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.76', 'url: https://lists.apache.org/thread/tkmozotlgcrpvhx5vt6kw0pxtfx11k67', 'cert-bund: WID-SEC-2022-1335', 'cert-bund: WID-SEC-2022-1228', 'cert-bund: WID-SEC-2022-0899', 'cert-bund: WID-SEC-2022-0740', 'cert-bund: CB-K22/0600', 'dfn-cert: DFN-CERT-2024-0762', 'dfn-cert: DFN-CERT-2022-1605']</t>
@@ -3708,7 +3152,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>8081</v>
       </c>
@@ -3756,18 +3199,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3785,7 +3216,6 @@
           <t>Update to version 9.0.108, 10.1.44, 11.0.10 or later.</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>['cve: CVE-2025-8671', 'cve: CVE-2025-48989', 'url: https://lists.apache.org/thread/9ydfg0xr0tchmglcprhxgwhj0hfwxlyf', 'url: https://lists.apache.org/thread/p09775q0rd185m6zz98krg0fp45j8kr0', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.108', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.44', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.10', 'url: https://galbarnahum.com/posts/made-you-reset-intro', 'url: https://deepness-lab.org/publications/madeyoureset/', 'url: https://kb.cert.org/vuls/id/767506', 'url: https://thehackernews.com/2025/08/new-http2-madeyoureset-vulnerability.html', 'cert-bund: WID-SEC-2026-0177', 'cert-bund: WID-SEC-2026-0175', 'cert-bund: WID-SEC-2026-0173', 'cert-bund: WID-SEC-2026-0165', 'cert-bund: WID-SEC-2025-2853', 'cert-bund: WID-SEC-2025-2373 cert-bund: WID-SEC-2025-2361', 'cert-bund: WID-SEC-2025-2360', 'cert-bund: WID-SEC-2025-2357', 'cert-bund: WID-SEC-2025-2356', 'cert-bund: WID-SEC-2025-1830', 'dfn-cert: DFN-CERT-2025-3431', 'dfn-cert: DFN-CERT-2025-2957', 'dfn-cert: DFN-CERT-2025-2390', 'dfn-cert: DFN-CERT-2025-2299', 'dfn-cert: DFN-CERT-2025-2224', 'dfn-cert: DFN-CERT-2025-2219']</t>
@@ -3796,7 +3226,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>8081</v>
       </c>
@@ -3847,18 +3276,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3891,7 +3308,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
         <v>8081</v>
       </c>
@@ -3935,18 +3351,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3965,7 +3369,6 @@
           <t>Update to version 9.0.107 or later.</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>['cve: CVE-2025-52434 url: https://lists.apache.org/thread/gxgh65004f25y8519coth6w7vchww030', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.107', 'cert-bund: WID-SEC-2026-0177', 'cert-bund: WID-SEC-2025-1905', 'cert-bund: WID-SEC-2025-1468', 'dfn-cert: DFN-CERT-2025-2957', 'dfn-cert: DFN-CERT-2025-2390', 'dfn-cert: DFN-CERT-2025-2299', 'dfn-cert: DFN-CERT-2025-2056', 'dfn-cert: DFN-CERT-2025-1991', 'dfn-cert: DFN-CERT-2025-1789']</t>
@@ -3976,7 +3379,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>8081</v>
       </c>
@@ -4021,18 +3423,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4050,7 +3440,6 @@
           <t>Update to version 9.0.106, 10.1.42, 11.0.8 or later.</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>['cve: CVE-2025-55668', 'url: https://lists.apache.org/thread/v6bknr96rl7l1qxkl1c03v0qdvbbqs47', 'cert-bund: WID-SEC-2025-1905', 'cert-bund: WID-SEC-2025-1826', 'dfn-cert: DFN-CERT-2025-1588']</t>
@@ -4061,7 +3450,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>8081</v>
       </c>
@@ -4105,18 +3493,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4134,7 +3510,6 @@
           <t>Update to version 9.0.106, 10.1.42, 11.0.8 or later.</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>['cve: CVE-2025-48976', 'cve: CVE-2025-48988', 'cve: CVE-2025-49125', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.8', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.42', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.106', 'url: https://lists.apache.org/thread/nzkqsok8t42qofgqfmck536mtyzygp18', 'url: https://lists.apache.org/thread/m66cytbfrty9k7dc4cg6tl1czhsnbywk', 'url: https://www.openwall.com/lists/oss-security/2025/06/16/1', 'url: https://www.openwall.com/lists/oss-security/2025/06/16/2', 'url: https://github.com/Samb102/POC-CVE-2025-48988-CVE-2025-48976', 'cert-bund: WID-SEC-2026-0177', 'cert-bund: WID-SEC-2026-0175', 'cert-bund: WID-SEC-2026-0165', 'cert-bund: WID-SEC-2026-0163', 'cert-bund: WID-SEC-2026-0162', 'cert-bund: WID-SEC-2026-0153', 'cert-bund: WID-SEC-2025-2853', 'cert-bund: WID-SEC-2025-2768', 'cert-bund: WID-SEC-2025-2373', 'cert-bund: WID-SEC-2025-2372', 'cert-bund: WID-SEC-2025-2371', 'cert-bund: WID-SEC-2025-2369 cert-bund: WID-SEC-2025-2366', 'cert-bund: WID-SEC-2025-2362', 'cert-bund: WID-SEC-2025-2361', 'cert-bund: WID-SEC-2025-2360', 'cert-bund: WID-SEC-2025-2359', 'cert-bund: WID-SEC-2025-2357', 'cert-bund: WID-SEC-2025-2356', 'cert-bund: WID-SEC-2025-2355', 'cert-bund: WID-SEC-2025-2353', 'cert-bund: WID-SEC-2025-2351', 'cert-bund: WID-SEC-2025-1562', 'cert-bund: WID-SEC-2025-1560', 'cert-bund: WID-SEC-2025-1559', 'cert-bund: WID-SEC-2025-1335', 'cert-bund: WID-SEC-2025-1334', 'dfn-cert: DFN-CERT-2026-0205', 'dfn-cert: DFN-CERT-2025-3541', 'dfn-cert: DFN-CERT-2025-3168', 'dfn-cert: DFN-CERT-2025-2941', 'dfn-cert: DFN-CERT-2025-2939', 'dfn-cert: DFN-CERT-2025-2390', 'dfn-cert: DFN-CERT-2025-2335', 'dfn-cert: DFN-CERT-2025-2299', 'dfn-cert: DFN-CERT-2025-2291', 'dfn-cert: DFN-CERT-2025-2098', 'dfn-cert: DFN-CERT-2025-2088', 'dfn-cert: DFN-CERT-2025-2056', 'dfn-cert: DFN-CERT-2025-1992', 'dfn-cert: DFN-CERT-2025-1991', 'dfn-cert: DFN-CERT-2025-1780', 'dfn-cert: DFN-CERT-2025-1739', 'dfn-cert: DFN-CERT-2025-1588']</t>
@@ -4145,7 +3520,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
         <v>8081</v>
       </c>
@@ -4192,18 +3566,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4221,7 +3583,6 @@
           <t>Update to version 9.0.107, 10.1.43, 11.0.9 or later.</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>['cve: CVE-2025-52520', 'cve: CVE-2025-53506', 'url: https://lists.apache.org/thread/trqq01bbxw6c92zx69kx2mw2qgmfy0o5', 'url: https://lists.apache.org/thread/p09775q0rd185m6zz98krg0fp45j8kr0', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.107', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.43', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.9', 'cert-bund: WID-SEC-2025-1905', 'cert-bund: WID-SEC-2025-1468', 'dfn-cert: DFN-CERT-2025-2390 dfn-cert: DFN-CERT-2025-2335', 'dfn-cert: DFN-CERT-2025-2299', 'dfn-cert: DFN-CERT-2025-2219', 'dfn-cert: DFN-CERT-2025-2168', 'dfn-cert: DFN-CERT-2025-2088', 'dfn-cert: DFN-CERT-2025-2056', 'dfn-cert: DFN-CERT-2025-1991', 'dfn-cert: DFN-CERT-2025-1789']</t>
@@ -4232,7 +3593,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
         <v>8081</v>
       </c>
@@ -4278,18 +3638,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4307,7 +3655,6 @@
           <t>Update to version 8.5.64, 9.0.44, 10.0.4 or later.</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>['cve: CVE-2021-41079', 'url: https://lists.apache.org/thread.html/rccdef0349fdf4fb73a4e4403095446d7fe626', ',→4e0a58e2df5c6799434%40%3Cannounce.tomcat.apache.org%3E', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-0673', 'cert-bund: WID-SEC-2022-0615', 'cert-bund: WID-SEC-2022-0607', 'cert-bund: CB-K21/0983', 'dfn-cert: DFN-CERT-2024-1989', 'dfn-cert: DFN-CERT-2024-0762', 'dfn-cert: DFN-CERT-2022-1530', 'dfn-cert: DFN-CERT-2022-0826', 'dfn-cert: DFN-CERT-2022-0733', 'dfn-cert: DFN-CERT-2021-2297', 'dfn-cert: DFN-CERT-2021-2169', 'dfn-cert: DFN-CERT-2021-1990']</t>
@@ -4318,7 +3665,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
         <v>8081</v>
       </c>
@@ -4362,18 +3708,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4391,7 +3725,6 @@
           <t>Update to version 8.5.60, 9.0.40, 10.0.0-M10 or later.</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>['cve: CVE-2020-17527', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.0.0-M1', ',→0', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.40', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.60', 'url: https://lists.apache.org/thread.html/rce5ac9a40173651d540babce59f6f3825f12c', ',→6d4e886ba00823b11e5%40%3Cannounce.tomcat.apache.org%3E', 'cert-bund: WID-SEC-2023-2466', 'cert-bund: WID-SEC-2023-0065', 'cert-bund: WID-SEC-2022-0624', 'cert-bund: CB-K21/0421', 'cert-bund: CB-K21/0418', 'cert-bund: CB-K20/1195', 'dfn-cert: DFN-CERT-2022-0733', 'dfn-cert: DFN-CERT-2021-2620', 'dfn-cert: DFN-CERT-2021-0821', 'dfn-cert: DFN-CERT-2021-0820', 'dfn-cert: DFN-CERT-2021-0338', 'dfn-cert: DFN-CERT-2021-0134', 'dfn-cert: DFN-CERT-2021-0034', 'dfn-cert: DFN-CERT-2020-2646']</t>
@@ -4402,7 +3735,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
         <v>8081</v>
       </c>
@@ -4448,18 +3780,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4477,7 +3797,6 @@
           <t>Update to version 8.5.94, 9.0.81, 10.1.14, 11.0.0-M12 or later.</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>['cve: CVE-2023-42795', 'cve: CVE-2023-44487', 'cve: CVE-2023-45648', 'url: https://lists.apache.org/thread/065jfyo583490r9j2v73nhpyxdob56lw', 'url: https://lists.apache.org/thread/3m81kt8c2gtg4nkjfwt2hvt5l9ycx6vl', 'url: https://lists.apache.org/thread/2pv8yz1pyp088tsxfb7ogltk9msk0jdp', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.0-M1', ',→2', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.14', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.81', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.94', 'url: https://cloud.google.com/blog/products/identity-security/how-it-works-the-n', ',→ovel-http2-rapid-reset-ddos-attack', 'url: https://blog.cloudflare.com/technical-breakdown-http2-rapid-reset-ddos-atta', ',→ck/', 'url: https://aws.amazon.com/blogs/security/how-aws-protects-customers-from-ddos-', ',→events/', 'url: https://www.openwall.com/lists/oss-security/2023/10/10/6', 'url: https://www.cisa.gov/news-events/alerts/2023/10/10/http2-rapid-reset-vulner', ',→ability-cve-2023-44487', 'url: https://www.cisa.gov/known-exploited-vulnerabilities-catalog', 'cisa: Known Exploited Vulnerability (KEV) catalog', 'cert-bund: WID-SEC-2025-0225', 'cert-bund: WID-SEC-2024-3684', 'cert-bund: WID-SEC-2024-1652', 'cert-bund: WID-SEC-2024-1643', 'cert-bund: WID-SEC-2024-1642', 'cert-bund: WID-SEC-2024-1307', 'cert-bund: WID-SEC-2024-1248', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-1228', 'cert-bund: WID-SEC-2024-0899', 'cert-bund: WID-SEC-2024-0894', 'cert-bund: WID-SEC-2024-0887', 'cert-bund: WID-SEC-2024-0874', 'cert-bund: WID-SEC-2024-0873', 'cert-bund: WID-SEC-2024-0870', 'cert-bund: WID-SEC-2024-0869', 'cert-bund: WID-SEC-2024-0794', 'cert-bund: WID-SEC-2024-0597', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2024-0521 cert-bund: WID-SEC-2024-0519', 'cert-bund: WID-SEC-2024-0123', 'cert-bund: WID-SEC-2024-0121', 'cert-bund: WID-SEC-2024-0118', 'cert-bund: WID-SEC-2024-0117', 'cert-bund: WID-SEC-2024-0116', 'cert-bund: WID-SEC-2024-0115', 'cert-bund: WID-SEC-2024-0108', 'cert-bund: WID-SEC-2024-0107', 'cert-bund: WID-SEC-2024-0106', 'cert-bund: WID-SEC-2024-0025', 'cert-bund: WID-SEC-2023-3146', 'cert-bund: WID-SEC-2023-2993', 'cert-bund: WID-SEC-2023-2963', 'cert-bund: WID-SEC-2023-2788', 'cert-bund: WID-SEC-2023-2723', 'cert-bund: WID-SEC-2023-2655', 'cert-bund: WID-SEC-2023-2628', 'cert-bund: WID-SEC-2023-2627', 'cert-bund: WID-SEC-2023-2618', 'cert-bund: WID-SEC-2023-2611', 'cert-bund: WID-SEC-2023-2606', 'dfn-cert: DFN-CERT-2025-2658', 'dfn-cert: DFN-CERT-2025-2038', 'dfn-cert: DFN-CERT-2025-1517', 'dfn-cert: DFN-CERT-2025-0267', 'dfn-cert: DFN-CERT-2024-3078', 'dfn-cert: DFN-CERT-2024-2706', 'dfn-cert: DFN-CERT-2024-2681', 'dfn-cert: DFN-CERT-2024-2487', 'dfn-cert: DFN-CERT-2024-2348', 'dfn-cert: DFN-CERT-2024-2290', 'dfn-cert: DFN-CERT-2024-1105', 'dfn-cert: DFN-CERT-2024-1016', 'dfn-cert: DFN-CERT-2024-1002', 'dfn-cert: DFN-CERT-2024-1000', 'dfn-cert: DFN-CERT-2024-0830', 'dfn-cert: DFN-CERT-2024-0819', 'dfn-cert: DFN-CERT-2024-0760', 'dfn-cert: DFN-CERT-2024-0526', 'dfn-cert: DFN-CERT-2024-0522', 'dfn-cert: DFN-CERT-2024-0491', 'dfn-cert: DFN-CERT-2024-0464', 'dfn-cert: DFN-CERT-2024-0411', 'dfn-cert: DFN-CERT-2024-0398', 'dfn-cert: DFN-CERT-2024-0367', 'dfn-cert: DFN-CERT-2024-0337 dfn-cert: DFN-CERT-2024-0149', 'dfn-cert: DFN-CERT-2024-0134', 'dfn-cert: DFN-CERT-2024-0133', 'dfn-cert: DFN-CERT-2024-0129', 'dfn-cert: DFN-CERT-2024-0081', 'dfn-cert: DFN-CERT-2024-0076', 'dfn-cert: DFN-CERT-2024-0048', 'dfn-cert: DFN-CERT-2023-3167', 'dfn-cert: DFN-CERT-2023-3124', 'dfn-cert: DFN-CERT-2023-3119', 'dfn-cert: DFN-CERT-2023-3073', 'dfn-cert: DFN-CERT-2023-3059', 'dfn-cert: DFN-CERT-2023-3035', 'dfn-cert: DFN-CERT-2023-3007', 'dfn-cert: DFN-CERT-2023-2996', 'dfn-cert: DFN-CERT-2023-2991', 'dfn-cert: DFN-CERT-2023-2971', 'dfn-cert: DFN-CERT-2023-2959', 'dfn-cert: DFN-CERT-2023-2912', 'dfn-cert: DFN-CERT-2023-2892', 'dfn-cert: DFN-CERT-2023-2882', 'dfn-cert: DFN-CERT-2023-2876', 'dfn-cert: DFN-CERT-2023-2864', 'dfn-cert: DFN-CERT-2023-2851', 'dfn-cert: DFN-CERT-2023-2849', 'dfn-cert: DFN-CERT-2023-2803', 'dfn-cert: DFN-CERT-2023-2787', 'dfn-cert: DFN-CERT-2023-2785', 'dfn-cert: DFN-CERT-2023-2730', 'dfn-cert: DFN-CERT-2023-2729', 'dfn-cert: DFN-CERT-2023-2708', 'dfn-cert: DFN-CERT-2023-2701', 'dfn-cert: DFN-CERT-2023-2696', 'dfn-cert: DFN-CERT-2023-2695', 'dfn-cert: DFN-CERT-2023-2680', 'dfn-cert: DFN-CERT-2023-2677', 'dfn-cert: DFN-CERT-2023-2675', 'dfn-cert: DFN-CERT-2023-2670', 'dfn-cert: DFN-CERT-2023-2666', 'dfn-cert: DFN-CERT-2023-2646', 'dfn-cert: DFN-CERT-2023-2637', 'dfn-cert: DFN-CERT-2023-2636', 'dfn-cert: DFN-CERT-2023-2635', 'dfn-cert: DFN-CERT-2023-2623', 'dfn-cert: DFN-CERT-2023-2603', 'dfn-cert: DFN-CERT-2023-2600', 'dfn-cert: DFN-CERT-2023-2599 dfn-cert: DFN-CERT-2023-2597', 'dfn-cert: DFN-CERT-2023-2596', 'dfn-cert: DFN-CERT-2023-2595', 'dfn-cert: DFN-CERT-2023-2590', 'dfn-cert: DFN-CERT-2023-2589', 'dfn-cert: DFN-CERT-2023-2586', 'dfn-cert: DFN-CERT-2023-2585', 'dfn-cert: DFN-CERT-2023-2572', 'dfn-cert: DFN-CERT-2023-2571', 'dfn-cert: DFN-CERT-2023-2568', 'dfn-cert: DFN-CERT-2023-2564', 'dfn-cert: DFN-CERT-2023-2556', 'dfn-cert: DFN-CERT-2023-2555', 'dfn-cert: DFN-CERT-2023-2552', 'dfn-cert: DFN-CERT-2023-2549', 'dfn-cert: DFN-CERT-2023-2547', 'dfn-cert: DFN-CERT-2023-2528', 'dfn-cert: DFN-CERT-2023-2522', 'dfn-cert: DFN-CERT-2023-2512', 'dfn-cert: DFN-CERT-2023-2504', 'dfn-cert: DFN-CERT-2023-2501', 'dfn-cert: DFN-CERT-2023-2487', 'dfn-cert: DFN-CERT-2023-2469', 'dfn-cert: DFN-CERT-2023-2468', 'dfn-cert: DFN-CERT-2023-2459', 'dfn-cert: DFN-CERT-2023-2457', 'dfn-cert: DFN-CERT-2023-2453', 'dfn-cert: DFN-CERT-2023-2450', 'dfn-cert: DFN-CERT-2023-2449', 'dfn-cert: DFN-CERT-2023-2439']</t>
@@ -4488,7 +3807,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
         <v>8081</v>
       </c>
@@ -4535,18 +3853,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4564,7 +3870,6 @@
           <t>Update to version 8.5.63, 9.0.43, 10.0.2 or later.</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>['cve: CVE-2021-25122', 'url: https://lists.apache.org/thread.html/r7b95bc248603360501f18c8eb03bb6001ec0e', ',→e3296205b34b07105b7@%3Cannounce.tomcat.apache.org%3E', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.0.2', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.43', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.63', 'cert-bund: WID-SEC-2022-1375', 'cert-bund: WID-SEC-2022-1099', 'cert-bund: WID-SEC-2022-0624', 'cert-bund: WID-SEC-2022-0607', 'cert-bund: CB-K21/1094', 'cert-bund: CB-K21/1081', 'cert-bund: CB-K21/0770', 'cert-bund: CB-K21/0222', 'dfn-cert: DFN-CERT-2024-1989', 'dfn-cert: DFN-CERT-2022-1530 dfn-cert: DFN-CERT-2022-0733', 'dfn-cert: DFN-CERT-2021-2191', 'dfn-cert: DFN-CERT-2021-1904', 'dfn-cert: DFN-CERT-2021-1537', 'dfn-cert: DFN-CERT-2021-1536', 'dfn-cert: DFN-CERT-2021-1403', 'dfn-cert: DFN-CERT-2021-0810', 'dfn-cert: DFN-CERT-2021-0807', 'dfn-cert: DFN-CERT-2021-0544', 'dfn-cert: DFN-CERT-2021-0445']</t>
@@ -4575,7 +3880,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
         <v>8081</v>
       </c>
@@ -4619,18 +3923,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4649,7 +3941,6 @@
 Update to version 8.5.41, 9.0.20 or later.</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>['cve: CVE-2019-10072', 'url: http://tomcat.apache.org/security-9.html', 'url: http://tomcat.apache.org/security-8.html', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: CB-K20/1008', 'cert-bund: CB-K20/0029', 'cert-bund: CB-K19/0915', 'cert-bund: CB-K19/0523', 'dfn-cert: DFN-CERT-2020-0501', 'dfn-cert: DFN-CERT-2020-0088', 'dfn-cert: DFN-CERT-2020-0027', 'dfn-cert: DFN-CERT-2019-2457', 'dfn-cert: DFN-CERT-2019-2149', 'dfn-cert: DFN-CERT-2019-1895', 'dfn-cert: DFN-CERT-2019-1472', 'dfn-cert: DFN-CERT-2019-1268']</t>
@@ -4660,7 +3951,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
         <v>8081</v>
       </c>
@@ -4704,18 +3994,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4733,7 +4011,6 @@
           <t>Update to version 8.5.41, 9.0.20 or later.</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>['cve: CVE-2019-10072', 'url: https://lists.apache.org/thread.html/df1a2c1b87c8a6c500ecdbbaf134c7f1491c8d-&gt;79d98b48c6b9f0fa6a@%3Cannounce.tomcat.apache.org%3E', 'url: http://www.securityfocus.com/bid/108874', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: CB-K20/1008', 'cert-bund: CB-K20/0029', 'cert-bund: CB-K19/0915', 'cert-bund: CB-K19/0523', 'dfn-cert: DFN-CERT-2020-0501', 'dfn-cert: DFN-CERT-2020-0088', 'dfn-cert: DFN-CERT-2020-0027', 'dfn-cert: DFN-CERT-2019-2457', 'dfn-cert: DFN-CERT-2019-2149', 'dfn-cert: DFN-CERT-2019-1895', 'dfn-cert: DFN-CERT-2019-1472', 'dfn-cert: DFN-CERT-2019-1268']</t>
@@ -4744,7 +4021,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
         <v>8081</v>
       </c>
@@ -4788,18 +4064,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4817,7 +4081,6 @@
           <t>Update to version 8.5.38, 9.0.16 or later.</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>['cve: CVE-2019-0199', 'url: http://tomcat.apache.org/security-9.html', 'url: http://tomcat.apache.org/security-8.html', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: CB-K20/0543', 'cert-bund: CB-K20/0029', 'cert-bund: CB-K19/0235', 'dfn-cert: DFN-CERT-2019-2710', 'dfn-cert: DFN-CERT-2019-1895', 'dfn-cert: DFN-CERT-2019-1755', 'dfn-cert: DFN-CERT-2019-1472', 'dfn-cert: DFN-CERT-2019-1231', 'dfn-cert: DFN-CERT-2019-1095', 'dfn-cert: DFN-CERT-2019-0594']</t>
@@ -4828,7 +4091,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
         <v>8081</v>
       </c>
@@ -4872,18 +4134,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4901,7 +4151,6 @@
           <t>Update to version 8.5.56, 9.0.36, 10.0.0-M6 or later.</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>['cve: CVE-2020-11996', 'url: https://lists.apache.org/thread.html/r5541ef6b6b68b49f76fc4c45695940116da2b', ',→cbe0312ef204a00a2e0%40%3Cannounce.tomcat.apache.org%3E', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2022-1375', 'cert-bund: CB-K20/1017', 'cert-bund: CB-K20/0637', 'cert-bund: CB-K20/0636', 'dfn-cert: DFN-CERT-2021-1736', 'dfn-cert: DFN-CERT-2021-0043', 'dfn-cert: DFN-CERT-2020-2006', 'dfn-cert: DFN-CERT-2020-1575', 'dfn-cert: DFN-CERT-2020-1490', 'dfn-cert: DFN-CERT-2020-1358']</t>
@@ -4912,7 +4161,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
         <v>8081</v>
       </c>
@@ -4941,7 +4189,6 @@
 Installation path / port: 8081/tcp</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
           <t>Product: cpe:/a:apache:tomcat:8.5.23
@@ -4949,18 +4196,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4978,7 +4213,6 @@
           <t>Update to version 8.5.57, 9.0.37, 10.0.0-M7 or later.</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>['cve: CVE-2020-13934', 'cve: CVE-2020-13935', 'url: https://lists.apache.org/thread.html/r61f411cf82488d6ec213063fc15feeeb88e31', ',→b0ca9c29652ee4f962e%40%3Cannounce.tomcat.apache.org%3E', 'url: https://lists.apache.org/thread.html/rd48c72bd3255bda87564d4da3791517c074d9', ',→4f8a701f93b85752651%40%3Cannounce.tomcat.apache.org%3E', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.0.0-M7', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.37', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.57', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2023-1048', 'cert-bund: WID-SEC-2022-1375', 'cert-bund: WID-SEC-2022-0519', 'cert-bund: CB-K20/1030', 'cert-bund: CB-K20/1021', 'cert-bund: CB-K20/1017', 'cert-bund: CB-K20/0717', 'dfn-cert: DFN-CERT-2022-1472 dfn-cert: DFN-CERT-2021-1736', 'dfn-cert: DFN-CERT-2021-0714', 'dfn-cert: DFN-CERT-2021-0132', 'dfn-cert: DFN-CERT-2020-2295', 'dfn-cert: DFN-CERT-2020-2287', 'dfn-cert: DFN-CERT-2020-2132', 'dfn-cert: DFN-CERT-2020-2006', 'dfn-cert: DFN-CERT-2020-1761', 'dfn-cert: DFN-CERT-2020-1707', 'dfn-cert: DFN-CERT-2020-1706', 'dfn-cert: DFN-CERT-2020-1575', 'dfn-cert: DFN-CERT-2020-1511']</t>
@@ -4989,7 +4223,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
         <v>8081</v>
       </c>
@@ -5032,18 +4265,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5062,7 +4283,6 @@
 Update to version 7.0.99, 8.5.50, 9.0.30 or later.</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>['cve: CVE-2019-17563', 'url: https://lists.apache.org/thread.html/8b4c1db8300117b28a0f3f743c0b9e3f964687a690cdf9662a884bbd%40%3Cannounce.tomcat.apache.org%3E', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2023-1229', 'cert-bund: WID-SEC-2023-1049', 'cert-bund: CB-K21/0071', 'cert-bund: CB-K20/1030', 'cert-bund: CB-K20/0318', 'cert-bund: CB-K20/0309', 'cert-bund: CB-K19/1102', 'dfn-cert: DFN-CERT-2021-0575', 'dfn-cert: DFN-CERT-2020-2132', 'dfn-cert: DFN-CERT-2020-1134', 'dfn-cert: DFN-CERT-2020-1129', 'dfn-cert: DFN-CERT-2020-0821', 'dfn-cert: DFN-CERT-2020-0780', 'dfn-cert: DFN-CERT-2020-0775', 'dfn-cert: DFN-CERT-2020-0557', 'dfn-cert: DFN-CERT-2020-0501', 'dfn-cert: DFN-CERT-2020-0345', 'dfn-cert: DFN-CERT-2020-0027', 'dfn-cert: DFN-CERT-2019-2710', 'dfn-cert: DFN-CERT-2019-2673']</t>
@@ -5073,7 +4293,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
         <v>8081</v>
       </c>
@@ -5119,18 +4338,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5163,7 +4370,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
         <v>8081</v>
       </c>
@@ -5204,18 +4410,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5233,7 +4427,6 @@
           <t>Update to version 8.5.83, 9.0.68, 10.0.27, 10.1.1 or later.</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>['http://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.10', 'http://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.0.53', 'http://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.32', 'http://tomcat.apache.org/security-7.html#Fixed_in_Apache_Tomcat_7.0.90', 'cert-bund: WID-SEC-2024-1682', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: CB-K19/0907', 'cert-bund: CB-K19/0616', 'cert-bund: CB-K19/0320', 'cert-bund: CB-K18/1005', 'cert-bund: CB-K18/0809', 'dfn-cert: DFN-CERT-2019-2418', 'dfn-cert: DFN-CERT-2019-1627', 'dfn-cert: DFN-CERT-2019-1237', 'dfn-cert: DFN-CERT-2019-0951', 'dfn-cert: DFN-CERT-2019-0451', 'dfn-cert: DFN-CERT-2019-0147', 'dfn-cert: DFN-CERT-2018-2165', 'dfn-cert: DFN-CERT-2018-2142', 'dfn-cert: DFN-CERT-2018-1753', 'dfn-cert: DFN-CERT-2018-1471', 'dfn-cert: DFN-CERT-2018-1443', 'dfn-cert: DFN-CERT-2018-1262']</t>
@@ -5244,7 +4437,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>8081</v>
       </c>
@@ -5276,25 +4468,12 @@
 path / port: 8081/tcp</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr">
         <is>
           <t>cpe:/a:apache:tomcat:8.5.23
 Detected by Apache Tomcat Detection Consolidation (OID: 1.3.6.1.4.1.25623.1.0.10  -&gt;7652)</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5327,7 +4506,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
         <v>8081</v>
       </c>
@@ -5372,18 +4550,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5401,7 +4567,6 @@
           <t>Update to version 8.5.96, 9.0.83, 10.1.16, 11.0.0-M11 or later.</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>['cve: CVE-2023-46589', 'url: https://lists.apache.org/thread/0rqq6ktozqc42ro8hhxdmmdjm1k1tpxr', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.0-M1', ',→1', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.16', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.83', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.96', 'cert-bund: WID-SEC-2025-0810', 'cert-bund: WID-SEC-2024-1653', 'cert-bund: WID-SEC-2024-1652', 'cert-bund: WID-SEC-2024-1642', 'cert-bund: WID-SEC-2024-1248', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-0899', 'cert-bund: WID-SEC-2024-0890', 'cert-bund: WID-SEC-2024-0873', 'cert-bund: WID-SEC-2024-0869', 'cert-bund: WID-SEC-2024-0769', 'cert-bund: WID-SEC-2024-0119', 'cert-bund: WID-SEC-2024-0108', 'cert-bund: WID-SEC-2024-0106', 'cert-bund: WID-SEC-2024-0101 cert-bund: WID-SEC-2024-0094', 'cert-bund: WID-SEC-2023-3020', 'dfn-cert: DFN-CERT-2024-1404', 'dfn-cert: DFN-CERT-2024-1036', 'dfn-cert: DFN-CERT-2024-1000', 'dfn-cert: DFN-CERT-2024-0723', 'dfn-cert: DFN-CERT-2024-0722', 'dfn-cert: DFN-CERT-2024-0506', 'dfn-cert: DFN-CERT-2024-0411', 'dfn-cert: DFN-CERT-2024-0174', 'dfn-cert: DFN-CERT-2024-0127', 'dfn-cert: DFN-CERT-2023-2977']</t>
@@ -5412,7 +4577,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
         <v>8081</v>
       </c>
@@ -5457,18 +4621,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5487,7 +4639,6 @@
 Update Apache Tomcat to version 10.1.0-M15, 10.0.21, 9.0.63, 8.5.79 or later to receive the corrected / updated documentation</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>['cve: CVE-2022-29885', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.0-M1', ',→5', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.0.21', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.63', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.79', 'url: https://lists.apache.org/thread/548bnqoxvp0rqqq2yyj90l0xvwhq087d', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2022-1780', 'cert-bund: WID-SEC-2022-1767', 'cert-bund: WID-SEC-2022-0799', 'cert-bund: WID-SEC-2022-0467', 'cert-bund: CB-K22/0597', 'dfn-cert: DFN-CERT-2024-1989', 'dfn-cert: DFN-CERT-2024-0762', 'dfn-cert: DFN-CERT-2022-2392', 'dfn-cert: DFN-CERT-2022-2323', 'dfn-cert: DFN-CERT-2022-1070']</t>
@@ -5498,7 +4649,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
         <v>8081</v>
       </c>
@@ -5542,18 +4692,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5566,8 +4704,6 @@
           <t>Apache Tomcat is prone to a denial of service (DoS) vulnerability.</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t>['cve: CVE-2023-24998', 'url: https://lists.apache.org/thread/g16kv0xpp272htz107molwbbgdrqrdk1', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.0-M3', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.5', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.71', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.85 url: https://lists.apache.org/thread/4xl4l09mhwg4vgsk7dxqogcjrobrrdoy', 'cert-bund: WID-SEC-2025-0810', 'cert-bund: WID-SEC-2024-1652', 'cert-bund: WID-SEC-2024-1642', 'cert-bund: WID-SEC-2024-1637', 'cert-bund: WID-SEC-2024-1622', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-0890', 'cert-bund: WID-SEC-2024-0888', 'cert-bund: WID-SEC-2024-0794', 'cert-bund: WID-SEC-2024-0124', 'cert-bund: WID-SEC-2024-0117', 'cert-bund: WID-SEC-2024-0054', 'cert-bund: WID-SEC-2023-2688', 'cert-bund: WID-SEC-2023-2675', 'cert-bund: WID-SEC-2023-2674', 'cert-bund: WID-SEC-2023-2625', 'cert-bund: WID-SEC-2023-2309', 'cert-bund: WID-SEC-2023-2031', 'cert-bund: WID-SEC-2023-1817', 'cert-bund: WID-SEC-2023-1815', 'cert-bund: WID-SEC-2023-1813', 'cert-bund: WID-SEC-2023-1812', 'cert-bund: WID-SEC-2023-1811', 'cert-bund: WID-SEC-2023-1809', 'cert-bund: WID-SEC-2023-1808', 'cert-bund: WID-SEC-2023-1807', 'cert-bund: WID-SEC-2023-1794', 'cert-bund: WID-SEC-2023-1792', 'cert-bund: WID-SEC-2023-1791', 'cert-bund: WID-SEC-2023-1784', 'cert-bund: WID-SEC-2023-1783', 'cert-bund: WID-SEC-2023-1782', 'cert-bund: WID-SEC-2023-1424', 'cert-bund: WID-SEC-2023-1142', 'cert-bund: WID-SEC-2023-1021', 'cert-bund: WID-SEC-2023-1017', 'cert-bund: WID-SEC-2023-1016', 'cert-bund: WID-SEC-2023-1012', 'cert-bund: WID-SEC-2023-1007', 'cert-bund: WID-SEC-2023-1005', 'cert-bund: WID-SEC-2023-0609', 'cert-bund: WID-SEC-2023-0433', 'dfn-cert: DFN-CERT-2025-1992', 'dfn-cert: DFN-CERT-2024-2151', 'dfn-cert: DFN-CERT-2024-1865', 'dfn-cert: DFN-CERT-2024-1006 dfn-cert: DFN-CERT-2024-0059', 'dfn-cert: DFN-CERT-2024-0048', 'dfn-cert: DFN-CERT-2023-2778', 'dfn-cert: DFN-CERT-2023-2545', 'dfn-cert: DFN-CERT-2023-2469', 'dfn-cert: DFN-CERT-2023-2054', 'dfn-cert: DFN-CERT-2023-1648', 'dfn-cert: DFN-CERT-2023-1643', 'dfn-cert: DFN-CERT-2023-1642', 'dfn-cert: DFN-CERT-2023-1423', 'dfn-cert: DFN-CERT-2023-1362', 'dfn-cert: DFN-CERT-2023-1109', 'dfn-cert: DFN-CERT-2023-0902', 'dfn-cert: DFN-CERT-2023-0886', 'dfn-cert: DFN-CERT-2023-0884', 'dfn-cert: DFN-CERT-2023-0881', 'dfn-cert: DFN-CERT-2023-0763', 'dfn-cert: DFN-CERT-2023-0574', 'dfn-cert: DFN-CERT-2023-0540', 'dfn-cert: DFN-CERT-2023-0414']</t>
@@ -5578,7 +4714,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
         <v>8081</v>
       </c>
@@ -5622,18 +4757,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5669,7 +4792,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
         <v>8081</v>
       </c>
@@ -5712,18 +4834,6 @@
 Method: Apache Tomcat Detection Consolidation</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5741,7 +4851,6 @@
           <t>Update to version 7.0.108, 8.5.63, 9.0.43, 10.0.2 or later.</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>['cve: CVE-2021-25329', 'url: https://lists.apache.org/thread.html/rfe62fbf9d4c314f166fe8c668e50e5d9dd882', ',→a99447f26f0367474bf@%3Cannounce.tomcat.apache.org%3E', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.0.2', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.43', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.63', 'url: https://tomcat.apache.org/security-7.html#Fixed_in_Apache_Tomcat_7.0.108', 'cert-bund: WID-SEC-2022-1099', 'cert-bund: WID-SEC-2022-0607', 'cert-bund: CB-K21/0222', 'dfn-cert: DFN-CERT-2024-1926', 'dfn-cert: DFN-CERT-2022-1530', 'dfn-cert: DFN-CERT-2022-0733', 'dfn-cert: DFN-CERT-2021-1904', 'dfn-cert: DFN-CERT-2021-1403', 'dfn-cert: DFN-CERT-2021-0903 dfn-cert: DFN-CERT-2021-0835', 'dfn-cert: DFN-CERT-2021-0807', 'dfn-cert: DFN-CERT-2021-0714', 'dfn-cert: DFN-CERT-2021-0544', 'dfn-cert: DFN-CERT-2021-0445']</t>
@@ -5752,7 +4861,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
         <v>8081</v>
       </c>
@@ -5796,18 +4904,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5825,7 +4921,6 @@
           <t>Update to version 7.0.109, 8.5.66, 9.0.46, 10.0.6 or later.</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>['cve: CVE-2021-30640', 'url: https://lists.apache.org/thread.html/r59f9ef03929d32120f91f4ea7e6e79edd5688', ',→d75d0a9b65fd26d1fe8%40%3Cannounce.tomcat.apache.org%3E', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.0.6', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.46', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.66', 'url: https://tomcat.apache.org/security-7.html#Fixed_in_Apache_Tomcat_7.0.109', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2022-1116', 'cert-bund: WID-SEC-2022-0623', 'cert-bund: WID-SEC-2022-0615', 'cert-bund: WID-SEC-2022-0607', 'cert-bund: CB-K21/0733', 'dfn-cert: DFN-CERT-2022-1530', 'dfn-cert: DFN-CERT-2022-0826', 'dfn-cert: DFN-CERT-2022-0733', 'dfn-cert: DFN-CERT-2021-2496', 'dfn-cert: DFN-CERT-2021-2438', 'dfn-cert: DFN-CERT-2021-2297', 'dfn-cert: DFN-CERT-2021-2169', 'dfn-cert: DFN-CERT-2021-1728', 'dfn-cert: DFN-CERT-2021-1668', 'dfn-cert: DFN-CERT-2021-1472']</t>
@@ -5836,7 +4931,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
         <v>8040</v>
       </c>
@@ -5881,18 +4975,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5910,7 +4992,6 @@
           <t>Upgrade to Apache Tomcat version 9.0.5, 8.5.28, 8.0.50, 7.0.85 or later.</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>['cve: CVE-2018-1305', 'cve: CVE-2018-1304', 'url: http://tomcat.apache.org/security-9.html', 'url: http://www.securityfocus.com/bid/103144', 'url: http://www.securityfocus.com/bid/103170', 'url: http://tomcat.apache.org/security-8.html', 'url: http://tomcat.apache.org/security-7.html', 'url: https://lists.apache.org/thread.html/b1d7e2425d6fd2cebed40d318f9365b4454607', ',→7e10949b01b1f8a0fb@%3Cannounce.tomcat.apache.org%3E', 'cert-bund: WID-SEC-2024-1682', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: CB-K19/1121', 'cert-bund: CB-K19/0321', 'cert-bund: CB-K18/1007', 'cert-bund: CB-K18/1006', 'cert-bund: CB-K18/1005', 'cert-bund: CB-K18/0790', 'cert-bund: CB-K18/0420', 'cert-bund: CB-K18/0349', 'dfn-cert: DFN-CERT-2019-1627', 'dfn-cert: DFN-CERT-2019-0772', 'dfn-cert: DFN-CERT-2018-2165', 'dfn-cert: DFN-CERT-2018-2142', 'dfn-cert: DFN-CERT-2018-2125', 'dfn-cert: DFN-CERT-2018-2103', 'dfn-cert: DFN-CERT-2018-1753', 'dfn-cert: DFN-CERT-2018-1407', 'dfn-cert: DFN-CERT-2018-1274', 'dfn-cert: DFN-CERT-2018-1253', 'dfn-cert: DFN-CERT-2018-1038', 'dfn-cert: DFN-CERT-2018-0922', 'dfn-cert: DFN-CERT-2018-0733', 'dfn-cert: DFN-CERT-2018-0455', 'dfn-cert: DFN-CERT-2018-0378']</t>
@@ -5921,7 +5002,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
         <v>8040</v>
       </c>
@@ -5970,18 +5050,6 @@
 Method: Apache Tomcat Detection Consolidation OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5999,7 +5067,6 @@
           <t>Update to version 9.0.96, 10.1.31, 11.0.0 or later.</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>['cve: CVE-2024-52316 url: https://lists.apache.org/thread/lopzlqh91jj9n334g02om08sbysdb928', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.0', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.31', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.96', 'cert-bund: WID-SEC-2025-0521', 'cert-bund: WID-SEC-2024-3684', 'cert-bund: WID-SEC-2024-3486', 'dfn-cert: DFN-CERT-2025-2285', 'dfn-cert: DFN-CERT-2025-2098', 'dfn-cert: DFN-CERT-2025-0890', 'dfn-cert: DFN-CERT-2025-0146', 'dfn-cert: DFN-CERT-2025-0134', 'dfn-cert: DFN-CERT-2024-3156', 'dfn-cert: DFN-CERT-2024-3077']</t>
@@ -6010,7 +5077,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
         <v>8040</v>
       </c>
@@ -6057,18 +5123,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6086,7 +5140,6 @@
           <t>Update to version 8.5.93, 9.0.80, 10.1.13, 11.0.0-M11 or later.</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>['cve: CVE-2023-41080', 'url: https://lists.apache.org/thread/71wvwprtx2j2m54fovq9zr7gbm2wow2f', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.0-M1', ',→1', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.13', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.80', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.93', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-0871', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2023-3070', 'cert-bund: WID-SEC-2023-2917', 'cert-bund: WID-SEC-2023-2690', 'cert-bund: WID-SEC-2023-2679', 'cert-bund: WID-SEC-2023-2182', 'dfn-cert: DFN-CERT-2024-3078', 'dfn-cert: DFN-CERT-2024-0723', 'dfn-cert: DFN-CERT-2024-0076', 'dfn-cert: DFN-CERT-2023-3070', 'dfn-cert: DFN-CERT-2023-3061', 'dfn-cert: DFN-CERT-2023-2803', 'dfn-cert: DFN-CERT-2023-2586', 'dfn-cert: DFN-CERT-2023-2568', 'dfn-cert: DFN-CERT-2023-2542', 'dfn-cert: DFN-CERT-2023-2536', 'dfn-cert: DFN-CERT-2023-2469', 'dfn-cert: DFN-CERT-2023-2468', 'dfn-cert: DFN-CERT-2023-1983']</t>
@@ -6097,7 +5150,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
         <v>8040</v>
       </c>
@@ -6114,7 +5166,6 @@
       <c r="K68" t="n">
         <v>6.1</v>
       </c>
-      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
           <t>Installed version: 8.5.23
@@ -6122,7 +5173,6 @@
 Installation path / port: 8040/tcp</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr">
         <is>
           <t>Product: cpe:/a:apache:tomcat:8.5.23
@@ -6130,18 +5180,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6176,7 +5214,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
         <v>8040</v>
       </c>
@@ -6220,18 +5257,6 @@
 Method: Apache Tomcat Detection Consolidation</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6264,7 +5289,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
         <v>8040</v>
       </c>
@@ -6308,18 +5332,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6337,7 +5349,6 @@
           <t>Update to version 7.0.107, 8.5.60, 9.0.40, 10.0.0-M10 or later.</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>['cve: CVE-2021-24122', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.0.0-M1', ',→0', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.40', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.60', 'url: https://tomcat.apache.org/security-7.html#Fixed_in_Apache_Tomcat_7.0.107', 'url: https://lists.apache.org/thread.html/rce5ac9a40173651d540babce59f6f3825f12c ,→6d4e886ba00823b11e5%40%3Cannounce.tomcat.apache.org%3E', 'cert-bund: WID-SEC-2023-2465', 'cert-bund: WID-SEC-2022-0607', 'cert-bund: CB-K21/0049', 'dfn-cert: DFN-CERT-2022-1530', 'dfn-cert: DFN-CERT-2021-1904', 'dfn-cert: DFN-CERT-2021-0835', 'dfn-cert: DFN-CERT-2021-0714', 'dfn-cert: DFN-CERT-2021-0544', 'dfn-cert: DFN-CERT-2021-0338', 'dfn-cert: DFN-CERT-2020-2646']</t>
@@ -6348,7 +5359,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
         <v>8040</v>
       </c>
@@ -6392,18 +5402,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6436,7 +5434,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
         <v>8040</v>
       </c>
@@ -6480,18 +5477,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6509,7 +5494,6 @@
           <t>Update to version 8.5.68, 9.0.48, 10.0.7 or later.</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>['cve: CVE-2021-33037', 'url: https://lists.apache.org/thread.html/r612a79269b0d5e5780c62dfd34286a8037232-&gt;fec0bc6f1a7e60c9381%40%3Cannounce.tomcat.apache.org%3E', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.0.7', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.48', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.68', 'cert-bund: WID-SEC-2024-2180', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2022-1894', 'cert-bund: WID-SEC-2022-1375', 'cert-bund: WID-SEC-2022-1296', 'cert-bund: WID-SEC-2022-1116', 'cert-bund: WID-SEC-2022-0624', 'cert-bund: WID-SEC-2022-0623', 'cert-bund: WID-SEC-2022-0615 cert-bund: WID-SEC-2022-0607 cert-bund: WID-SEC-2022-0094', 'cert-bund: CB-K22/0066', 'cert-bund: CB-K21/1087', 'cert-bund: CB-K21/1084', 'cert-bund: CB-K21/0733', 'dfn-cert: DFN-CERT-2022-1530', 'dfn-cert: DFN-CERT-2022-0872', 'dfn-cert: DFN-CERT-2022-0826', 'dfn-cert: DFN-CERT-2022-0733', 'dfn-cert: DFN-CERT-2021-2496', 'dfn-cert: DFN-CERT-2021-2297', 'dfn-cert: DFN-CERT-2021-2223', 'dfn-cert: DFN-CERT-2021-2193', 'dfn-cert: DFN-CERT-2021-2188', 'dfn-cert: DFN-CERT-2021-1728', 'dfn-cert: DFN-CERT-2021-1668', 'dfn-cert: DFN-CERT-2021-1472']</t>
@@ -6520,7 +5504,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
         <v>8040</v>
       </c>
@@ -6565,18 +5548,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6595,7 +5566,6 @@
           <t>Update to version 8.5.64, 9.0.44 or later.</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>['cve: CVE-2024-21733', 'url: https://lists.apache.org/thread/h9bjqdd0odj6lhs2o96qgowcc6hb0cfz', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.44', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.64', 'cert-bund: WID-SEC-2024-0769', 'cert-bund: WID-SEC-2024-0163', 'dfn-cert: DFN-CERT-2025-1517', 'dfn-cert: DFN-CERT-2025-0134', 'dfn-cert: DFN-CERT-2024-1404', 'dfn-cert: DFN-CERT-2024-0648']</t>
@@ -6606,7 +5576,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
         <v>8040</v>
       </c>
@@ -6650,18 +5619,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6679,7 +5636,6 @@
           <t>Update to version 8.5.99, 9.0.86, 10.1.19, 11.0.0-M17 or later.</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>['cve: CVE-2024-23672', 'cve: CVE-2024-24549', 'url: https://lists.apache.org/thread/cmpswfx6tj4s7x0nxxosvfqs11lvdx2f', 'url: https://lists.apache.org/thread/4c50rmomhbbsdgfjsgwlb51xdwfjdcvg', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.0-M1', ',→7', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.19', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.86', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.99', 'url: https://nowotarski.info/http2-continuation-flood/', 'url: https://nowotarski.info/http2-continuation-flood-technical-details/', 'cert-bund: WID-SEC-2024-3663', 'cert-bund: WID-SEC-2024-3508', 'cert-bund: WID-SEC-2024-3377 cert-bund: WID-SEC-2024-3220', 'cert-bund: WID-SEC-2024-3219', 'cert-bund: WID-SEC-2024-3196', 'cert-bund: WID-SEC-2024-3195', 'cert-bund: WID-SEC-2024-3191', 'cert-bund: WID-SEC-2024-1656', 'cert-bund: WID-SEC-2024-1642', 'cert-bund: WID-SEC-2024-1638', 'cert-bund: WID-SEC-2024-1622', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-1214', 'cert-bund: WID-SEC-2024-1210', 'cert-bund: WID-SEC-2024-0769', 'cert-bund: WID-SEC-2024-0630', 'dfn-cert: DFN-CERT-2025-1517', 'dfn-cert: DFN-CERT-2024-3096', 'dfn-cert: DFN-CERT-2024-3078', 'dfn-cert: DFN-CERT-2024-2743', 'dfn-cert: DFN-CERT-2024-1846', 'dfn-cert: DFN-CERT-2024-1372', 'dfn-cert: DFN-CERT-2024-1235', 'dfn-cert: DFN-CERT-2024-1036', 'dfn-cert: DFN-CERT-2024-1011', 'dfn-cert: DFN-CERT-2024-0723', 'dfn-cert: DFN-CERT-2024-0722', 'dfn-cert: DFN-CERT-2024-0697']</t>
@@ -6690,7 +5646,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
         <v>8040</v>
       </c>
@@ -6736,18 +5691,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6760,8 +5703,6 @@
           <t>Apache Tomcat is prone to multiple vulnerabilities.</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>['cert-bund: WID-SEC-2024-3377', 'cert-bund: WID-SEC-2024-3220', 'cert-bund: WID-SEC-2024-3219', 'cert-bund: WID-SEC-2024-3196', 'cert-bund: WID-SEC-2024-3195', 'cert-bund: WID-SEC-2024-3191', 'cert-bund: WID-SEC-2024-1656', 'cert-bund: WID-SEC-2024-1642', 'cert-bund: WID-SEC-2024-1638', 'cert-bund: WID-SEC-2024-1622', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-1214', 'cert-bund: WID-SEC-2024-1210', 'cert-bund: WID-SEC-2024-0769', 'cert-bund: WID-SEC-2024-0630', 'dfn-cert: DFN-CERT-2025-1517', 'dfn-cert: DFN-CERT-2024-3096', 'dfn-cert: DFN-CERT-2024-3078', 'dfn-cert: DFN-CERT-2024-2743', 'dfn-cert: DFN-CERT-2024-1846', 'dfn-cert: DFN-CERT-2024-1372', 'dfn-cert: DFN-CERT-2024-1235', 'dfn-cert: DFN-CERT-2024-1036', 'dfn-cert: DFN-CERT-2024-1011', 'dfn-cert: DFN-CERT-2024-0723', 'dfn-cert: DFN-CERT-2024-0722', 'dfn-cert: DFN-CERT-2024-0697']</t>
@@ -6772,7 +5713,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
         <v>8040</v>
       </c>
@@ -6834,17 +5774,6 @@
 incomplete</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6863,7 +5792,6 @@
           <t>Update to version 9.0.105, 10.1.41, 11.0.7 or later.</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>['cve: CVE-2025-46701', 'url: https://lists.apache.org/thread/xhqqk9w5q45srcdqhogdk04lhdscv30j', 'cert-bund: WID-SEC-2025-1850', 'cert-bund: WID-SEC-2025-1365', 'cert-bund: WID-SEC-2025-1165', 'dfn-cert: DFN-CERT-2025-2285', 'dfn-cert: DFN-CERT-2025-2098', 'dfn-cert: DFN-CERT-2025-1991', 'dfn-cert: DFN-CERT-2025-1905', 'dfn-cert: DFN-CERT-2025-1780', 'dfn-cert: DFN-CERT-2025-1384']</t>
@@ -6874,7 +5802,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
         <v>8040</v>
       </c>
@@ -6918,18 +5845,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6947,7 +5862,6 @@
           <t>Update to version 8.5.86, 9.0.72, 10.1.6, 11.0.0-M3 or later.</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>['cve: CVE-2023-28708', 'url: https://lists.apache.org/thread/hdksc59z3s7tm39x0pp33mtwdrt8qr67', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.0-M3', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.6', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.72', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.86', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2023-2674', 'cert-bund: WID-SEC-2023-1812', 'cert-bund: WID-SEC-2023-1808', 'cert-bund: WID-SEC-2023-1784', 'cert-bund: WID-SEC-2023-1783', 'cert-bund: WID-SEC-2023-1782', 'cert-bund: WID-SEC-2023-1424', 'cert-bund: WID-SEC-2023-1021', 'cert-bund: WID-SEC-2023-1017', 'cert-bund: WID-SEC-2023-0717', 'dfn-cert: DFN-CERT-2025-1517', 'dfn-cert: DFN-CERT-2024-3078', 'dfn-cert: DFN-CERT-2023-2778', 'dfn-cert: DFN-CERT-2023-2545', 'dfn-cert: DFN-CERT-2023-2054', 'dfn-cert: DFN-CERT-2023-0772', 'dfn-cert: DFN-CERT-2023-0763', 'dfn-cert: DFN-CERT-2023-0640']</t>
@@ -6958,7 +5872,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
         <v>8040</v>
       </c>
@@ -7002,18 +5915,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7031,7 +5932,6 @@
           <t>Update to version 8.5.58, 9.0.38, 10.0.0-M8 or later.</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>['cve: CVE-2020-13943', 'url: https://lists.apache.org/thread.html/r4a390027eb27e4550142fac6c8317cc684b157ae314d31514747f307%40%3Cannounce.tomcat.apache.org%3E', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2023-2467', 'cert-bund: CB-K20/0971', 'dfn-cert: DFN-CERT-2022-0733', 'dfn-cert: DFN-CERT-2021-2620', 'dfn-cert: DFN-CERT-2021-0338', 'dfn-cert: DFN-CERT-2021-0134', 'dfn-cert: DFN-CERT-2021-0034', 'dfn-cert: DFN-CERT-2020-2224']</t>
@@ -7042,7 +5942,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
         <v>8040</v>
       </c>
@@ -7086,18 +5985,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -7115,7 +6002,6 @@
           <t>Update to version 7.0.91, 8.5.34, 9.0.12 or later.</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>['cve: CVE-2018-11784', 'url: http://tomcat.apache.org/security-9.html', 'url: http://tomcat.apache.org/security-8.html', 'url: http://tomcat.apache.org/security-7.html', 'cert-bund: WID-SEC-2025-1212', 'cert-bund: WID-SEC-2024-1682', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2023-0531 cert-bund: WID-SEC-2023-0460', 'cert-bund: CB-K20/0029', 'cert-bund: CB-K19/1121', 'cert-bund: CB-K19/0907', 'cert-bund: CB-K19/0616', 'cert-bund: CB-K19/0320', 'cert-bund: CB-K19/0050', 'cert-bund: CB-K18/0963', 'dfn-cert: DFN-CERT-2019-2710', 'dfn-cert: DFN-CERT-2019-2159', 'dfn-cert: DFN-CERT-2019-1562', 'dfn-cert: DFN-CERT-2019-1237', 'dfn-cert: DFN-CERT-2019-0771', 'dfn-cert: DFN-CERT-2019-0147', 'dfn-cert: DFN-CERT-2019-0104', 'dfn-cert: DFN-CERT-2018-2435', 'dfn-cert: DFN-CERT-2018-2165', 'dfn-cert: DFN-CERT-2018-2142', 'dfn-cert: DFN-CERT-2018-2000']</t>
@@ -7126,7 +6012,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
         <v>8040</v>
       </c>
@@ -7143,7 +6028,6 @@
       <c r="K80" t="n">
         <v>6.5</v>
       </c>
-      <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
           <t>Installed version: 8.5.23
@@ -7166,18 +6050,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -7195,7 +6067,6 @@
           <t>Update to version 7.0.91, 8.5.34, 9.0.12 or later.</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>['cve: CVE-2021-30640', 'url: https://lists.apache.org/thread.html/r59f9ef03929d32120f91f4ea7e6e79edd5688', ',→d75d0a9b65fd26d1fe8%40%3Cannounce.tomcat.apache.org%3E', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.0.6', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.46', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.66', 'url: https://tomcat.apache.org/security-7.html#Fixed_in_Apache_Tomcat_7.0.109', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2022-1116', 'cert-bund: WID-SEC-2022-0623', 'cert-bund: WID-SEC-2022-0615', 'cert-bund: WID-SEC-2022-0607', 'cert-bund: CB-K21/0733', 'dfn-cert: DFN-CERT-2022-1530', 'dfn-cert: DFN-CERT-2022-0826', 'dfn-cert: DFN-CERT-2022-0733', 'dfn-cert: DFN-CERT-2021-2496', 'dfn-cert: DFN-CERT-2021-2438 dfn-cert: DFN-CERT-2021-2297', 'dfn-cert: DFN-CERT-2021-2169', 'dfn-cert: DFN-CERT-2021-1728', 'dfn-cert: DFN-CERT-2021-1668', 'dfn-cert: DFN-CERT-2021-1472']</t>
@@ -7206,7 +6077,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
         <v>8081</v>
       </c>
@@ -7223,7 +6093,6 @@
       <c r="K81" t="n">
         <v>6.5</v>
       </c>
-      <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
           <t>Installed version: 8.5.23
@@ -7247,18 +6116,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7292,7 +6149,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
         <v>8081</v>
       </c>
@@ -7338,18 +6194,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7368,7 +6212,6 @@
           <t>Update to version 9.0.96, 10.1.31, 11.0.0 or later.</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>['cve: CVE-2024-52316', 'url: https://lists.apache.org/thread/lopzlqh91jj9n334g02om08sbysdb928', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.0', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.31', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.96', 'cert-bund: WID-SEC-2025-0521', 'cert-bund: WID-SEC-2024-3684', 'cert-bund: WID-SEC-2024-3486', 'dfn-cert: DFN-CERT-2025-2285', 'dfn-cert: DFN-CERT-2025-2098', 'dfn-cert: DFN-CERT-2025-0890', 'dfn-cert: DFN-CERT-2025-0146', 'dfn-cert: DFN-CERT-2025-0134', 'dfn-cert: DFN-CERT-2024-3156', 'dfn-cert: DFN-CERT-2024-3077']</t>
@@ -7379,7 +6222,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
         <v>8081</v>
       </c>
@@ -7425,18 +6267,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr"/>
-      <c r="R83" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7454,7 +6284,6 @@
           <t>Update to version 7.0.94, 8.5.40, 9.0.18 or later.</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>['cve: CVE-2019-0221', 'url: https://seclists.org/fulldisclosure/2019/May/50', 'url: https://lists.apache.org/thread.html/6e6e9eacf7b28fd63d249711e9d3ccd4e0a83f556e324aee37be5a8c@%3Cannounce.tomcat.apache.org%3E', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2023-1994', 'cert-bund: CB-K20/0029', 'cert-bund: CB-K19/0434', 'dfn-cert: DFN-CERT-2024-1926', 'dfn-cert: DFN-CERT-2021-0819', 'dfn-cert: DFN-CERT-2020-1129', 'dfn-cert: DFN-CERT-2020-1094', 'dfn-cert: DFN-CERT-2020-0557', 'dfn-cert: DFN-CERT-2019-2710', 'dfn-cert: DFN-CERT-2019-2457', 'dfn-cert: DFN-CERT-2019-1895', 'dfn-cert: DFN-CERT-2019-1704', 'dfn-cert: DFN-CERT-2019-1472', 'dfn-cert: DFN-CERT-2019-1231 dfn-cert: DFN-CERT-2019-1092']</t>
@@ -7465,7 +6294,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
         <v>8081</v>
       </c>
@@ -7509,18 +6337,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7539,7 +6355,6 @@
           <t>Update to version 8.5.93, 9.0.80, 10.1.13, 11.0.0-M11 or later.</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>['cve: CVE-2023-41080', 'url: https://lists.apache.org/thread/71wvwprtx2j2m54fovq9zr7gbm2wow2f', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.0-M1', ',→1', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.13', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.80', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.93', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-0871', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2023-3070', 'cert-bund: WID-SEC-2023-2917', 'cert-bund: WID-SEC-2023-2690', 'cert-bund: WID-SEC-2023-2679', 'cert-bund: WID-SEC-2023-2182', 'dfn-cert: DFN-CERT-2024-3078', 'dfn-cert: DFN-CERT-2024-0723', 'dfn-cert: DFN-CERT-2024-0076', 'dfn-cert: DFN-CERT-2023-3070', 'dfn-cert: DFN-CERT-2023-3061', 'dfn-cert: DFN-CERT-2023-2803', 'dfn-cert: DFN-CERT-2023-2586', 'dfn-cert: DFN-CERT-2023-2568', 'dfn-cert: DFN-CERT-2023-2542', 'dfn-cert: DFN-CERT-2023-2536', 'dfn-cert: DFN-CERT-2023-2469', 'dfn-cert: DFN-CERT-2023-2468', 'dfn-cert: DFN-CERT-2023-1983']</t>
@@ -7550,7 +6365,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
         <v>8081</v>
       </c>
@@ -7592,18 +6406,6 @@
 Method: Apache Tomcat Detection Consolidation OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7636,7 +6438,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
         <v>8081</v>
       </c>
@@ -7680,18 +6481,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -7710,7 +6499,6 @@
           <t>Update to version 7.0.107, 8.5.60, 9.0.40, 10.0.0-M10 or later.</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>['cve: CVE-2021-24122', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.0.0-M1', ',→0', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.40', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.60', 'url: https://tomcat.apache.org/security-7.html#Fixed_in_Apache_Tomcat_7.0.107', 'url: https://lists.apache.org/thread.html/rce5ac9a40173651d540babce59f6f3825f12c', ',→6d4e886ba00823b11e5%40%3Cannounce.tomcat.apache.org%3E', 'cert-bund: WID-SEC-2023-2465', 'cert-bund: WID-SEC-2022-0607', 'cert-bund: CB-K21/0049', 'dfn-cert: DFN-CERT-2022-1530', 'dfn-cert: DFN-CERT-2021-1904', 'dfn-cert: DFN-CERT-2021-0835', 'dfn-cert: DFN-CERT-2021-0714', 'dfn-cert: DFN-CERT-2021-0544', 'dfn-cert: DFN-CERT-2021-0338', 'dfn-cert: DFN-CERT-2020-2646']</t>
@@ -7721,7 +6509,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
         <v>8081</v>
       </c>
@@ -7765,18 +6552,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -7789,8 +6564,6 @@
           <t>Apache Tomcat is prone to an HTTP request smuggling vulnerability.</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>['cve: CVE-2021-33037', 'url: https://lists.apache.org/thread.html/r612a79269b0d5e5780c62dfd34286a8037232', ',→fec0bc6f1a7e60c9381%40%3Cannounce.tomcat.apache.org%3E', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.0.7', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.48', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.68', 'cert-bund: WID-SEC-2024-2180', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2022-1894', 'cert-bund: WID-SEC-2022-1375', 'cert-bund: WID-SEC-2022-1296', 'cert-bund: WID-SEC-2022-1116', 'cert-bund: WID-SEC-2022-0624', 'cert-bund: WID-SEC-2022-0623', 'cert-bund: WID-SEC-2022-0615', 'cert-bund: WID-SEC-2022-0607', 'cert-bund: WID-SEC-2022-0094', 'cert-bund: CB-K22/0066 cert-bund: CB-K21/1087', 'cert-bund: CB-K21/1084', 'cert-bund: CB-K21/0733', 'dfn-cert: DFN-CERT-2022-1530', 'dfn-cert: DFN-CERT-2022-0872', 'dfn-cert: DFN-CERT-2022-0826', 'dfn-cert: DFN-CERT-2022-0733', 'dfn-cert: DFN-CERT-2021-2496', 'dfn-cert: DFN-CERT-2021-2297', 'dfn-cert: DFN-CERT-2021-2223', 'dfn-cert: DFN-CERT-2021-2193', 'dfn-cert: DFN-CERT-2021-2188', 'dfn-cert: DFN-CERT-2021-1728', 'dfn-cert: DFN-CERT-2021-1668', 'dfn-cert: DFN-CERT-2021-1472']</t>
@@ -7801,7 +6574,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
         <v>8081</v>
       </c>
@@ -7818,7 +6590,6 @@
       <c r="K88" t="n">
         <v>5.3</v>
       </c>
-      <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
           <t>Installed version: 8.5.23
@@ -7841,18 +6612,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
-      <c r="R88" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7871,7 +6630,6 @@
           <t>Update to version 8.5.64, 9.0.44 or later.</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
           <t>['cve: CVE-2024-21733', 'url: https://lists.apache.org/thread/h9bjqdd0odj6lhs2o96qgowcc6hb0cfz', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.44', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.64', 'cert-bund: WID-SEC-2024-0769', 'cert-bund: WID-SEC-2024-0163', 'dfn-cert: DFN-CERT-2025-1517', 'dfn-cert: DFN-CERT-2025-0134', 'dfn-cert: DFN-CERT-2024-1404', 'dfn-cert: DFN-CERT-2024-0648']</t>
@@ -7882,7 +6640,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
         <v>8081</v>
       </c>
@@ -7926,18 +6683,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr"/>
-      <c r="R89" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7955,7 +6700,6 @@
           <t>Update to version 7.0.84, 8.0.48, 8.5.24, 9.0.2 or later.</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>['cve: CVE-2017-15706', 'url: http://tomcat.apache.org/security-9.html', 'url: http://tomcat.apache.org/security-8.html', 'url: http://tomcat.apache.org/security-7.html', 'url: https://lists.apache.org/thread/jocvjoxftkq59c4z8sdp12oskkvm56dy', 'cert-bund: CB-K18/0199', 'dfn-cert: DFN-CERT-2018-2165', 'dfn-cert: DFN-CERT-2018-2142', 'dfn-cert: DFN-CERT-2018-1038', 'dfn-cert: DFN-CERT-2018-0733', 'dfn-cert: DFN-CERT-2018-0217']</t>
@@ -7966,7 +6710,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
         <v>8081</v>
       </c>
@@ -8009,18 +6752,6 @@
           <t>Product: cpe:/a:apache:tomcat:8.5.23
 Method: Apache Tomcat Detection Consolidation
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
-        </is>
-      </c>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
-      <c r="R90" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>[]</t>
         </is>
       </c>
     </row>
@@ -8050,7 +6781,6 @@
 problematic cache have been removed)</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>['cve: CVE-2024-50379', 'cve: CVE-2024-54677', 'cve: CVE-2024-56337', 'url: https://lists.apache.org/thread/y6lj6q1xnp822g6ro70tn19sgtjmr80r', 'url: https://lists.apache.org/thread/tdtbbxpg5trdwc2wnopcth9ccvdftq2n', 'url: https://lists.apache.org/thread/b2b9qrgjrz1kvo4ym8y2wkfdvwoq6qbp', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.2', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.34', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.98', 'cert-bund: WID-SEC-2025-0823', 'cert-bund: WID-SEC-2025-0819', 'cert-bund: WID-SEC-2025-0818', 'cert-bund: WID-SEC-2025-0808', 'cert-bund: WID-SEC-2025-0719', 'cert-bund: WID-SEC-2025-0148', 'cert-bund: WID-SEC-2024-3744', 'cert-bund: WID-SEC-2024-3722', 'dfn-cert: DFN-CERT-2025-2285', 'dfn-cert: DFN-CERT-2025-2098', 'dfn-cert: DFN-CERT-2025-1991', 'dfn-cert: DFN-CERT-2025-1923', 'dfn-cert: DFN-CERT-2025-1181', 'dfn-cert: DFN-CERT-2025-0974', 'dfn-cert: DFN-CERT-2025-0890', 'dfn-cert: DFN-CERT-2025-0888', 'dfn-cert: DFN-CERT-2025-0766', 'dfn-cert: DFN-CERT-2025-0528', 'dfn-cert: DFN-CERT-2025-0509', 'dfn-cert: DFN-CERT-2025-0444', 'dfn-cert: DFN-CERT-2025-0146', 'dfn-cert: DFN-CERT-2025-0138', 'dfn-cert: DFN-CERT-2025-0134', 'dfn-cert: DFN-CERT-2025-0036', 'dfn-cert: DFN-CERT-2024-3364']</t>
@@ -8061,7 +6791,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
         <v>8081</v>
       </c>
@@ -8109,18 +6838,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr"/>
-      <c r="R91" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -8138,7 +6855,6 @@
           <t>Update to version 9.0.105, 10.1.41, 11.0.7 or later.</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t>['cve: CVE-2025-46701', 'url: https://lists.apache.org/thread/xhqqk9w5q45srcdqhogdk04lhdscv30j', 'cert-bund: WID-SEC-2025-1850', 'cert-bund: WID-SEC-2025-1365', 'cert-bund: WID-SEC-2025-1165', 'dfn-cert: DFN-CERT-2025-2285', 'dfn-cert: DFN-CERT-2025-2098', 'dfn-cert: DFN-CERT-2025-1991', 'dfn-cert: DFN-CERT-2025-1905', 'dfn-cert: DFN-CERT-2025-1780', 'dfn-cert: DFN-CERT-2025-1384']</t>
@@ -8149,7 +6865,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
         <v>8081</v>
       </c>
@@ -8194,18 +6909,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -8223,7 +6926,6 @@
           <t>Update to version 8.5.99, 9.0.86, 10.1.19, 11.0.0-M17 or later.</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
           <t>['cve: CVE-2024-23672', 'cve: CVE-2024-24549', 'url: https://lists.apache.org/thread/cmpswfx6tj4s7x0nxxosvfqs11lvdx2f', 'url: https://lists.apache.org/thread/4c50rmomhbbsdgfjsgwlb51xdwfjdcvg', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.0-M1', ',→7', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.19', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.86', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.99', 'url: https://nowotarski.info/http2-continuation-flood/', 'url: https://nowotarski.info/http2-continuation-flood-technical-details/', 'cert-bund: WID-SEC-2024-3663', 'cert-bund: WID-SEC-2024-3508', 'cert-bund: WID-SEC-2024-3377', 'cert-bund: WID-SEC-2024-3220', 'cert-bund: WID-SEC-2024-3219', 'cert-bund: WID-SEC-2024-3196', 'cert-bund: WID-SEC-2024-3195', 'cert-bund: WID-SEC-2024-3191', 'cert-bund: WID-SEC-2024-1656', 'cert-bund: WID-SEC-2024-1642', 'cert-bund: WID-SEC-2024-1638', 'cert-bund: WID-SEC-2024-1622', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-1214', 'cert-bund: WID-SEC-2024-1210', 'cert-bund: WID-SEC-2024-0769', 'cert-bund: WID-SEC-2024-0630 dfn-cert: DFN-CERT-2025-1517', 'dfn-cert: DFN-CERT-2024-3096', 'dfn-cert: DFN-CERT-2024-3078', 'dfn-cert: DFN-CERT-2024-2743', 'dfn-cert: DFN-CERT-2024-1846', 'dfn-cert: DFN-CERT-2024-1372', 'dfn-cert: DFN-CERT-2024-1235', 'dfn-cert: DFN-CERT-2024-1036', 'dfn-cert: DFN-CERT-2024-1011', 'dfn-cert: DFN-CERT-2024-0723', 'dfn-cert: DFN-CERT-2024-0722', 'dfn-cert: DFN-CERT-2024-0697']</t>
@@ -8234,7 +6936,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
         <v>8081</v>
       </c>
@@ -8281,18 +6982,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -8311,7 +7000,6 @@
           <t>Update to version 8.5.86, 9.0.72, 10.1.6, 11.0.0-M3 or later.</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
           <t>['cve: CVE-2023-28708', 'url: https://lists.apache.org/thread/hdksc59z3s7tm39x0pp33mtwdrt8qr67', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.0-M3', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.6', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.72', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.86', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2023-2674', 'cert-bund: WID-SEC-2023-1812', 'cert-bund: WID-SEC-2023-1808', 'cert-bund: WID-SEC-2023-1784', 'cert-bund: WID-SEC-2023-1783', 'cert-bund: WID-SEC-2023-1782', 'cert-bund: WID-SEC-2023-1424', 'cert-bund: WID-SEC-2023-1021', 'cert-bund: WID-SEC-2023-1017', 'cert-bund: WID-SEC-2023-0717', 'dfn-cert: DFN-CERT-2025-1517', 'dfn-cert: DFN-CERT-2024-3078', 'dfn-cert: DFN-CERT-2023-2778', 'dfn-cert: DFN-CERT-2023-2545', 'dfn-cert: DFN-CERT-2023-2054', 'dfn-cert: DFN-CERT-2023-0772', 'dfn-cert: DFN-CERT-2023-0763', 'dfn-cert: DFN-CERT-2023-0640']</t>
@@ -8322,7 +7010,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
         <v>8081</v>
       </c>
@@ -8366,18 +7053,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
-      <c r="R94" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -8395,7 +7070,6 @@
           <t>Update to version 7.0.91, 8.5.34, 9.0.12 or later.</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
           <t>['cve: CVE-2018-11784', 'url: http://tomcat.apache.org/security-9.html', 'url: http://tomcat.apache.org/security-8.html', 'url: http://tomcat.apache.org/security-7.html', 'cert-bund: WID-SEC-2025-1212 cert-bund: WID-SEC-2024-1682', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2023-0531', 'cert-bund: WID-SEC-2023-0460', 'cert-bund: CB-K20/0029', 'cert-bund: CB-K19/1121', 'cert-bund: CB-K19/0907', 'cert-bund: CB-K19/0616', 'cert-bund: CB-K19/0320', 'cert-bund: CB-K19/0050', 'cert-bund: CB-K18/0963', 'dfn-cert: DFN-CERT-2019-2710', 'dfn-cert: DFN-CERT-2019-2159', 'dfn-cert: DFN-CERT-2019-1562', 'dfn-cert: DFN-CERT-2019-1237', 'dfn-cert: DFN-CERT-2019-0771', 'dfn-cert: DFN-CERT-2019-0147', 'dfn-cert: DFN-CERT-2019-0104', 'dfn-cert: DFN-CERT-2018-2435', 'dfn-cert: DFN-CERT-2018-2165', 'dfn-cert: DFN-CERT-2018-2142', 'dfn-cert: DFN-CERT-2018-2000']</t>
@@ -8406,7 +7080,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
         <v>8081</v>
       </c>
@@ -8423,7 +7096,6 @@
       <c r="K95" t="n">
         <v>4.3</v>
       </c>
-      <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
           <t>Installed version: 8.5.23
@@ -8446,18 +7118,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -8475,7 +7135,6 @@
           <t>Update to version 8.5.58, 9.0.38, 10.0.0-M8 or later.</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
           <t>['cve: CVE-2020-13943', 'url: https://lists.apache.org/thread.html/r4a390027eb27e4550142fac6c8317cc684b15', ',→7ae314d31514747f307%40%3Cannounce.tomcat.apache.org%3E', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2023-2467', 'cert-bund: CB-K20/0971', 'dfn-cert: DFN-CERT-2022-0733', 'dfn-cert: DFN-CERT-2021-2620', 'dfn-cert: DFN-CERT-2021-0338', 'dfn-cert: DFN-CERT-2021-0134', 'dfn-cert: DFN-CERT-2021-0034', 'dfn-cert: DFN-CERT-2020-2224']</t>
@@ -8486,7 +7145,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
         <v>8081</v>
       </c>
@@ -8503,7 +7161,6 @@
       <c r="K96" t="n">
         <v>4.3</v>
       </c>
-      <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
           <t>Installed version: 8.5.23
@@ -8526,18 +7183,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr"/>
-      <c r="R96" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -8572,7 +7217,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
           <t>general</t>
@@ -8613,19 +7257,6 @@
 Version used: 2025-01-21T05:37:33Z</t>
         </is>
       </c>
-      <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr"/>
-      <c r="R97" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -8643,7 +7274,6 @@
           <t>Update to version 8.5.78, 9.0.62, 10.0.20, 10.1.0-M14 or later.</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
           <t>['cve: CVE-2021-43980', 'url: https://lists.apache.org/thread/3jjqbsp6j88b198x5rmg99b1qr8ht3g3', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2022-1558', 'dfn-cert: DFN-CERT-2022-2684', 'dfn-cert: DFN-CERT-2022-2605', 'dfn-cert: DFN-CERT-2022-2392']</t>
@@ -8654,7 +7284,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
         <v>8040</v>
       </c>
@@ -8699,18 +7328,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr"/>
-      <c r="R98" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -8746,7 +7363,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
         <v>8040</v>
       </c>
@@ -8786,19 +7402,6 @@
 Version used: 2023-12-15T16:10:08Z</t>
         </is>
       </c>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr"/>
-      <c r="R99" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -8816,7 +7419,6 @@
           <t>Update to version 8.5.78, 9.0.62, 10.0.20, 10.1.0-M14 or later.</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
           <t>['cve: CVE-2021-43980', 'url: https://lists.apache.org/thread/3jjqbsp6j88b198x5rmg99b1qr8ht3g3', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2022-1558', 'dfn-cert: DFN-CERT-2022-2684', 'dfn-cert: DFN-CERT-2022-2605', 'dfn-cert: DFN-CERT-2022-2392']</t>
@@ -8827,7 +7429,6 @@
           <t>LOG</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
         <v>8081</v>
       </c>
@@ -8871,18 +7472,6 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
-      <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="inlineStr"/>
-      <c r="R100" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -8896,8 +7485,6 @@
 </t>
         </is>
       </c>
-      <c r="C101" t="inlineStr"/>
-      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>['url: https://tomcat.apache.org/connectors-doc/ajp/ajpv13a.html']</t>
@@ -8908,7 +7495,6 @@
           <t>LOG</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
           <t>general</t>
@@ -8937,7 +7523,6 @@
           <t>A service supporting the Apache JServ Protocol (AJP) v1.3 seems to be running on this port.</t>
         </is>
       </c>
-      <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr">
         <is>
           <t>172.31.1.54|cpe:/a:apache:tomcat:8.5.23
@@ -8950,17 +7535,6 @@
           <t>Details: Apache JServ Protocol (AJP) v1.3 Detection (TCP)
 OID:1.3.6.1.4.1.25623.1.0.108082
 Version used: 2025-07-11T05:42:17Z</t>
-        </is>
-      </c>
-      <c r="Q101" t="inlineStr"/>
-      <c r="R101" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>[]</t>
         </is>
       </c>
     </row>
@@ -8980,8 +7554,6 @@
 the older CPE.</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr"/>
-      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
           <t>['https://nvd.nist.gov/products/cpe']</t>
@@ -8992,7 +7564,6 @@
           <t>LOG</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
           <t>general</t>
@@ -9011,7 +7582,6 @@
       <c r="K102" t="n">
         <v>0</v>
       </c>
-      <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
           <t>172.31.1.54|cpe:/a:apache:tomcat:8.5.23
@@ -9019,8 +7589,6 @@
 172.31.1.54|cpe:/o:linux:kernel</t>
         </is>
       </c>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Details: CPE Inventory
@@ -9028,17 +7596,6 @@
 Version used: 2022-07-27T10:11:28Z</t>
         </is>
       </c>
-      <c r="Q102" t="inlineStr"/>
-      <c r="R102" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -9051,15 +7608,11 @@
           <t>This plugin performs service detection.</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
           <t>LOG</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
         <v>8040</v>
       </c>
@@ -9088,8 +7641,6 @@
           <t>A web server is running on this port</t>
         </is>
       </c>
-      <c r="N103" t="inlineStr"/>
-      <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Details: Services
@@ -9097,17 +7648,6 @@
 Version used: 2025-03-05T05:38:53Z</t>
         </is>
       </c>
-      <c r="Q103" t="inlineStr"/>
-      <c r="R103" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -9120,8 +7660,6 @@
           <t>Enumerates which HTTP methods are allowed.</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
           <t>['https://nvd.nist.gov/products/cpe']</t>
@@ -9132,7 +7670,6 @@
           <t>LOG</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
         <v>8040</v>
       </c>
@@ -9162,8 +7699,6 @@
           <t>The following list contains the URLs and corresponding supported HTTP methods.</t>
         </is>
       </c>
-      <c r="N104" t="inlineStr"/>
-      <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Sends multiple HTTP requests and checks the responses.
@@ -9178,17 +7713,6 @@
 Version used: 2025-02-28T05:38:49Z</t>
         </is>
       </c>
-      <c r="Q104" t="inlineStr"/>
-      <c r="R104" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -9203,15 +7727,11 @@
 (including its value and if it is deprecated) or is missing on the target.</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr"/>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
           <t>LOG</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
         <v>8040</v>
       </c>
@@ -9245,22 +7765,9 @@
 ,→e: This is an upcoming header</t>
         </is>
       </c>
-      <c r="N105" t="inlineStr"/>
-      <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>rudimentary information about the possible enabled methods</t>
-        </is>
-      </c>
-      <c r="Q105" t="inlineStr"/>
-      <c r="R105" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>[]</t>
         </is>
       </c>
     </row>
@@ -9281,7 +7788,6 @@
           <t>Solution:</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>['url: https://owasp.org/www-project-secure-headers/', 'url: https://owasp.org/www-project-secure-headers/#div-headers', 'url: https://securityheaders.com/']</t>
@@ -9292,7 +7798,6 @@
           <t>LOG</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
         <v>8040</v>
       </c>
@@ -9343,7 +7848,6 @@
 Version used: 2025-03-21T15:40:43Z</t>
         </is>
       </c>
-      <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Details: HTTP Security Headers Detection
@@ -9351,17 +7855,6 @@
 Version used: 2025-03-21T15:40:43Z</t>
         </is>
       </c>
-      <c r="Q106" t="inlineStr"/>
-      <c r="R106" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -9375,8 +7868,6 @@
 Quality of Detection (QoD): 80%</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr"/>
-      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
           <t>['url: https://jfrog.com/artifactory/']</t>
@@ -9387,7 +7878,6 @@
           <t>LOG</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
         <v>8040</v>
       </c>
@@ -9419,24 +7909,11 @@
 Concluded from version/product identification location: http://artifactory5.trabalho_vulnnet:8040/artifactory/ui/auth/screen/footer</t>
         </is>
       </c>
-      <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Details: JFrog Artifactory Detection (HTTP)
 OID:1.3.6.1.4.1.25623.1.0.103918
 Version used: 2026-01-06T05:47:51Z</t>
-        </is>
-      </c>
-      <c r="Q107" t="inlineStr"/>
-      <c r="R107" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>[]</t>
         </is>
       </c>
     </row>
@@ -9462,8 +7939,6 @@
 If you think any of this information is wrong please report it to the referenced community forum.</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr"/>
-      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
           <t>['url: https://forum.greenbone.net/c/vulnerability-tests/7']</t>
@@ -9474,7 +7949,6 @@
           <t>LOG</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
         <v>8040</v>
       </c>
@@ -9491,7 +7965,6 @@
       <c r="K108" t="n">
         <v>0</v>
       </c>
-      <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
           <t>The Hostname/IP "artifactory5.trabalho_vulnnet" was used to access the remote ho
@@ -9516,8 +7989,6 @@
 ,→s</t>
         </is>
       </c>
-      <c r="N108" t="inlineStr"/>
-      <c r="O108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Details: Web Application Scanning Consolidation / Info Reporting
@@ -9525,17 +7996,6 @@
 Version used: 2026-01-13T05:47:36Z</t>
         </is>
       </c>
-      <c r="Q108" t="inlineStr"/>
-      <c r="R108" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -9548,15 +8008,11 @@
           <t>The script reports information on how the hostname of the target was determined.</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr"/>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
           <t>LOG</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
         <v>8040</v>
       </c>
@@ -9587,8 +8043,6 @@
 Network distance between scanner and target: 2</t>
         </is>
       </c>
-      <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>A combination of the protocols ICMP and TCP is used to determine the route. This method is
@@ -9598,17 +8052,6 @@
 Version used: 2022-10-17T11:13:19Z</t>
         </is>
       </c>
-      <c r="Q109" t="inlineStr"/>
-      <c r="R109" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -9621,15 +8064,11 @@
           <t>Collect information about the network route and network distance between the scanner host and the target host.</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr"/>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
           <t>LOG</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
         <v>8040</v>
       </c>
@@ -9659,8 +8098,6 @@
 Network distance between scanner and target: 2</t>
         </is>
       </c>
-      <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>A combination of the protocols ICMP and TCP is used to determine the route. This method is
@@ -9670,17 +8107,6 @@
 Version used: 2022-10-17T11:13:19Z</t>
         </is>
       </c>
-      <c r="Q110" t="inlineStr"/>
-      <c r="R110" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -9693,8 +8119,6 @@
           <t>Checks if the remote host has IP forwarding enabled.</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr"/>
-      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
           <t>['cve: CVE-1999-0511']</t>
@@ -9705,7 +8129,6 @@
           <t>LOG</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
         <v>8040</v>
       </c>
@@ -9722,7 +8145,6 @@
       <c r="K111" t="n">
         <v>0</v>
       </c>
-      <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
           <t>It was possible to route a TCP packet through the target host and received an answer which means IP forwarding is enabled.</t>
@@ -9733,7 +8155,6 @@
           <t>Sends a crafted Local Link Layer (LLL) frame and checks the response.</t>
         </is>
       </c>
-      <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Details: OS Detection Consolidation and Reporting
@@ -9741,17 +8162,6 @@
 Version used: 2026-01-21T05:50:46Z</t>
         </is>
       </c>
-      <c r="Q111" t="inlineStr"/>
-      <c r="R111" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -9765,8 +8175,6 @@
 Furthermore it reports all previously collected information leading to this best matching OS.</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr"/>
-      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
           <t>['https://forum.greenbone.net/c/vulnerability-tests/7']</t>
@@ -9777,7 +8185,6 @@
           <t>LOG</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
         <v>8040</v>
       </c>
@@ -9794,7 +8201,6 @@
       <c r="K112" t="n">
         <v>0</v>
       </c>
-      <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
           <t>Best matching OS: Linux Kernel
@@ -9807,7 +8213,6 @@
 Concluded from ICMP based OS fingerprint</t>
         </is>
       </c>
-      <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Log Method
@@ -9816,17 +8221,6 @@
 Version used: 2026-01-21T05:50:46Z</t>
         </is>
       </c>
-      <c r="Q112" t="inlineStr"/>
-      <c r="R112" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -9839,8 +8233,6 @@
           <t>Consolidation of Apache Tomcat detections.</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
           <t>['http://tomcat.apache.org/']</t>
@@ -9851,7 +8243,6 @@
           <t>LOG</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
         <v>8040</v>
       </c>
@@ -9868,7 +8259,6 @@
       <c r="K113" t="n">
         <v>0</v>
       </c>
-      <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
           <t>Detected Apache Tomcat
@@ -9877,7 +8267,6 @@
 CPE: cpe:/a:apache:tomcat:8.5.23</t>
         </is>
       </c>
-      <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr">
         <is>
           <t>Detected Apache Tomcat
@@ -9906,17 +8295,6 @@
 Version used: 2021-02-17T12:31:13Z</t>
         </is>
       </c>
-      <c r="Q113" t="inlineStr"/>
-      <c r="R113" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -9940,8 +8318,6 @@
 If you think any of this information is wrong please report it to the referenced community forum.)</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr"/>
-      <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
           <t>['url: https://forum.greenbone.net/c/vulnerability-tests/7']</t>
@@ -9952,7 +8328,6 @@
           <t>LOG</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
         <v>8040</v>
       </c>
@@ -9969,7 +8344,6 @@
       <c r="K114" t="n">
         <v>0</v>
       </c>
-      <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
           <t>The Hostname/IP "artifactory5.trabalho_vulnnet" was used to access the remote ho
@@ -9994,8 +8368,6 @@
 ,→s</t>
         </is>
       </c>
-      <c r="N114" t="inlineStr"/>
-      <c r="O114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Details: Web Application Scanning Consolidation / Info Reporting
@@ -10003,17 +8375,6 @@
 Version used: 2026-01-13T05:47:36Z</t>
         </is>
       </c>
-      <c r="Q114" t="inlineStr"/>
-      <c r="R114" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -10026,15 +8387,11 @@
           <t>Enumerates which HTTP methods are allowed.</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr"/>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
           <t>LOG</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
         <v>8040</v>
       </c>
@@ -10067,8 +8424,6 @@
 ,→NS (obtained via HTTP OPTIONS method)</t>
         </is>
       </c>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Details: Web Application Scanning Consolidation / Info Reporting
@@ -10076,17 +8431,6 @@
 Version used: 2026-01-13T05:47:36Z</t>
         </is>
       </c>
-      <c r="Q115" t="inlineStr"/>
-      <c r="R115" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -10099,15 +8443,11 @@
           <t>This plugin performs service detection.</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr"/>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
           <t>LOG</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
         <v>8040</v>
       </c>
@@ -10131,13 +8471,11 @@
 information available for other check routines.</t>
         </is>
       </c>
-      <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr">
         <is>
           <t>This plugin attempts to guess which service is running on the remote port(s).</t>
         </is>
       </c>
-      <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Details: Services
@@ -10145,17 +8483,6 @@
 Version used: 2025-03-05T05:38:53Z</t>
         </is>
       </c>
-      <c r="Q116" t="inlineStr"/>
-      <c r="R116" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -10169,8 +8496,6 @@
 Quality of Detection (QoD): 80%</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr"/>
-      <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
           <t>['https://jfrog.com/artifactory/']</t>
@@ -10181,7 +8506,6 @@
           <t>LOG</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
         <v>8081</v>
       </c>
@@ -10198,7 +8522,6 @@
       <c r="K117" t="n">
         <v>8</v>
       </c>
-      <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
           <t>Detected JFrog Artifactory
@@ -10209,24 +8532,11 @@
 Concluded from version/product identification location: http://artifactory5.trabalho_vulnnet:8081/artifactory/ui/auth/screen/footer</t>
         </is>
       </c>
-      <c r="N117" t="inlineStr"/>
-      <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Details: JFrog Artifactory Detection (HTTP)
 OID:1.3.6.1.4.1.25623.1.0.103918
 Version used: 2026-01-06T05:47:51Z</t>
-        </is>
-      </c>
-      <c r="Q117" t="inlineStr"/>
-      <c r="R117" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>[]</t>
         </is>
       </c>
     </row>

--- a/resources/openvas/openvas_artifactory-oss_5.11.0.xlsx
+++ b/resources/openvas/openvas_artifactory-oss_5.11.0.xlsx
@@ -582,7 +582,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>An EOL version of Apache Tomcat is not receiving any security updates from the vendor. Unxed security vulnerabilities might be leveraged by an attacker to compromise the security of this host.</t>
+          <t>An EOL version of Apache Tomcat is not receiving any security updates from the vendor. Unfixed security vulnerabilities might be leveraged by an attacker to compromise the security of this host.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>An EOL version of Apache Tomcat is not receiving any security updates from the vendor. Unxed security vulnerabilities might be leveraged by an attacker to compromise the security of this host.</t>
+          <t>An EOL version of Apache Tomcat is not receiving any security updates from the vendor. Unfixed security vulnerabilities might be leveraged by an attacker to compromise the security of this host.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -5020,10 +5020,10 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Multiple fiaws are due to:
+          <t>Multiple flaws are due to:
 - The system does not properly enforce security constraints that defined by annotations of Servlets
 in certain cases, depending on the order that Servlets are loaded.
-- The URL pattern of _x0011_ (the empty string) which exactly maps to the context root was not
+- The URL pattern of '' (the empty string) which exactly maps to the context root was not
 correctly handled when used as part of a security constraint definition.</t>
         </is>
       </c>
@@ -7515,7 +7515,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>The AJP protocol is used in various products like e.g. Apache Tomcat, JBoss or Wildy.</t>
+          <t>The AJP protocol is used in various products like e.g. Apache Tomcat, JBoss or WildFly.</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">

--- a/resources/openvas/openvas_artifactory-oss_5.11.0.xlsx
+++ b/resources/openvas/openvas_artifactory-oss_5.11.0.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -515,6 +515,7 @@
 For other products using Tomcat please contact the vendor for more information on fixed versions</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>['cve: CVE-2020-1938', 'url: https://lists.apache.org/thread/bnys5lvg1875dsslkkx2vmwxv833l35x', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.31', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.51', 'url: https://tomcat.apache.org/security-7.html#Fixed_in_Apache_Tomcat_7.0.100', 'url: https://web.archive.org/web/20250114042903/https://www.chaitin.cn/en/ghostcat', 'url: https://www.cnvd.org.cn/flaw/show/CNVD-2020-10487', 'url: https://github.com/YDHCUI/CNVD-2020-10487-Tomcat-Ajp-lfi', 'url: https://securityboulevard.com/2020/02/patch-your-tomcat-and-jboss-instances-to-protect-from-ghostcat-vulnerability-cve-2020-1938-and/', 'url: https://www.cisa.gov/known-exploited-vulnerabilities-catalog cisa: Known Exploited Vulnerability (KEV) catalog', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2023-2480', 'cert-bund: CB-K20/0711', 'cert-bund: CB-K20/0705', 'cert-bund: CB-K20/0693', 'cert-bund: CB-K20/0555', 'cert-bund: CB-K20/0543', 'cert-bund: CB-K20/0154', 'dfn-cert: DFN-CERT-2021-1736', 'dfn-cert: DFN-CERT-2020-1508', 'dfn-cert: DFN-CERT-2020-1413', 'dfn-cert: DFN-CERT-2020-1276', 'dfn-cert: DFN-CERT-2020-1134', 'dfn-cert: DFN-CERT-2020-0850', 'dfn-cert: DFN-CERT-2020-0835', 'dfn-cert: DFN-CERT-2020-0821', 'dfn-cert: DFN-CERT-2020-0569', 'dfn-cert: DFN-CERT-2020-0557', 'dfn-cert: DFN-CERT-2020-0501', 'dfn-cert: DFN-CERT-2020-0381']</t>
@@ -525,6 +526,7 @@
           <t>CRITICAL</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>8019</v>
       </c>
@@ -558,11 +560,8 @@
 Version used: 2025-07-11T05:42:17Z</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>The 'Apache Tomcat' version on the remote host has reached the end of life.</t>
-        </is>
-      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -595,6 +594,7 @@
           <t>CRITICAL</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>8040</v>
       </c>
@@ -611,6 +611,7 @@
       <c r="K3" t="n">
         <v>10</v>
       </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>The "Apache Tomcat" version on the remote host has reached the end of life.
@@ -637,6 +638,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652</t>
         </is>
       </c>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -672,6 +674,7 @@
           <t>CRITICAL</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>8040</v>
       </c>
@@ -712,6 +715,7 @@
 ,→7652)</t>
         </is>
       </c>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -729,6 +733,7 @@
           <t>Update to version 9.0.99, 10.1.35, 11.0.3 or later.</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>['cve: CVE-2025-24813', 'cisa: Known Exploited Vulnerability (KEV) catalog', 'url: https://www.cisa.gov/known-exploited-vulnerabilities-catalog', 'url: https://lists.apache.org/thread/j5fkjv2k477os90nczf2v9l61fb0kkgq', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.3', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.35', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.99', 'url: https://github.com/iSee857/CVE-2025-24813-PoC', 'url: https://lab.wallarm.com/one-put-request-to-own-tomcat-cve-2025-24813-rce-is-in-the-wild/', 'url: https://www.openwall.com/lists/oss-security/2025/03/10/5', 'url: https://scrapco.de/blog/analysis-of-cve-2025-24813-apache-tomcat-path-equivalence-rce.html', 'url: https://bishopfox.com/blog/tomcat-cve-2025-24813-what-you-need-to-know-blog', 'cert-bund: WID-SEC-2025-1564', 'cert-bund: WID-SEC-2025-1439 cert-bund: WID-SEC-2025-0825', 'cert-bund: WID-SEC-2025-0824', 'cert-bund: WID-SEC-2025-0823', 'cert-bund: WID-SEC-2025-0511', 'dfn-cert: DFN-CERT-2025-2098', 'dfn-cert: DFN-CERT-2025-0993', 'dfn-cert: DFN-CERT-2025-0890', 'dfn-cert: DFN-CERT-2025-0888', 'dfn-cert: DFN-CERT-2025-0766', 'dfn-cert: DFN-CERT-2025-0622']</t>
@@ -739,6 +744,7 @@
           <t>CRITICAL</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>8040</v>
       </c>
@@ -784,6 +790,7 @@
 ,→7652)</t>
         </is>
       </c>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -802,6 +809,7 @@
 Update to version 7.0.100, 8.5.51, 9.0.31 or later.</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>['cve: CVE-2020-1935', 'cve: CVE-2020-1938', 'cisa: Known Exploited Vulnerability (KEV) catalog', 'url: https://www.cisa.gov/known-exploited-vulnerabilities-catalog', 'url: https://lists.apache.org/thread.html/r127f76181aceffea2bd4711b03c595d0f115f', ',→63e020348fe925a916c%40%3Cannounce.tomcat.apache.org%3E', 'url: https://lists.apache.org/thread.html/r7c6f492fbd39af34a68681dbbba0468490ff1', ',→a97a1bd79c6a53610ef%40%3Cannounce.tomcat.apache.org%3E', 'url: https://www.chaitin.cn/en/ghostcat', 'url: https://www.cnvd.org.cn/flaw/show/CNVD-2020-10487', 'url: https://github.com/YDHCUI/CNVD-2020-10487-Tomcat-Ajp-lfi', 'url: https://tomcat.apache.org/tomcat-7.0-doc/changelog.html', 'url: https://tomcat.apache.org/tomcat-8.5-doc/changelog.html', 'url: https://tomcat.apache.org/tomcat-9.0-doc/changelog.html', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2023-2480', 'cert-bund: WID-SEC-2023-2130', 'cert-bund: CB-K20/0711', 'cert-bund: CB-K20/0705', 'cert-bund: CB-K20/0693', 'cert-bund: CB-K20/0555', 'cert-bund: CB-K20/0543', 'cert-bund: CB-K20/0165', 'cert-bund: CB-K20/0154', 'dfn-cert: DFN-CERT-2021-1736', 'dfn-cert: DFN-CERT-2021-0575', 'dfn-cert: DFN-CERT-2020-2482', 'dfn-cert: DFN-CERT-2020-1707', 'dfn-cert: DFN-CERT-2020-1706', 'dfn-cert: DFN-CERT-2020-1508', 'dfn-cert: DFN-CERT-2020-1413', 'dfn-cert: DFN-CERT-2020-1276', 'dfn-cert: DFN-CERT-2020-1134', 'dfn-cert: DFN-CERT-2020-0850', 'dfn-cert: DFN-CERT-2020-0835 dfn-cert: DFN-CERT-2020-0821', 'dfn-cert: DFN-CERT-2020-0569', 'dfn-cert: DFN-CERT-2020-0557', 'dfn-cert: DFN-CERT-2020-0501', 'dfn-cert: DFN-CERT-2020-0381']</t>
@@ -812,6 +820,7 @@
           <t>CRITICAL</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>8040</v>
       </c>
@@ -842,12 +851,14 @@
 Installation path / port: 8040/tcp</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
           <t>cpe:/a:apache:tomcat:8.5.23
 Detected by Apache Tomcat Detection Consolidation (OID: 1.3.6.1.4.1.25623.1.0.10-&gt;7652)</t>
         </is>
       </c>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -866,6 +877,7 @@
           <t>Update to version 9.0.104, 10.1.40, 11.0.6 or later.</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>['cve: CVE-2025-31651', 'url: https://lists.apache.org/thread/cpklvqwvdrp4k9hmd2l3q33j0gzy4fox', 'cert-bund: WID-SEC-2025-2372', 'cert-bund: WID-SEC-2025-1850', 'cert-bund: WID-SEC-2025-1572', 'cert-bund: WID-SEC-2025-1565', 'cert-bund: WID-SEC-2025-1563', 'cert-bund: WID-SEC-2025-1439', 'cert-bund: WID-SEC-2025-1365', 'cert-bund: WID-SEC-2025-0895', 'dfn-cert: DFN-CERT-2025-3462', 'dfn-cert: DFN-CERT-2025-3454', 'dfn-cert: DFN-CERT-2025-3431', 'dfn-cert: DFN-CERT-2025-3113', 'dfn-cert: DFN-CERT-2025-2285', 'dfn-cert: DFN-CERT-2025-2098', 'dfn-cert: DFN-CERT-2025-1991', 'dfn-cert: DFN-CERT-2025-1905', 'dfn-cert: DFN-CERT-2025-1898', 'dfn-cert: DFN-CERT-2025-1557', 'dfn-cert: DFN-CERT-2025-1081']</t>
@@ -876,6 +888,7 @@
           <t>CRITICAL</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>8040</v>
       </c>
@@ -916,6 +929,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652</t>
         </is>
       </c>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -949,6 +963,7 @@
           <t>CRITICAL</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>8081</v>
       </c>
@@ -965,6 +980,7 @@
       <c r="K8" t="n">
         <v>10</v>
       </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>The "Apache Tomcat" version on the remote host has reached the end of life.
@@ -990,6 +1006,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652</t>
         </is>
       </c>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1022,6 +1039,7 @@
           <t>CRITICAL</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>8081</v>
       </c>
@@ -1061,6 +1079,7 @@
 Method: Apache Tomcat Detection Consolidation OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1078,6 +1097,7 @@
           <t>Update to version 7.0.100, 8.5.51, 9.0.31 or later.</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>['cve: CVE-2020-1935', 'cve: CVE-2020-1938', 'cisa: Known Exploited Vulnerability (KEV) catalog', 'url: https://www.cisa.gov/known-exploited-vulnerabilities-catalog', 'url: https://lists.apache.org/thread.html/r127f76181aceffea2bd4711b03c595d0f115f63e020348fe925a916c%40%3Cannounce.tomcat.apache.org%3E', 'url: https://lists.apache.org/thread.html/r7c6f492fbd39af34a68681dbbba0468490ffa97a1bd79c6a53610ef%40%3Cannounce.tomcat.apache.org%3E', 'url: https://www.chaitin.cn/en/ghostcat', 'url: https://www.cnvd.org.cn/flaw/show/CNVD-2020-10487', 'url: https://github.com/YDHCUI/CNVD-2020-10487-Tomcat-Ajp-lfi', 'url: https://tomcat.apache.org/tomcat-7.0-doc/changelog.html', 'url: https://tomcat.apache.org/tomcat-8.5-doc/changelog.html', 'url: https://tomcat.apache.org/tomcat-9.0-doc/changelog.html', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2023-2480', 'cert-bund: WID-SEC-2023-2130', 'cert-bund: CB-K20/0711', 'cert-bund: CB-K20/0705']</t>
@@ -1088,6 +1108,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>8081</v>
       </c>
@@ -1133,6 +1154,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1150,6 +1172,7 @@
           <t>Update to version 9.0.104, 10.1.40, 11.0.6 or later.</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>['cve: CVE-2025-31651', 'url: https://lists.apache.org/thread/cpklvqwvdrp4k9hmd2l3q33j0gzy4fox', 'cert-bund: WID-SEC-2025-2372', 'cert-bund: WID-SEC-2025-1850', 'cert-bund: WID-SEC-2025-1572', 'cert-bund: WID-SEC-2025-1565', 'cert-bund: WID-SEC-2025-1563', 'cert-bund: WID-SEC-2025-1439', 'cert-bund: WID-SEC-2025-1365', 'cert-bund: WID-SEC-2025-0895', 'dfn-cert: DFN-CERT-2025-3462', 'dfn-cert: DFN-CERT-2025-3454', 'dfn-cert: DFN-CERT-2025-3431', 'dfn-cert: DFN-CERT-2025-3113', 'dfn-cert: DFN-CERT-2025-2285', 'dfn-cert: DFN-CERT-2025-2098', 'dfn-cert: DFN-CERT-2025-1991', 'dfn-cert: DFN-CERT-2025-1905', 'dfn-cert: DFN-CERT-2025-1898', 'dfn-cert: DFN-CERT-2025-1557', 'dfn-cert: DFN-CERT-2025-1081']</t>
@@ -1160,6 +1183,7 @@
           <t>CRITICAL</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>8081</v>
       </c>
@@ -1203,6 +1227,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1220,6 +1245,7 @@
           <t>Update to version 9.0.99, 10.1.35, 11.0.3 or later.</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>['cve: CVE-2025-24813', 'cisa: Known Exploited Vulnerability (KEV) catalog', 'url: https://www.cisa.gov/known-exploited-vulnerabilities-catalog', 'url: https://lists.apache.org/thread/j5fkjv2k477os90nczf2v9l61fb0kkgq', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.3', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.35', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.99', 'url: https://github.com/iSee857/CVE-2025-24813-PoC', 'url: https://lab.wallarm.com/one-put-request-to-own-tomcat-cve-2025-24813-rce-is-in-the-wild/', 'url: https://www.openwall.com/lists/oss-security/2025/03/10/5', 'url: https://scrapco.de/blog/analysis-of-cve-2025-24813-apache-tomcat-path-equivalence-rce.html', 'url: https://bishopfox.com/blog/tomcat-cve-2025-24813-what-you-need-to-know-blog', 'cert-bund: WID-SEC-2025-1564', 'cert-bund: WID-SEC-2025-1439', 'cert-bund: WID-SEC-2025-0825', 'cert-bund: WID-SEC-2025-0824', 'cert-bund: WID-SEC-2025-0823', 'cert-bund: WID-SEC-2025-0511', 'dfn-cert: DFN-CERT-2025-2098', 'dfn-cert: DFN-CERT-2025-0993', 'dfn-cert: DFN-CERT-2025-0890', 'dfn-cert: DFN-CERT-2025-0888', 'dfn-cert: DFN-CERT-2025-0766', 'dfn-cert: DFN-CERT-2025-0622']</t>
@@ -1230,6 +1256,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>8081</v>
       </c>
@@ -1288,6 +1315,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1305,6 +1333,7 @@
           <t>Update to version 8.5.76, 9.0.21 or later.</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>['cve: CVE-2022-25762', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.21', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.76', 'url: https://lists.apache.org/thread/tkmozotlgcrpvhx5vt6kw0pxtfx11k67', 'cert-bund: WID-SEC-2022-1335', 'cert-bund: WID-SEC-2022-1228', 'cert-bund: WID-SEC-2022-0899', 'cert-bund: WID-SEC-2022-0740', 'cert-bund: CB-K22/0600', 'dfn-cert: DFN-CERT-2024-0762', 'dfn-cert: DFN-CERT-2022-1605']</t>
@@ -1315,6 +1344,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>8040</v>
       </c>
@@ -1336,6 +1366,7 @@
           <t>The error handling triggered in this case could cause the a pooled object to be placed in the pool twice. This could result in subsequent connections using the same object concurrently which could result in data being returned to the wrong user and/or other errors.</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>Checks if a vulnerable version is present on the target host.
@@ -1351,6 +1382,7 @@
 ,→7652)</t>
         </is>
       </c>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1368,6 +1400,7 @@
           <t>Update to version 9.0.106, 10.1.42, 11.0.8 or later.</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>['cve: CVE-2022-25762', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.21', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.76', 'url: https://lists.apache.org/thread/tkmozotlgcrpvhx5vt6kw0pxtfx11k67', 'cert-bund: WID-SEC-2022-1335', 'cert-bund: WID-SEC-2022-1228', 'cert-bund: WID-SEC-2022-0899', 'cert-bund: WID-SEC-2022-0740', 'cert-bund: CB-K22/0600', 'dfn-cert: DFN-CERT-2024-0762', 'dfn-cert: DFN-CERT-2022-1605']</t>
@@ -1378,6 +1411,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>8040</v>
       </c>
@@ -1423,6 +1457,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1440,6 +1475,7 @@
           <t>Update to version 9.0.90, 10.1.25, 11.0.0-M21 or later.</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>['cve: CVE-2024-34750', 'url: https://lists.apache.org/thread/4kqf0bc9gxymjc2x7v3p7dvplnl77y8l', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.0-M2', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.25', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.90', 'cert-bund: WID-SEC-2025-0163', 'cert-bund: WID-SEC-2025-0161', 'cert-bund: WID-SEC-2025-0148', 'cert-bund: WID-SEC-2025-0144', 'cert-bund: WID-SEC-2025-0143', 'cert-bund: WID-SEC-2024-3197', 'cert-bund: WID-SEC-2024-3195', 'cert-bund: WID-SEC-2024-2100', 'cert-bund: WID-SEC-2024-1905', 'cert-bund: WID-SEC-2024-1522', 'dfn-cert: DFN-CERT-2025-2098', 'dfn-cert: DFN-CERT-2025-1991', 'dfn-cert: DFN-CERT-2025-1517', 'dfn-cert: DFN-CERT-2025-0170', 'dfn-cert: DFN-CERT-2025-0146', 'dfn-cert: DFN-CERT-2024-2192', 'dfn-cert: DFN-CERT-2024-2031 dfn-cert: DFN-CERT-2024-1723']</t>
@@ -1450,6 +1486,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>8040</v>
       </c>
@@ -1493,6 +1530,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1510,6 +1548,7 @@
           <t>Update to version 9.0.107 or later.</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>['cve: CVE-2025-52434', 'url: https://lists.apache.org/thread/gxgh65004f25y8519coth6w7vchww030', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.107', 'cert-bund: WID-SEC-2026-0177', 'cert-bund: WID-SEC-2025-1905', 'cert-bund: WID-SEC-2025-1468', 'dfn-cert: DFN-CERT-2025-2957', 'dfn-cert: DFN-CERT-2025-2390', 'dfn-cert: DFN-CERT-2025-2299', 'dfn-cert: DFN-CERT-2025-2056', 'dfn-cert: DFN-CERT-2025-1991', 'dfn-cert: DFN-CERT-2025-1789']</t>
@@ -1520,6 +1559,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>8040</v>
       </c>
@@ -1560,6 +1600,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1578,6 +1619,7 @@
           <t>Update to version 9.0.108, 10.1.44, 11.0.10 or later.</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>['cve: CVE-2025-8671', 'cve: CVE-2025-48989', 'url: https://lists.apache.org/thread/9ydfg0xr0tchmglcprhxgwhj0hfwxlyf', 'url: https://lists.apache.org/thread/p09775q0rd185m6zz98krg0fp45j8kr0', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.108', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.44', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.10', 'url: https://galbarnahum.com/posts/made-you-reset-intro', 'url: https://deepness-lab.org/publications/madeyoureset/', 'url: https://kb.cert.org/vuls/id/767506', 'url: https://thehackernews.com/2025/08/new-http2-madeyoureset-vulnerability.html', 'cert-bund: WID-SEC-2026-0177', 'cert-bund: WID-SEC-2026-0175', 'cert-bund: WID-SEC-2026-0173', 'cert-bund: WID-SEC-2026-0165', 'cert-bund: WID-SEC-2025-2853', 'cert-bund: WID-SEC-2025-2373', 'cert-bund: WID-SEC-2025-2361', 'cert-bund: WID-SEC-2025-2360 cert-bund: WID-SEC-2025-2356', 'cert-bund: WID-SEC-2025-1830', 'dfn-cert: DFN-CERT-2025-3431', 'dfn-cert: DFN-CERT-2025-2957', 'dfn-cert: DFN-CERT-2025-2390', 'dfn-cert: DFN-CERT-2025-2299', 'dfn-cert: DFN-CERT-2025-2224', 'dfn-cert: DFN-CERT-2025-2219']</t>
@@ -1588,6 +1630,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>8040</v>
       </c>
@@ -1632,6 +1675,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1649,6 +1693,7 @@
           <t>Update to version 9.0.106, 10.1.42, 11.0.8 or later.</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>['cve: CVE-2025-48976', 'cve: CVE-2025-48988', 'cve: CVE-2025-49125', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.8', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.42', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.106', 'url: https://lists.apache.org/thread/nzkqsok8t42qofgqfmck536mtyzygp18', 'url: https://lists.apache.org/thread/m66cytbfrty9k7dc4cg6tl1czhsnbywk', 'url: https://www.openwall.com/lists/oss-security/2025/06/16/1', 'url: https://www.openwall.com/lists/oss-security/2025/06/16/2', 'url: https://github.com/Samb102/POC-CVE-2025-48988-CVE-2025-48976', 'cert-bund: WID-SEC-2026-0177', 'cert-bund: WID-SEC-2026-0175', 'cert-bund: WID-SEC-2026-0165', 'cert-bund: WID-SEC-2026-0163', 'cert-bund: WID-SEC-2026-0162', 'cert-bund: WID-SEC-2026-0153', 'cert-bund: WID-SEC-2025-2853', 'cert-bund: WID-SEC-2025-2768', 'cert-bund: WID-SEC-2025-2373', 'cert-bund: WID-SEC-2025-2372', 'cert-bund: WID-SEC-2025-2371', 'cert-bund: WID-SEC-2025-2369', 'cert-bund: WID-SEC-2025-2366', 'cert-bund: WID-SEC-2025-2362', 'cert-bund: WID-SEC-2025-2361', 'cert-bund: WID-SEC-2025-2360', 'cert-bund: WID-SEC-2025-2359', 'cert-bund: WID-SEC-2025-2357', 'cert-bund: WID-SEC-2025-2356', 'cert-bund: WID-SEC-2025-2355', 'cert-bund: WID-SEC-2025-2353', 'cert-bund: WID-SEC-2025-2351 cert-bund: WID-SEC-2025-1562', 'cert-bund: WID-SEC-2025-1560', 'cert-bund: WID-SEC-2025-1559', 'cert-bund: WID-SEC-2025-1335', 'cert-bund: WID-SEC-2025-1334', 'dfn-cert: DFN-CERT-2026-0205', 'dfn-cert: DFN-CERT-2025-3541', 'dfn-cert: DFN-CERT-2025-3168', 'dfn-cert: DFN-CERT-2025-2941', 'dfn-cert: DFN-CERT-2025-2939', 'dfn-cert: DFN-CERT-2025-2390', 'dfn-cert: DFN-CERT-2025-2335', 'dfn-cert: DFN-CERT-2025-2299', 'dfn-cert: DFN-CERT-2025-2291', 'dfn-cert: DFN-CERT-2025-2098', 'dfn-cert: DFN-CERT-2025-2088', 'dfn-cert: DFN-CERT-2025-2056', 'dfn-cert: DFN-CERT-2025-1992', 'dfn-cert: DFN-CERT-2025-1991', 'dfn-cert: DFN-CERT-2025-1780', 'dfn-cert: DFN-CERT-2025-1739', 'dfn-cert: DFN-CERT-2025-1588']</t>
@@ -1659,6 +1704,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>8040</v>
       </c>
@@ -1704,6 +1750,7 @@
 Detected by Apache Tomcat Detection Consolidation (OID: 1.3.6.1.4.1.25623.1.0.10 -&gt;7652)</t>
         </is>
       </c>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1722,6 +1769,7 @@
 Update to version 9.0.107, 10.1.43, 11.0.9 or later.</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>['cve: CVE-2025-52520', 'cve: CVE-2025-53506', 'url: https://lists.apache.org/thread/trqq01bbxw6c92zx69kx2mw2qgmfy0o5', 'url: https://lists.apache.org/thread/p09775q0rd185m6zz98krg0fp45j8kr0', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.107', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.43', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.9', 'cert-bund: WID-SEC-2025-1905', 'cert-bund: WID-SEC-2025-1468', 'dfn-cert: DFN-CERT-2025-2390', 'dfn-cert: DFN-CERT-2025-2335', 'dfn-cert: DFN-CERT-2025-2299', 'dfn-cert: DFN-CERT-2025-2219', 'dfn-cert: DFN-CERT-2025-2168', 'dfn-cert: DFN-CERT-2025-2088', 'dfn-cert: DFN-CERT-2025-2056', 'dfn-cert: DFN-CERT-2025-1991', 'dfn-cert: DFN-CERT-2025-1789']</t>
@@ -1732,6 +1780,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>8040</v>
       </c>
@@ -1778,6 +1827,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1795,6 +1845,7 @@
           <t>Update to version 8.5.64, 9.0.44, 10.0.4 or later.</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>['cve: CVE-2021-41079', 'url: https://lists.apache.org/thread.html/rccdef0349fdf4fb73a4e4403095446d7fe6264e0a58e2df5c6799434%40%3Cannounce.tomcat.apache.org%3E', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-0673', 'cert-bund: WID-SEC-2022-0615', 'cert-bund: WID-SEC-2022-0607', 'cert-bund: CB-K21/0983', 'dfn-cert: DFN-CERT-2024-1989', 'dfn-cert: DFN-CERT-2024-0762', 'dfn-cert: DFN-CERT-2022-1530', 'dfn-cert: DFN-CERT-2022-0826', 'dfn-cert: DFN-CERT-2022-0733', 'dfn-cert: DFN-CERT-2021-2297', 'dfn-cert: DFN-CERT-2021-2169', 'dfn-cert: DFN-CERT-2021-1990']</t>
@@ -1805,6 +1856,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>8040</v>
       </c>
@@ -1850,6 +1902,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1867,6 +1920,7 @@
           <t>Update to version 8.5.94, 9.0.81, 10.1.14, 11.0.0-M12 or later.</t>
         </is>
       </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>['cve: CVE-2023-42795', 'cve: CVE-2023-44487', 'cve: CVE-2023-45648', 'url: https://lists.apache.org/thread/065jfyo583490r9j2v73nhpyxdob56lw', 'url: https://lists.apache.org/thread/3m81kt8c2gtg4nkjfwt2hvt5l9ycx6vl', 'url: https://lists.apache.org/thread/2pv8yz1pyp088tsxfb7ogltk9msk0jdp', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.0-M1', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.14', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.81', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.94', 'url: https://cloud.google.com/blog/products/identity-security/how-it-works-the-n', 'url: https://blog.cloudflare.com/technical-breakdown-http2-rapid-reset-ddos-atta', 'url: https://aws.amazon.com/blogs/security/how-aws-protects-customers-from-ddosurl: https://www.openwall.com/lists/oss-security/2023/10/10/6', 'url: https://www.cisa.gov/news-events/alerts/2023/10/10/http2-rapid-reset-vulner', 'url: https://www.cisa.gov/known-exploited-vulnerabilities-catalog', 'cisa: Known Exploited Vulnerability (KEV) catalog', 'cert-bund: WID-SEC-2025-0225', 'cert-bund: WID-SEC-2024-3684', 'cert-bund: WID-SEC-2024-1652 cert-bund: WID-SEC-2024-1643', 'cert-bund: WID-SEC-2024-1642', 'cert-bund: WID-SEC-2024-1307', 'cert-bund: WID-SEC-2024-1248', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-1228', 'cert-bund: WID-SEC-2024-0899', 'cert-bund: WID-SEC-2024-0894', 'cert-bund: WID-SEC-2024-0887', 'cert-bund: WID-SEC-2024-0874', 'cert-bund: WID-SEC-2024-0873', 'cert-bund: WID-SEC-2024-0870', 'cert-bund: WID-SEC-2024-0869', 'cert-bund: WID-SEC-2024-0794', 'cert-bund: WID-SEC-2024-0597', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2024-0521', 'cert-bund: WID-SEC-2024-0519', 'cert-bund: WID-SEC-2024-0123', 'cert-bund: WID-SEC-2024-0121', 'cert-bund: WID-SEC-2024-0118', 'cert-bund: WID-SEC-2024-0117', 'cert-bund: WID-SEC-2024-0116', 'cert-bund: WID-SEC-2024-0115', 'cert-bund: WID-SEC-2024-0108', 'cert-bund: WID-SEC-2024-0107', 'cert-bund: WID-SEC-2024-0106', 'cert-bund: WID-SEC-2024-0025', 'cert-bund: WID-SEC-2023-3146', 'cert-bund: WID-SEC-2023-2993', 'cert-bund: WID-SEC-2023-2963', 'cert-bund: WID-SEC-2023-2788', 'cert-bund: WID-SEC-2023-2723', 'cert-bund: WID-SEC-2023-2655', 'cert-bund: WID-SEC-2023-2628', 'cert-bund: WID-SEC-2023-2627', 'cert-bund: WID-SEC-2023-2618', 'cert-bund: WID-SEC-2023-2611', 'cert-bund: WID-SEC-2023-2606', 'dfn-cert: DFN-CERT-2025-2658', 'dfn-cert: DFN-CERT-2025-2038', 'dfn-cert: DFN-CERT-2025-1517', 'dfn-cert: DFN-CERT-2025-0267', 'dfn-cert: DFN-CERT-2024-3078', 'dfn-cert: DFN-CERT-2024-2706', 'dfn-cert: DFN-CERT-2024-2681', 'dfn-cert: DFN-CERT-2024-2487 dfn-cert: DFN-CERT-2024-2348', 'dfn-cert: DFN-CERT-2024-2290', 'dfn-cert: DFN-CERT-2024-1105', 'dfn-cert: DFN-CERT-2024-1016', 'dfn-cert: DFN-CERT-2024-1002', 'dfn-cert: DFN-CERT-2024-1000', 'dfn-cert: DFN-CERT-2024-0830', 'dfn-cert: DFN-CERT-2024-0819', 'dfn-cert: DFN-CERT-2024-0760', 'dfn-cert: DFN-CERT-2024-0526', 'dfn-cert: DFN-CERT-2024-0522', 'dfn-cert: DFN-CERT-2024-0491', 'dfn-cert: DFN-CERT-2024-0464', 'dfn-cert: DFN-CERT-2024-0411', 'dfn-cert: DFN-CERT-2024-0398', 'dfn-cert: DFN-CERT-2024-0367', 'dfn-cert: DFN-CERT-2024-0337', 'dfn-cert: DFN-CERT-2024-0149', 'dfn-cert: DFN-CERT-2024-0134', 'dfn-cert: DFN-CERT-2024-0133', 'dfn-cert: DFN-CERT-2024-0129', 'dfn-cert: DFN-CERT-2024-0081', 'dfn-cert: DFN-CERT-2024-0076', 'dfn-cert: DFN-CERT-2024-0048', 'dfn-cert: DFN-CERT-2023-3167', 'dfn-cert: DFN-CERT-2023-3124', 'dfn-cert: DFN-CERT-2023-3119', 'dfn-cert: DFN-CERT-2023-3073', 'dfn-cert: DFN-CERT-2023-3059', 'dfn-cert: DFN-CERT-2023-3035', 'dfn-cert: DFN-CERT-2023-3007', 'dfn-cert: DFN-CERT-2023-2996', 'dfn-cert: DFN-CERT-2023-2991', 'dfn-cert: DFN-CERT-2023-2971', 'dfn-cert: DFN-CERT-2023-2959', 'dfn-cert: DFN-CERT-2023-2912', 'dfn-cert: DFN-CERT-2023-2892', 'dfn-cert: DFN-CERT-2023-2882', 'dfn-cert: DFN-CERT-2023-2876', 'dfn-cert: DFN-CERT-2023-2864', 'dfn-cert: DFN-CERT-2023-2851', 'dfn-cert: DFN-CERT-2023-2849', 'dfn-cert: DFN-CERT-2023-2803', 'dfn-cert: DFN-CERT-2023-2787', 'dfn-cert: DFN-CERT-2023-2785', 'dfn-cert: DFN-CERT-2023-2730', 'dfn-cert: DFN-CERT-2023-2729 dfn-cert: DFN-CERT-2023-2708', 'dfn-cert: DFN-CERT-2023-2701', 'dfn-cert: DFN-CERT-2023-2696', 'dfn-cert: DFN-CERT-2023-2695', 'dfn-cert: DFN-CERT-2023-2680', 'dfn-cert: DFN-CERT-2023-2677', 'dfn-cert: DFN-CERT-2023-2675', 'dfn-cert: DFN-CERT-2023-2670', 'dfn-cert: DFN-CERT-2023-2666', 'dfn-cert: DFN-CERT-2023-2646', 'dfn-cert: DFN-CERT-2023-2637', 'dfn-cert: DFN-CERT-2023-2636', 'dfn-cert: DFN-CERT-2023-2635', 'dfn-cert: DFN-CERT-2023-2623', 'dfn-cert: DFN-CERT-2023-2603', 'dfn-cert: DFN-CERT-2023-2600', 'dfn-cert: DFN-CERT-2023-2599', 'dfn-cert: DFN-CERT-2023-2597', 'dfn-cert: DFN-CERT-2023-2596', 'dfn-cert: DFN-CERT-2023-2595', 'dfn-cert: DFN-CERT-2023-2590', 'dfn-cert: DFN-CERT-2023-2589', 'dfn-cert: DFN-CERT-2023-2586', 'dfn-cert: DFN-CERT-2023-2585', 'dfn-cert: DFN-CERT-2023-2572', 'dfn-cert: DFN-CERT-2023-2571', 'dfn-cert: DFN-CERT-2023-2568', 'dfn-cert: DFN-CERT-2023-2564', 'dfn-cert: DFN-CERT-2023-2556', 'dfn-cert: DFN-CERT-2023-2555', 'dfn-cert: DFN-CERT-2023-2552', 'dfn-cert: DFN-CERT-2023-2549', 'dfn-cert: DFN-CERT-2023-2547', 'dfn-cert: DFN-CERT-2023-2528', 'dfn-cert: DFN-CERT-2023-2522', 'dfn-cert: DFN-CERT-2023-2512', 'dfn-cert: DFN-CERT-2023-2504', 'dfn-cert: DFN-CERT-2023-2501', 'dfn-cert: DFN-CERT-2023-2487', 'dfn-cert: DFN-CERT-2023-2469', 'dfn-cert: DFN-CERT-2023-2468', 'dfn-cert: DFN-CERT-2023-2459', 'dfn-cert: DFN-CERT-2023-2457', 'dfn-cert: DFN-CERT-2023-2453', 'dfn-cert: DFN-CERT-2023-2450', 'dfn-cert: DFN-CERT-2023-2449', 'dfn-cert: DFN-CERT-2023-2439']</t>
@@ -1877,6 +1931,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>8040</v>
       </c>
@@ -1920,6 +1975,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1937,6 +1993,7 @@
           <t>Update to version 8.5.60, 9.0.40, 10.0.0-M10 or later.</t>
         </is>
       </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>['cve: CVE-2020-17527', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.0.0-M1', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.40', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.60', 'url: https://lists.apache.org/thread.html/rce5ac9a40173651d540babce59f6f3825f12c6d4e886ba00823b11e5%40%3Cannounce.tomcat.apache.org%3E', 'cert-bund: WID-SEC-2023-2466', 'cert-bund: WID-SEC-2023-0065', 'cert-bund: WID-SEC-2022-0624', 'cert-bund: CB-K21/0421', 'cert-bund: CB-K21/0418', 'cert-bund: CB-K20/1195', 'dfn-cert: DFN-CERT-2022-0733', 'dfn-cert: DFN-CERT-2021-2620', 'dfn-cert: DFN-CERT-2021-0821', 'dfn-cert: DFN-CERT-2021-0820', 'dfn-cert: DFN-CERT-2021-0338', 'dfn-cert: DFN-CERT-2021-0134', 'dfn-cert: DFN-CERT-2021-0034', 'dfn-cert: DFN-CERT-2020-2646']</t>
@@ -1947,6 +2004,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>8040</v>
       </c>
@@ -1992,6 +2050,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2009,6 +2068,7 @@
           <t>Update to version 8.5.63, 9.0.43, 10.0.2 or later.</t>
         </is>
       </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>['cve: CVE-2021-25122', 'url: https://lists.apache.org/thread.html/r7b95bc248603360501f18c8eb03bb6001ec0e', ',→e3296205b34b07105b7@%3Cannounce.tomcat.apache.org%3E', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.0.2', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.43', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.63', 'cert-bund: WID-SEC-2022-1375', 'cert-bund: WID-SEC-2022-1099', 'cert-bund: WID-SEC-2022-0624', 'cert-bund: WID-SEC-2022-0607', 'cert-bund: CB-K21/1094', 'cert-bund: CB-K21/1081', 'cert-bund: CB-K21/0770', 'cert-bund: CB-K21/0222', 'dfn-cert: DFN-CERT-2024-1989', 'dfn-cert: DFN-CERT-2022-1530', 'dfn-cert: DFN-CERT-2022-0733', 'dfn-cert: DFN-CERT-2021-2191', 'dfn-cert: DFN-CERT-2021-1904', 'dfn-cert: DFN-CERT-2021-1537', 'dfn-cert: DFN-CERT-2021-1536', 'dfn-cert: DFN-CERT-2021-1403', 'dfn-cert: DFN-CERT-2021-0810', 'dfn-cert: DFN-CERT-2021-0807', 'dfn-cert: DFN-CERT-2021-0544', 'dfn-cert: DFN-CERT-2021-0445']</t>
@@ -2019,6 +2079,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>8040</v>
       </c>
@@ -2035,6 +2096,7 @@
       <c r="K23" t="n">
         <v>7.5</v>
       </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Installed version: 8.5.23
@@ -2057,6 +2119,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2074,6 +2137,7 @@
           <t>Update to version 7.0.99, 8.5.50, 9.0.30 or later.</t>
         </is>
       </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>['cve: CVE-2019-17563', 'url: https://lists.apache.org/thread.html/8b4c1db8300117b28a0f3f743c0b9e3f964687a690cdf9662a884bbd%40%3Cannounce.tomcat.apache.org%3E', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2023-1229', 'cert-bund: WID-SEC-2023-1049', 'cert-bund: CB-K21/0071', 'cert-bund: CB-K20/1030', 'cert-bund: CB-K20/0318', 'cert-bund: CB-K20/0309', 'cert-bund: CB-K19/1102', 'dfn-cert: DFN-CERT-2021-0575', 'dfn-cert: DFN-CERT-2020-2132', 'dfn-cert: DFN-CERT-2020-1134', 'dfn-cert: DFN-CERT-2020-1129', 'dfn-cert: DFN-CERT-2020-0821', 'dfn-cert: DFN-CERT-2020-0780', 'dfn-cert: DFN-CERT-2020-0775', 'dfn-cert: DFN-CERT-2020-0557', 'dfn-cert: DFN-CERT-2020-0501', 'dfn-cert: DFN-CERT-2020-0345', 'dfn-cert: DFN-CERT-2020-0027', 'dfn-cert: DFN-CERT-2019-2710', 'dfn-cert: DFN-CERT-2019-2673']</t>
@@ -2084,6 +2148,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>8040</v>
       </c>
@@ -2129,6 +2194,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2146,6 +2212,7 @@
           <t>Update to version 8.5.41, 9.0.20 or later.</t>
         </is>
       </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>['cve: CVE-2019-10072', 'url: https://lists.apache.org/thread.html/df1a2c1b87c8a6c500ecdbbaf134c7f1491c8d79d98b48c6b9f0fa6a@%3Cannounce.tomcat.apache.org%3E', 'url: http://www.securityfocus.com/bid/108874', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: CB-K20/1008', 'cert-bund: CB-K20/0029', 'cert-bund: CB-K19/0915', 'cert-bund: CB-K19/0523', 'dfn-cert: DFN-CERT-2020-0501', 'dfn-cert: DFN-CERT-2020-0088', 'dfn-cert: DFN-CERT-2020-0027', 'dfn-cert: DFN-CERT-2019-2457', 'dfn-cert: DFN-CERT-2019-2149', 'dfn-cert: DFN-CERT-2019-1895', 'dfn-cert: DFN-CERT-2019-1472', 'dfn-cert: DFN-CERT-2019-1268']</t>
@@ -2156,6 +2223,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>8040</v>
       </c>
@@ -2196,6 +2264,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2213,6 +2282,7 @@
           <t>Update to version 8.5.41, 9.0.20 or later.</t>
         </is>
       </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>['cve: CVE-2019-10072', 'url: http://tomcat.apache.org/security-9.html', 'url: http://tomcat.apache.org/security-8.html', 'cert-bund: WID-SEC-2024-0528 cert-bund: CB-K20/1008', 'cert-bund: CB-K20/0029', 'cert-bund: CB-K19/0915', 'cert-bund: CB-K19/0523', 'dfn-cert: DFN-CERT-2020-0501', 'dfn-cert: DFN-CERT-2020-0088', 'dfn-cert: DFN-CERT-2020-0027', 'dfn-cert: DFN-CERT-2019-2457', 'dfn-cert: DFN-CERT-2019-2149', 'dfn-cert: DFN-CERT-2019-1895', 'dfn-cert: DFN-CERT-2019-1472', 'dfn-cert: DFN-CERT-2019-1268']</t>
@@ -2223,6 +2293,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>8040</v>
       </c>
@@ -2267,6 +2338,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2284,6 +2356,7 @@
           <t>Update to version 8.5.38, 9.0.16 or later.</t>
         </is>
       </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>['cve: CVE-2019-0199', 'url: http://tomcat.apache.org/security-9.html', 'url: http://tomcat.apache.org/security-8.html', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: CB-K20/0543', 'cert-bund: CB-K20/0029', 'cert-bund: CB-K19/0235', 'dfn-cert: DFN-CERT-2019-2710', 'dfn-cert: DFN-CERT-2019-1895', 'dfn-cert: DFN-CERT-2019-1755', 'dfn-cert: DFN-CERT-2019-1472', 'dfn-cert: DFN-CERT-2019-1231', 'dfn-cert: DFN-CERT-2019-1095', 'dfn-cert: DFN-CERT-2019-0594']</t>
@@ -2294,6 +2367,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>8040</v>
       </c>
@@ -2338,6 +2412,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2356,6 +2431,7 @@
 Update to version 8.5.56, 9.0.36, 10.0.0-M6 or later.</t>
         </is>
       </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>['cve: CVE-2020-11996', 'url: https://lists.apache.org/thread.html/r5541ef6b6b68b49f76fc4c45695940116da2b', ',→cbe0312ef204a00a2e0%40%3Cannounce.tomcat.apache.org%3E', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2022-1375', 'cert-bund: CB-K20/1017', 'cert-bund: CB-K20/0637', 'cert-bund: CB-K20/0636', 'dfn-cert: DFN-CERT-2021-1736', 'dfn-cert: DFN-CERT-2021-0043', 'dfn-cert: DFN-CERT-2020-2006', 'dfn-cert: DFN-CERT-2020-1575', 'dfn-cert: DFN-CERT-2020-1490', 'dfn-cert: DFN-CERT-2020-1358']</t>
@@ -2366,6 +2442,9 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>OPENVAS</t>
@@ -2374,6 +2453,7 @@
       <c r="K28" t="n">
         <v>7.5</v>
       </c>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>Installed version: 8.5.23
@@ -2393,6 +2473,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2410,6 +2491,7 @@
           <t>Update to version 8.5.57, 9.0.37, 10.0.0-M7 or later.</t>
         </is>
       </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>['cve: CVE-2020-13934', 'cve: CVE-2020-13935', 'url: https://lists.apache.org/thread.html/r61f411cf82488d6ec213063fc15feeeb88e31-&gt;b0ca9c29652ee4f962e%40%3Cannounce.tomcat.apache.org%3E', 'url: https://lists.apache.org/thread.html/rd48c72bd3255bda87564d4da3791517c074d9-&gt;4f8a701f93b85752651%40%3Cannounce.tomcat.apache.org%3E', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.0.0-M7', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.37', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.57', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2023-1048', 'cert-bund: WID-SEC-2022-1375', 'cert-bund: WID-SEC-2022-0519', 'cert-bund: CB-K20/1030', 'cert-bund: CB-K20/1021', 'cert-bund: CB-K20/1017', 'cert-bund: CB-K20/0717', 'dfn-cert: DFN-CERT-2022-1472', 'dfn-cert: DFN-CERT-2021-1736', 'dfn-cert: DFN-CERT-2021-0714', 'dfn-cert: DFN-CERT-2021-0132', 'dfn-cert: DFN-CERT-2020-2295', 'dfn-cert: DFN-CERT-2020-2287', 'dfn-cert: DFN-CERT-2020-2132', 'dfn-cert: DFN-CERT-2020-2006', 'dfn-cert: DFN-CERT-2020-1761', 'dfn-cert: DFN-CERT-2020-1707', 'dfn-cert: DFN-CERT-2020-1706', 'dfn-cert: DFN-CERT-2020-1575', 'dfn-cert: DFN-CERT-2020-1511']</t>
@@ -2420,6 +2502,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>8040</v>
       </c>
@@ -2443,6 +2526,7 @@
 - WebSocket Denial of Service (CVE-2020-13935) </t>
         </is>
       </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>Checks if a vulnerable version is present on the target host.
@@ -2458,6 +2542,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2470,6 +2555,8 @@
           <t>Apache Tomcat is prone to a request smuggling vulnerability.</t>
         </is>
       </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>['url: https://lists.apache.org/thread.html/r61f411cf82488d6ec213063fc15feeeb88e31-&gt;b0ca9c29652ee4f962e%40%3Cannounce.tomcat.apache.org%3E', 'url: https://lists.apache.org/thread.html/rd48c72bd3255bda87564d4da3791517c074d9-&gt;4f8a701f93b85752651%40%3Cannounce.tomcat.apache.org%3E', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.0.0-M7', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.37', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.57', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2023-1048', 'cert-bund: WID-SEC-2022-1375', 'cert-bund: WID-SEC-2022-0519', 'cert-bund: CB-K20/1030', 'cert-bund: CB-K20/1021', 'cert-bund: CB-K20/1017', 'cert-bund: CB-K20/0717', 'dfn-cert: DFN-CERT-2022-1472', 'dfn-cert: DFN-CERT-2021-1736', 'dfn-cert: DFN-CERT-2021-0714', 'dfn-cert: DFN-CERT-2021-0132', 'dfn-cert: DFN-CERT-2020-2295', 'dfn-cert: DFN-CERT-2020-2287', 'dfn-cert: DFN-CERT-2020-2132', 'dfn-cert: DFN-CERT-2020-2006', 'dfn-cert: DFN-CERT-2020-1761', 'dfn-cert: DFN-CERT-2020-1707', 'dfn-cert: DFN-CERT-2020-1706', 'dfn-cert: DFN-CERT-2020-1575', 'dfn-cert: DFN-CERT-2020-1511']</t>
@@ -2480,6 +2567,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>8040</v>
       </c>
@@ -2496,18 +2584,21 @@
       <c r="K30" t="n">
         <v>7.5</v>
       </c>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>Installed version: 8.5.23
 Fixed version: 8.5.83</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
           <t>Product: cpe:/a:apache:tomcat:8.5.23
 Method: Apache Tomcat Detection Consolidation</t>
         </is>
       </c>
+      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2540,6 +2631,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>8040</v>
       </c>
@@ -2561,6 +2653,7 @@
           <t>The flaw exists due to a missing host name verification when using TLS with the WebSocket client.</t>
         </is>
       </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>Checks if a vulnerable version is present on the target host.
@@ -2575,6 +2668,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652</t>
         </is>
       </c>
+      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2592,6 +2686,7 @@
           <t>Update to version 8.5.96, 9.0.83, 10.1.16, 11.0.0-M11 or later.</t>
         </is>
       </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>['cve: CVE-2023-46589', 'url: https://lists.apache.org/thread/0rqq6ktozqc42ro8hhxdmmdjm1k1tpxr', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.0-M1', ',→1', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.16', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.83', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.96', 'cert-bund: WID-SEC-2025-0810', 'cert-bund: WID-SEC-2024-1653 cert-bund: WID-SEC-2024-1652', 'cert-bund: WID-SEC-2024-1642', 'cert-bund: WID-SEC-2024-1248', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-0899', 'cert-bund: WID-SEC-2024-0890', 'cert-bund: WID-SEC-2024-0873', 'cert-bund: WID-SEC-2024-0869', 'cert-bund: WID-SEC-2024-0769', 'cert-bund: WID-SEC-2024-0119', 'cert-bund: WID-SEC-2024-0108', 'cert-bund: WID-SEC-2024-0106', 'cert-bund: WID-SEC-2024-0101', 'cert-bund: WID-SEC-2024-0094', 'cert-bund: WID-SEC-2023-3020', 'dfn-cert: DFN-CERT-2024-1404', 'dfn-cert: DFN-CERT-2024-1036', 'dfn-cert: DFN-CERT-2024-1000', 'dfn-cert: DFN-CERT-2024-0723', 'dfn-cert: DFN-CERT-2024-0722', 'dfn-cert: DFN-CERT-2024-0506', 'dfn-cert: DFN-CERT-2024-0411', 'dfn-cert: DFN-CERT-2024-0174', 'dfn-cert: DFN-CERT-2024-0127', 'dfn-cert: DFN-CERT-2023-2977']</t>
@@ -2602,6 +2697,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>8040</v>
       </c>
@@ -2645,6 +2741,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652</t>
         </is>
       </c>
+      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2677,6 +2774,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>8040</v>
       </c>
@@ -2720,6 +2818,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652</t>
         </is>
       </c>
+      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2738,6 +2837,7 @@
 Update Apache Tomcat to version 10.1.0-M15, 10.0.21, 9.0.63, 8.5.79 or later to receive the corrected / updated documentation</t>
         </is>
       </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>['cve: CVE-2022-29885', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.0-M1', ',→5', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.0.21', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.63', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.79', 'url: https://lists.apache.org/thread/548bnqoxvp0rqqq2yyj90l0xvwhq087d', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2022-1780', 'cert-bund: WID-SEC-2022-1767', 'cert-bund: WID-SEC-2022-0799', 'cert-bund: WID-SEC-2022-0467', 'cert-bund: CB-K22/0597', 'dfn-cert: DFN-CERT-2024-1989', 'dfn-cert: DFN-CERT-2024-0762', 'dfn-cert: DFN-CERT-2022-2392', 'dfn-cert: DFN-CERT-2022-2323', 'dfn-cert: DFN-CERT-2022-1070']</t>
@@ -2748,6 +2848,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>8040</v>
       </c>
@@ -2769,6 +2870,7 @@
           <t>The documentation for the EncryptInterceptor incorrectly stated it enabled Tomcat clustering to run over an untrusted network. This was not correct. While the EncryptInterceptor does provide confidentiality and integrity protection, it does not protect against all risks associated with running over any untrusted network, particularly DoS risks.</t>
         </is>
       </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>Checks if a vulnerable version is present on the target host. Details: Apache Tomcat Clustering DoS Vulnerability (May 2022)
@@ -2783,6 +2885,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2795,6 +2898,8 @@
           <t>Apache Tomcat is prone to a denial of service (DoS) vulnerability.</t>
         </is>
       </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>['cve: CVE-2023-24998', 'url: https://lists.apache.org/thread/g16kv0xpp272htz107molwbbgdrqrdk1', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.0-M3', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.5', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.71', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.85', 'url: https://lists.apache.org/thread/4xl4l09mhwg4vgsk7dxqogcjrobrrdoy', 'cert-bund: WID-SEC-2025-0810', 'cert-bund: WID-SEC-2024-1652', 'cert-bund: WID-SEC-2024-1642', 'cert-bund: WID-SEC-2024-1637', 'cert-bund: WID-SEC-2024-1622', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-0890']</t>
@@ -2805,6 +2910,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>8040</v>
       </c>
@@ -2821,6 +2927,7 @@
       <c r="K35" t="n">
         <v>7.5</v>
       </c>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
           <t>Installed version: 8.5.23 Fixed version: 8.5.85
@@ -2843,6 +2950,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2877,6 +2985,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>8040</v>
       </c>
@@ -2920,6 +3029,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2937,6 +3047,7 @@
           <t>Update to version 7.0.108, 8.5.63, 9.0.43, 10.0.2 or later.</t>
         </is>
       </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>['cve: CVE-2019-12418', 'url: https://lists.apache.org/thread.html/43530b91506e2e0c11cfbe691173f5df8c48f5-&gt;1b98262426d7493b67%40%3Cannounce.tomcat.apache.org%3E', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2023-1229', 'cert-bund: CB-K20/0309', 'cert-bund: CB-K19/1102', 'dfn-cert: DFN-CERT-2020-1129', 'dfn-cert: DFN-CERT-2020-1094', 'dfn-cert: DFN-CERT-2020-0821', 'dfn-cert: DFN-CERT-2020-0604', 'dfn-cert: DFN-CERT-2020-0557', 'dfn-cert: DFN-CERT-2020-0501', 'dfn-cert: DFN-CERT-2020-0345', 'dfn-cert: DFN-CERT-2020-0027', 'dfn-cert: DFN-CERT-2019-2710', 'dfn-cert: DFN-CERT-2019-2673']</t>
@@ -2947,6 +3058,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>8040</v>
       </c>
@@ -2986,6 +3098,7 @@
 Method: Apache Tomcat Detection Consolidation</t>
         </is>
       </c>
+      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3003,6 +3116,7 @@
           <t>Update to version 7.0.104, 8.5.55, 9.0.35, 10.0.0-M5 or later.</t>
         </is>
       </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>['cve: CVE-2020-9484', 'url: https://lists.apache.org/thread.html/r77eae567ed829da9012cadb29af17f2df8fa2', ',→3bf66faf88229857bb1%40%3Cannounce.tomcat.apache.org%3E', 'cert-bund: WID-SEC-2022-1870', 'cert-bund: WID-SEC-2022-0607', 'cert-bund: WID-SEC-2022-0432', 'cert-bund: WID-SEC-2022-0302', 'cert-bund: CB-K21/1094', 'cert-bund: CB-K21/0069', 'cert-bund: CB-K20/1017', 'cert-bund: CB-K20/0494', 'dfn-cert: DFN-CERT-2024-1989', 'dfn-cert: DFN-CERT-2024-1926', 'dfn-cert: DFN-CERT-2022-1530', 'dfn-cert: DFN-CERT-2022-0733', 'dfn-cert: DFN-CERT-2021-1736', 'dfn-cert: DFN-CERT-2020-2286', 'dfn-cert: DFN-CERT-2020-1706', 'dfn-cert: DFN-CERT-2020-1635', 'dfn-cert: DFN-CERT-2020-1575', 'dfn-cert: DFN-CERT-2020-1490', 'dfn-cert: DFN-CERT-2020-1289', 'dfn-cert: DFN-CERT-2020-1134', 'dfn-cert: DFN-CERT-2020-1129', 'dfn-cert: DFN-CERT-2020-1094 dfn-cert: DFN-CERT-2020-1086']</t>
@@ -3013,6 +3127,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
         <v>8040</v>
       </c>
@@ -3056,6 +3171,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3088,6 +3204,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>8081</v>
       </c>
@@ -3104,11 +3221,7 @@
       <c r="K39" t="n">
         <v>8.6</v>
       </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>If a web application sends a WebSocket message concurrently with the WebSocket connection closing, it is possible that the application will continue to use the socket after it has been closed.</t>
-        </is>
-      </c>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
           <t>Checks if a vulnerable version is present on the target host.</t>
@@ -3125,6 +3238,7 @@
 Method: Apache Tomcat Detection Consolidation</t>
         </is>
       </c>
+      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3142,6 +3256,7 @@
           <t>Update to version 8.5.76, 9.0.21 or later.</t>
         </is>
       </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>['cve: CVE-2022-25762', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.21', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.76', 'url: https://lists.apache.org/thread/tkmozotlgcrpvhx5vt6kw0pxtfx11k67', 'cert-bund: WID-SEC-2022-1335', 'cert-bund: WID-SEC-2022-1228', 'cert-bund: WID-SEC-2022-0899', 'cert-bund: WID-SEC-2022-0740', 'cert-bund: CB-K22/0600', 'dfn-cert: DFN-CERT-2024-0762', 'dfn-cert: DFN-CERT-2022-1605']</t>
@@ -3152,6 +3267,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>8081</v>
       </c>
@@ -3199,6 +3315,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3216,6 +3333,7 @@
           <t>Update to version 9.0.108, 10.1.44, 11.0.10 or later.</t>
         </is>
       </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>['cve: CVE-2025-8671', 'cve: CVE-2025-48989', 'url: https://lists.apache.org/thread/9ydfg0xr0tchmglcprhxgwhj0hfwxlyf', 'url: https://lists.apache.org/thread/p09775q0rd185m6zz98krg0fp45j8kr0', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.108', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.44', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.10', 'url: https://galbarnahum.com/posts/made-you-reset-intro', 'url: https://deepness-lab.org/publications/madeyoureset/', 'url: https://kb.cert.org/vuls/id/767506', 'url: https://thehackernews.com/2025/08/new-http2-madeyoureset-vulnerability.html', 'cert-bund: WID-SEC-2026-0177', 'cert-bund: WID-SEC-2026-0175', 'cert-bund: WID-SEC-2026-0173', 'cert-bund: WID-SEC-2026-0165', 'cert-bund: WID-SEC-2025-2853', 'cert-bund: WID-SEC-2025-2373 cert-bund: WID-SEC-2025-2361', 'cert-bund: WID-SEC-2025-2360', 'cert-bund: WID-SEC-2025-2357', 'cert-bund: WID-SEC-2025-2356', 'cert-bund: WID-SEC-2025-1830', 'dfn-cert: DFN-CERT-2025-3431', 'dfn-cert: DFN-CERT-2025-2957', 'dfn-cert: DFN-CERT-2025-2390', 'dfn-cert: DFN-CERT-2025-2299', 'dfn-cert: DFN-CERT-2025-2224', 'dfn-cert: DFN-CERT-2025-2219']</t>
@@ -3226,6 +3344,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>8081</v>
       </c>
@@ -3276,6 +3395,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3308,6 +3428,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
         <v>8081</v>
       </c>
@@ -3351,6 +3472,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3369,6 +3491,7 @@
           <t>Update to version 9.0.107 or later.</t>
         </is>
       </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>['cve: CVE-2025-52434 url: https://lists.apache.org/thread/gxgh65004f25y8519coth6w7vchww030', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.107', 'cert-bund: WID-SEC-2026-0177', 'cert-bund: WID-SEC-2025-1905', 'cert-bund: WID-SEC-2025-1468', 'dfn-cert: DFN-CERT-2025-2957', 'dfn-cert: DFN-CERT-2025-2390', 'dfn-cert: DFN-CERT-2025-2299', 'dfn-cert: DFN-CERT-2025-2056', 'dfn-cert: DFN-CERT-2025-1991', 'dfn-cert: DFN-CERT-2025-1789']</t>
@@ -3379,6 +3502,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>8081</v>
       </c>
@@ -3423,6 +3547,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652</t>
         </is>
       </c>
+      <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3440,6 +3565,7 @@
           <t>Update to version 9.0.106, 10.1.42, 11.0.8 or later.</t>
         </is>
       </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>['cve: CVE-2025-55668', 'url: https://lists.apache.org/thread/v6bknr96rl7l1qxkl1c03v0qdvbbqs47', 'cert-bund: WID-SEC-2025-1905', 'cert-bund: WID-SEC-2025-1826', 'dfn-cert: DFN-CERT-2025-1588']</t>
@@ -3450,6 +3576,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>8081</v>
       </c>
@@ -3493,6 +3620,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652</t>
         </is>
       </c>
+      <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3510,6 +3638,7 @@
           <t>Update to version 9.0.106, 10.1.42, 11.0.8 or later.</t>
         </is>
       </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>['cve: CVE-2025-48976', 'cve: CVE-2025-48988', 'cve: CVE-2025-49125', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.8', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.42', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.106', 'url: https://lists.apache.org/thread/nzkqsok8t42qofgqfmck536mtyzygp18', 'url: https://lists.apache.org/thread/m66cytbfrty9k7dc4cg6tl1czhsnbywk', 'url: https://www.openwall.com/lists/oss-security/2025/06/16/1', 'url: https://www.openwall.com/lists/oss-security/2025/06/16/2', 'url: https://github.com/Samb102/POC-CVE-2025-48988-CVE-2025-48976', 'cert-bund: WID-SEC-2026-0177', 'cert-bund: WID-SEC-2026-0175', 'cert-bund: WID-SEC-2026-0165', 'cert-bund: WID-SEC-2026-0163', 'cert-bund: WID-SEC-2026-0162', 'cert-bund: WID-SEC-2026-0153', 'cert-bund: WID-SEC-2025-2853', 'cert-bund: WID-SEC-2025-2768', 'cert-bund: WID-SEC-2025-2373', 'cert-bund: WID-SEC-2025-2372', 'cert-bund: WID-SEC-2025-2371', 'cert-bund: WID-SEC-2025-2369 cert-bund: WID-SEC-2025-2366', 'cert-bund: WID-SEC-2025-2362', 'cert-bund: WID-SEC-2025-2361', 'cert-bund: WID-SEC-2025-2360', 'cert-bund: WID-SEC-2025-2359', 'cert-bund: WID-SEC-2025-2357', 'cert-bund: WID-SEC-2025-2356', 'cert-bund: WID-SEC-2025-2355', 'cert-bund: WID-SEC-2025-2353', 'cert-bund: WID-SEC-2025-2351', 'cert-bund: WID-SEC-2025-1562', 'cert-bund: WID-SEC-2025-1560', 'cert-bund: WID-SEC-2025-1559', 'cert-bund: WID-SEC-2025-1335', 'cert-bund: WID-SEC-2025-1334', 'dfn-cert: DFN-CERT-2026-0205', 'dfn-cert: DFN-CERT-2025-3541', 'dfn-cert: DFN-CERT-2025-3168', 'dfn-cert: DFN-CERT-2025-2941', 'dfn-cert: DFN-CERT-2025-2939', 'dfn-cert: DFN-CERT-2025-2390', 'dfn-cert: DFN-CERT-2025-2335', 'dfn-cert: DFN-CERT-2025-2299', 'dfn-cert: DFN-CERT-2025-2291', 'dfn-cert: DFN-CERT-2025-2098', 'dfn-cert: DFN-CERT-2025-2088', 'dfn-cert: DFN-CERT-2025-2056', 'dfn-cert: DFN-CERT-2025-1992', 'dfn-cert: DFN-CERT-2025-1991', 'dfn-cert: DFN-CERT-2025-1780', 'dfn-cert: DFN-CERT-2025-1739', 'dfn-cert: DFN-CERT-2025-1588']</t>
@@ -3520,6 +3649,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
         <v>8081</v>
       </c>
@@ -3566,6 +3696,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652</t>
         </is>
       </c>
+      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3583,6 +3714,7 @@
           <t>Update to version 9.0.107, 10.1.43, 11.0.9 or later.</t>
         </is>
       </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>['cve: CVE-2025-52520', 'cve: CVE-2025-53506', 'url: https://lists.apache.org/thread/trqq01bbxw6c92zx69kx2mw2qgmfy0o5', 'url: https://lists.apache.org/thread/p09775q0rd185m6zz98krg0fp45j8kr0', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.107', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.43', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.9', 'cert-bund: WID-SEC-2025-1905', 'cert-bund: WID-SEC-2025-1468', 'dfn-cert: DFN-CERT-2025-2390 dfn-cert: DFN-CERT-2025-2335', 'dfn-cert: DFN-CERT-2025-2299', 'dfn-cert: DFN-CERT-2025-2219', 'dfn-cert: DFN-CERT-2025-2168', 'dfn-cert: DFN-CERT-2025-2088', 'dfn-cert: DFN-CERT-2025-2056', 'dfn-cert: DFN-CERT-2025-1991', 'dfn-cert: DFN-CERT-2025-1789']</t>
@@ -3593,6 +3725,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
         <v>8081</v>
       </c>
@@ -3638,6 +3771,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3655,6 +3789,7 @@
           <t>Update to version 8.5.64, 9.0.44, 10.0.4 or later.</t>
         </is>
       </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>['cve: CVE-2021-41079', 'url: https://lists.apache.org/thread.html/rccdef0349fdf4fb73a4e4403095446d7fe626', ',→4e0a58e2df5c6799434%40%3Cannounce.tomcat.apache.org%3E', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-0673', 'cert-bund: WID-SEC-2022-0615', 'cert-bund: WID-SEC-2022-0607', 'cert-bund: CB-K21/0983', 'dfn-cert: DFN-CERT-2024-1989', 'dfn-cert: DFN-CERT-2024-0762', 'dfn-cert: DFN-CERT-2022-1530', 'dfn-cert: DFN-CERT-2022-0826', 'dfn-cert: DFN-CERT-2022-0733', 'dfn-cert: DFN-CERT-2021-2297', 'dfn-cert: DFN-CERT-2021-2169', 'dfn-cert: DFN-CERT-2021-1990']</t>
@@ -3665,6 +3800,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
         <v>8081</v>
       </c>
@@ -3708,6 +3844,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652</t>
         </is>
       </c>
+      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3725,6 +3862,7 @@
           <t>Update to version 8.5.60, 9.0.40, 10.0.0-M10 or later.</t>
         </is>
       </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>['cve: CVE-2020-17527', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.0.0-M1', ',→0', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.40', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.60', 'url: https://lists.apache.org/thread.html/rce5ac9a40173651d540babce59f6f3825f12c', ',→6d4e886ba00823b11e5%40%3Cannounce.tomcat.apache.org%3E', 'cert-bund: WID-SEC-2023-2466', 'cert-bund: WID-SEC-2023-0065', 'cert-bund: WID-SEC-2022-0624', 'cert-bund: CB-K21/0421', 'cert-bund: CB-K21/0418', 'cert-bund: CB-K20/1195', 'dfn-cert: DFN-CERT-2022-0733', 'dfn-cert: DFN-CERT-2021-2620', 'dfn-cert: DFN-CERT-2021-0821', 'dfn-cert: DFN-CERT-2021-0820', 'dfn-cert: DFN-CERT-2021-0338', 'dfn-cert: DFN-CERT-2021-0134', 'dfn-cert: DFN-CERT-2021-0034', 'dfn-cert: DFN-CERT-2020-2646']</t>
@@ -3735,6 +3873,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
         <v>8081</v>
       </c>
@@ -3780,6 +3919,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652</t>
         </is>
       </c>
+      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3797,6 +3937,7 @@
           <t>Update to version 8.5.94, 9.0.81, 10.1.14, 11.0.0-M12 or later.</t>
         </is>
       </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>['cve: CVE-2023-42795', 'cve: CVE-2023-44487', 'cve: CVE-2023-45648', 'url: https://lists.apache.org/thread/065jfyo583490r9j2v73nhpyxdob56lw', 'url: https://lists.apache.org/thread/3m81kt8c2gtg4nkjfwt2hvt5l9ycx6vl', 'url: https://lists.apache.org/thread/2pv8yz1pyp088tsxfb7ogltk9msk0jdp', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.0-M1', ',→2', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.14', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.81', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.94', 'url: https://cloud.google.com/blog/products/identity-security/how-it-works-the-n', ',→ovel-http2-rapid-reset-ddos-attack', 'url: https://blog.cloudflare.com/technical-breakdown-http2-rapid-reset-ddos-atta', ',→ck/', 'url: https://aws.amazon.com/blogs/security/how-aws-protects-customers-from-ddos-', ',→events/', 'url: https://www.openwall.com/lists/oss-security/2023/10/10/6', 'url: https://www.cisa.gov/news-events/alerts/2023/10/10/http2-rapid-reset-vulner', ',→ability-cve-2023-44487', 'url: https://www.cisa.gov/known-exploited-vulnerabilities-catalog', 'cisa: Known Exploited Vulnerability (KEV) catalog', 'cert-bund: WID-SEC-2025-0225', 'cert-bund: WID-SEC-2024-3684', 'cert-bund: WID-SEC-2024-1652', 'cert-bund: WID-SEC-2024-1643', 'cert-bund: WID-SEC-2024-1642', 'cert-bund: WID-SEC-2024-1307', 'cert-bund: WID-SEC-2024-1248', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-1228', 'cert-bund: WID-SEC-2024-0899', 'cert-bund: WID-SEC-2024-0894', 'cert-bund: WID-SEC-2024-0887', 'cert-bund: WID-SEC-2024-0874', 'cert-bund: WID-SEC-2024-0873', 'cert-bund: WID-SEC-2024-0870', 'cert-bund: WID-SEC-2024-0869', 'cert-bund: WID-SEC-2024-0794', 'cert-bund: WID-SEC-2024-0597', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2024-0521 cert-bund: WID-SEC-2024-0519', 'cert-bund: WID-SEC-2024-0123', 'cert-bund: WID-SEC-2024-0121', 'cert-bund: WID-SEC-2024-0118', 'cert-bund: WID-SEC-2024-0117', 'cert-bund: WID-SEC-2024-0116', 'cert-bund: WID-SEC-2024-0115', 'cert-bund: WID-SEC-2024-0108', 'cert-bund: WID-SEC-2024-0107', 'cert-bund: WID-SEC-2024-0106', 'cert-bund: WID-SEC-2024-0025', 'cert-bund: WID-SEC-2023-3146', 'cert-bund: WID-SEC-2023-2993', 'cert-bund: WID-SEC-2023-2963', 'cert-bund: WID-SEC-2023-2788', 'cert-bund: WID-SEC-2023-2723', 'cert-bund: WID-SEC-2023-2655', 'cert-bund: WID-SEC-2023-2628', 'cert-bund: WID-SEC-2023-2627', 'cert-bund: WID-SEC-2023-2618', 'cert-bund: WID-SEC-2023-2611', 'cert-bund: WID-SEC-2023-2606', 'dfn-cert: DFN-CERT-2025-2658', 'dfn-cert: DFN-CERT-2025-2038', 'dfn-cert: DFN-CERT-2025-1517', 'dfn-cert: DFN-CERT-2025-0267', 'dfn-cert: DFN-CERT-2024-3078', 'dfn-cert: DFN-CERT-2024-2706', 'dfn-cert: DFN-CERT-2024-2681', 'dfn-cert: DFN-CERT-2024-2487', 'dfn-cert: DFN-CERT-2024-2348', 'dfn-cert: DFN-CERT-2024-2290', 'dfn-cert: DFN-CERT-2024-1105', 'dfn-cert: DFN-CERT-2024-1016', 'dfn-cert: DFN-CERT-2024-1002', 'dfn-cert: DFN-CERT-2024-1000', 'dfn-cert: DFN-CERT-2024-0830', 'dfn-cert: DFN-CERT-2024-0819', 'dfn-cert: DFN-CERT-2024-0760', 'dfn-cert: DFN-CERT-2024-0526', 'dfn-cert: DFN-CERT-2024-0522', 'dfn-cert: DFN-CERT-2024-0491', 'dfn-cert: DFN-CERT-2024-0464', 'dfn-cert: DFN-CERT-2024-0411', 'dfn-cert: DFN-CERT-2024-0398', 'dfn-cert: DFN-CERT-2024-0367', 'dfn-cert: DFN-CERT-2024-0337 dfn-cert: DFN-CERT-2024-0149', 'dfn-cert: DFN-CERT-2024-0134', 'dfn-cert: DFN-CERT-2024-0133', 'dfn-cert: DFN-CERT-2024-0129', 'dfn-cert: DFN-CERT-2024-0081', 'dfn-cert: DFN-CERT-2024-0076', 'dfn-cert: DFN-CERT-2024-0048', 'dfn-cert: DFN-CERT-2023-3167', 'dfn-cert: DFN-CERT-2023-3124', 'dfn-cert: DFN-CERT-2023-3119', 'dfn-cert: DFN-CERT-2023-3073', 'dfn-cert: DFN-CERT-2023-3059', 'dfn-cert: DFN-CERT-2023-3035', 'dfn-cert: DFN-CERT-2023-3007', 'dfn-cert: DFN-CERT-2023-2996', 'dfn-cert: DFN-CERT-2023-2991', 'dfn-cert: DFN-CERT-2023-2971', 'dfn-cert: DFN-CERT-2023-2959', 'dfn-cert: DFN-CERT-2023-2912', 'dfn-cert: DFN-CERT-2023-2892', 'dfn-cert: DFN-CERT-2023-2882', 'dfn-cert: DFN-CERT-2023-2876', 'dfn-cert: DFN-CERT-2023-2864', 'dfn-cert: DFN-CERT-2023-2851', 'dfn-cert: DFN-CERT-2023-2849', 'dfn-cert: DFN-CERT-2023-2803', 'dfn-cert: DFN-CERT-2023-2787', 'dfn-cert: DFN-CERT-2023-2785', 'dfn-cert: DFN-CERT-2023-2730', 'dfn-cert: DFN-CERT-2023-2729', 'dfn-cert: DFN-CERT-2023-2708', 'dfn-cert: DFN-CERT-2023-2701', 'dfn-cert: DFN-CERT-2023-2696', 'dfn-cert: DFN-CERT-2023-2695', 'dfn-cert: DFN-CERT-2023-2680', 'dfn-cert: DFN-CERT-2023-2677', 'dfn-cert: DFN-CERT-2023-2675', 'dfn-cert: DFN-CERT-2023-2670', 'dfn-cert: DFN-CERT-2023-2666', 'dfn-cert: DFN-CERT-2023-2646', 'dfn-cert: DFN-CERT-2023-2637', 'dfn-cert: DFN-CERT-2023-2636', 'dfn-cert: DFN-CERT-2023-2635', 'dfn-cert: DFN-CERT-2023-2623', 'dfn-cert: DFN-CERT-2023-2603', 'dfn-cert: DFN-CERT-2023-2600', 'dfn-cert: DFN-CERT-2023-2599 dfn-cert: DFN-CERT-2023-2597', 'dfn-cert: DFN-CERT-2023-2596', 'dfn-cert: DFN-CERT-2023-2595', 'dfn-cert: DFN-CERT-2023-2590', 'dfn-cert: DFN-CERT-2023-2589', 'dfn-cert: DFN-CERT-2023-2586', 'dfn-cert: DFN-CERT-2023-2585', 'dfn-cert: DFN-CERT-2023-2572', 'dfn-cert: DFN-CERT-2023-2571', 'dfn-cert: DFN-CERT-2023-2568', 'dfn-cert: DFN-CERT-2023-2564', 'dfn-cert: DFN-CERT-2023-2556', 'dfn-cert: DFN-CERT-2023-2555', 'dfn-cert: DFN-CERT-2023-2552', 'dfn-cert: DFN-CERT-2023-2549', 'dfn-cert: DFN-CERT-2023-2547', 'dfn-cert: DFN-CERT-2023-2528', 'dfn-cert: DFN-CERT-2023-2522', 'dfn-cert: DFN-CERT-2023-2512', 'dfn-cert: DFN-CERT-2023-2504', 'dfn-cert: DFN-CERT-2023-2501', 'dfn-cert: DFN-CERT-2023-2487', 'dfn-cert: DFN-CERT-2023-2469', 'dfn-cert: DFN-CERT-2023-2468', 'dfn-cert: DFN-CERT-2023-2459', 'dfn-cert: DFN-CERT-2023-2457', 'dfn-cert: DFN-CERT-2023-2453', 'dfn-cert: DFN-CERT-2023-2450', 'dfn-cert: DFN-CERT-2023-2449', 'dfn-cert: DFN-CERT-2023-2439']</t>
@@ -3807,6 +3948,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
         <v>8081</v>
       </c>
@@ -3853,6 +3995,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652</t>
         </is>
       </c>
+      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3870,6 +4013,7 @@
           <t>Update to version 8.5.63, 9.0.43, 10.0.2 or later.</t>
         </is>
       </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>['cve: CVE-2021-25122', 'url: https://lists.apache.org/thread.html/r7b95bc248603360501f18c8eb03bb6001ec0e', ',→e3296205b34b07105b7@%3Cannounce.tomcat.apache.org%3E', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.0.2', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.43', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.63', 'cert-bund: WID-SEC-2022-1375', 'cert-bund: WID-SEC-2022-1099', 'cert-bund: WID-SEC-2022-0624', 'cert-bund: WID-SEC-2022-0607', 'cert-bund: CB-K21/1094', 'cert-bund: CB-K21/1081', 'cert-bund: CB-K21/0770', 'cert-bund: CB-K21/0222', 'dfn-cert: DFN-CERT-2024-1989', 'dfn-cert: DFN-CERT-2022-1530 dfn-cert: DFN-CERT-2022-0733', 'dfn-cert: DFN-CERT-2021-2191', 'dfn-cert: DFN-CERT-2021-1904', 'dfn-cert: DFN-CERT-2021-1537', 'dfn-cert: DFN-CERT-2021-1536', 'dfn-cert: DFN-CERT-2021-1403', 'dfn-cert: DFN-CERT-2021-0810', 'dfn-cert: DFN-CERT-2021-0807', 'dfn-cert: DFN-CERT-2021-0544', 'dfn-cert: DFN-CERT-2021-0445']</t>
@@ -3880,6 +4024,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
         <v>8081</v>
       </c>
@@ -3923,6 +4068,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3941,6 +4087,7 @@
 Update to version 8.5.41, 9.0.20 or later.</t>
         </is>
       </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>['cve: CVE-2019-10072', 'url: http://tomcat.apache.org/security-9.html', 'url: http://tomcat.apache.org/security-8.html', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: CB-K20/1008', 'cert-bund: CB-K20/0029', 'cert-bund: CB-K19/0915', 'cert-bund: CB-K19/0523', 'dfn-cert: DFN-CERT-2020-0501', 'dfn-cert: DFN-CERT-2020-0088', 'dfn-cert: DFN-CERT-2020-0027', 'dfn-cert: DFN-CERT-2019-2457', 'dfn-cert: DFN-CERT-2019-2149', 'dfn-cert: DFN-CERT-2019-1895', 'dfn-cert: DFN-CERT-2019-1472', 'dfn-cert: DFN-CERT-2019-1268']</t>
@@ -3951,6 +4098,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
         <v>8081</v>
       </c>
@@ -3994,6 +4142,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652</t>
         </is>
       </c>
+      <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4011,6 +4160,7 @@
           <t>Update to version 8.5.41, 9.0.20 or later.</t>
         </is>
       </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>['cve: CVE-2019-10072', 'url: https://lists.apache.org/thread.html/df1a2c1b87c8a6c500ecdbbaf134c7f1491c8d-&gt;79d98b48c6b9f0fa6a@%3Cannounce.tomcat.apache.org%3E', 'url: http://www.securityfocus.com/bid/108874', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: CB-K20/1008', 'cert-bund: CB-K20/0029', 'cert-bund: CB-K19/0915', 'cert-bund: CB-K19/0523', 'dfn-cert: DFN-CERT-2020-0501', 'dfn-cert: DFN-CERT-2020-0088', 'dfn-cert: DFN-CERT-2020-0027', 'dfn-cert: DFN-CERT-2019-2457', 'dfn-cert: DFN-CERT-2019-2149', 'dfn-cert: DFN-CERT-2019-1895', 'dfn-cert: DFN-CERT-2019-1472', 'dfn-cert: DFN-CERT-2019-1268']</t>
@@ -4021,6 +4171,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
         <v>8081</v>
       </c>
@@ -4064,6 +4215,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4081,6 +4233,7 @@
           <t>Update to version 8.5.38, 9.0.16 or later.</t>
         </is>
       </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>['cve: CVE-2019-0199', 'url: http://tomcat.apache.org/security-9.html', 'url: http://tomcat.apache.org/security-8.html', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: CB-K20/0543', 'cert-bund: CB-K20/0029', 'cert-bund: CB-K19/0235', 'dfn-cert: DFN-CERT-2019-2710', 'dfn-cert: DFN-CERT-2019-1895', 'dfn-cert: DFN-CERT-2019-1755', 'dfn-cert: DFN-CERT-2019-1472', 'dfn-cert: DFN-CERT-2019-1231', 'dfn-cert: DFN-CERT-2019-1095', 'dfn-cert: DFN-CERT-2019-0594']</t>
@@ -4091,6 +4244,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
         <v>8081</v>
       </c>
@@ -4134,6 +4288,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4151,6 +4306,7 @@
           <t>Update to version 8.5.56, 9.0.36, 10.0.0-M6 or later.</t>
         </is>
       </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>['cve: CVE-2020-11996', 'url: https://lists.apache.org/thread.html/r5541ef6b6b68b49f76fc4c45695940116da2b', ',→cbe0312ef204a00a2e0%40%3Cannounce.tomcat.apache.org%3E', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2022-1375', 'cert-bund: CB-K20/1017', 'cert-bund: CB-K20/0637', 'cert-bund: CB-K20/0636', 'dfn-cert: DFN-CERT-2021-1736', 'dfn-cert: DFN-CERT-2021-0043', 'dfn-cert: DFN-CERT-2020-2006', 'dfn-cert: DFN-CERT-2020-1575', 'dfn-cert: DFN-CERT-2020-1490', 'dfn-cert: DFN-CERT-2020-1358']</t>
@@ -4161,6 +4317,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
         <v>8081</v>
       </c>
@@ -4189,6 +4346,7 @@
 Installation path / port: 8081/tcp</t>
         </is>
       </c>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
           <t>Product: cpe:/a:apache:tomcat:8.5.23
@@ -4196,6 +4354,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4213,6 +4372,7 @@
           <t>Update to version 8.5.57, 9.0.37, 10.0.0-M7 or later.</t>
         </is>
       </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>['cve: CVE-2020-13934', 'cve: CVE-2020-13935', 'url: https://lists.apache.org/thread.html/r61f411cf82488d6ec213063fc15feeeb88e31', ',→b0ca9c29652ee4f962e%40%3Cannounce.tomcat.apache.org%3E', 'url: https://lists.apache.org/thread.html/rd48c72bd3255bda87564d4da3791517c074d9', ',→4f8a701f93b85752651%40%3Cannounce.tomcat.apache.org%3E', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.0.0-M7', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.37', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.57', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2023-1048', 'cert-bund: WID-SEC-2022-1375', 'cert-bund: WID-SEC-2022-0519', 'cert-bund: CB-K20/1030', 'cert-bund: CB-K20/1021', 'cert-bund: CB-K20/1017', 'cert-bund: CB-K20/0717', 'dfn-cert: DFN-CERT-2022-1472 dfn-cert: DFN-CERT-2021-1736', 'dfn-cert: DFN-CERT-2021-0714', 'dfn-cert: DFN-CERT-2021-0132', 'dfn-cert: DFN-CERT-2020-2295', 'dfn-cert: DFN-CERT-2020-2287', 'dfn-cert: DFN-CERT-2020-2132', 'dfn-cert: DFN-CERT-2020-2006', 'dfn-cert: DFN-CERT-2020-1761', 'dfn-cert: DFN-CERT-2020-1707', 'dfn-cert: DFN-CERT-2020-1706', 'dfn-cert: DFN-CERT-2020-1575', 'dfn-cert: DFN-CERT-2020-1511']</t>
@@ -4223,6 +4383,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
         <v>8081</v>
       </c>
@@ -4265,6 +4426,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4283,6 +4445,7 @@
 Update to version 7.0.99, 8.5.50, 9.0.30 or later.</t>
         </is>
       </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>['cve: CVE-2019-17563', 'url: https://lists.apache.org/thread.html/8b4c1db8300117b28a0f3f743c0b9e3f964687a690cdf9662a884bbd%40%3Cannounce.tomcat.apache.org%3E', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2023-1229', 'cert-bund: WID-SEC-2023-1049', 'cert-bund: CB-K21/0071', 'cert-bund: CB-K20/1030', 'cert-bund: CB-K20/0318', 'cert-bund: CB-K20/0309', 'cert-bund: CB-K19/1102', 'dfn-cert: DFN-CERT-2021-0575', 'dfn-cert: DFN-CERT-2020-2132', 'dfn-cert: DFN-CERT-2020-1134', 'dfn-cert: DFN-CERT-2020-1129', 'dfn-cert: DFN-CERT-2020-0821', 'dfn-cert: DFN-CERT-2020-0780', 'dfn-cert: DFN-CERT-2020-0775', 'dfn-cert: DFN-CERT-2020-0557', 'dfn-cert: DFN-CERT-2020-0501', 'dfn-cert: DFN-CERT-2020-0345', 'dfn-cert: DFN-CERT-2020-0027', 'dfn-cert: DFN-CERT-2019-2710', 'dfn-cert: DFN-CERT-2019-2673']</t>
@@ -4293,6 +4456,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
         <v>8081</v>
       </c>
@@ -4338,6 +4502,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652</t>
         </is>
       </c>
+      <c r="P56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4370,6 +4535,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
         <v>8081</v>
       </c>
@@ -4410,6 +4576,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652</t>
         </is>
       </c>
+      <c r="P57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4427,6 +4594,7 @@
           <t>Update to version 8.5.83, 9.0.68, 10.0.27, 10.1.1 or later.</t>
         </is>
       </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>['http://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.10', 'http://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.0.53', 'http://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.32', 'http://tomcat.apache.org/security-7.html#Fixed_in_Apache_Tomcat_7.0.90', 'cert-bund: WID-SEC-2024-1682', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: CB-K19/0907', 'cert-bund: CB-K19/0616', 'cert-bund: CB-K19/0320', 'cert-bund: CB-K18/1005', 'cert-bund: CB-K18/0809', 'dfn-cert: DFN-CERT-2019-2418', 'dfn-cert: DFN-CERT-2019-1627', 'dfn-cert: DFN-CERT-2019-1237', 'dfn-cert: DFN-CERT-2019-0951', 'dfn-cert: DFN-CERT-2019-0451', 'dfn-cert: DFN-CERT-2019-0147', 'dfn-cert: DFN-CERT-2018-2165', 'dfn-cert: DFN-CERT-2018-2142', 'dfn-cert: DFN-CERT-2018-1753', 'dfn-cert: DFN-CERT-2018-1471', 'dfn-cert: DFN-CERT-2018-1443', 'dfn-cert: DFN-CERT-2018-1262']</t>
@@ -4437,6 +4605,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>8081</v>
       </c>
@@ -4468,12 +4637,14 @@
 path / port: 8081/tcp</t>
         </is>
       </c>
+      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr">
         <is>
           <t>cpe:/a:apache:tomcat:8.5.23
 Detected by Apache Tomcat Detection Consolidation (OID: 1.3.6.1.4.1.25623.1.0.10  -&gt;7652)</t>
         </is>
       </c>
+      <c r="P58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4506,6 +4677,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
         <v>8081</v>
       </c>
@@ -4550,6 +4722,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4567,6 +4740,7 @@
           <t>Update to version 8.5.96, 9.0.83, 10.1.16, 11.0.0-M11 or later.</t>
         </is>
       </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>['cve: CVE-2023-46589', 'url: https://lists.apache.org/thread/0rqq6ktozqc42ro8hhxdmmdjm1k1tpxr', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.0-M1', ',→1', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.16', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.83', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.96', 'cert-bund: WID-SEC-2025-0810', 'cert-bund: WID-SEC-2024-1653', 'cert-bund: WID-SEC-2024-1652', 'cert-bund: WID-SEC-2024-1642', 'cert-bund: WID-SEC-2024-1248', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-0899', 'cert-bund: WID-SEC-2024-0890', 'cert-bund: WID-SEC-2024-0873', 'cert-bund: WID-SEC-2024-0869', 'cert-bund: WID-SEC-2024-0769', 'cert-bund: WID-SEC-2024-0119', 'cert-bund: WID-SEC-2024-0108', 'cert-bund: WID-SEC-2024-0106', 'cert-bund: WID-SEC-2024-0101 cert-bund: WID-SEC-2024-0094', 'cert-bund: WID-SEC-2023-3020', 'dfn-cert: DFN-CERT-2024-1404', 'dfn-cert: DFN-CERT-2024-1036', 'dfn-cert: DFN-CERT-2024-1000', 'dfn-cert: DFN-CERT-2024-0723', 'dfn-cert: DFN-CERT-2024-0722', 'dfn-cert: DFN-CERT-2024-0506', 'dfn-cert: DFN-CERT-2024-0411', 'dfn-cert: DFN-CERT-2024-0174', 'dfn-cert: DFN-CERT-2024-0127', 'dfn-cert: DFN-CERT-2023-2977']</t>
@@ -4577,6 +4751,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
         <v>8081</v>
       </c>
@@ -4621,6 +4796,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4639,6 +4815,7 @@
 Update Apache Tomcat to version 10.1.0-M15, 10.0.21, 9.0.63, 8.5.79 or later to receive the corrected / updated documentation</t>
         </is>
       </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>['cve: CVE-2022-29885', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.0-M1', ',→5', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.0.21', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.63', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.79', 'url: https://lists.apache.org/thread/548bnqoxvp0rqqq2yyj90l0xvwhq087d', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2022-1780', 'cert-bund: WID-SEC-2022-1767', 'cert-bund: WID-SEC-2022-0799', 'cert-bund: WID-SEC-2022-0467', 'cert-bund: CB-K22/0597', 'dfn-cert: DFN-CERT-2024-1989', 'dfn-cert: DFN-CERT-2024-0762', 'dfn-cert: DFN-CERT-2022-2392', 'dfn-cert: DFN-CERT-2022-2323', 'dfn-cert: DFN-CERT-2022-1070']</t>
@@ -4649,6 +4826,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
         <v>8081</v>
       </c>
@@ -4692,6 +4870,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4704,6 +4883,8 @@
           <t>Apache Tomcat is prone to a denial of service (DoS) vulnerability.</t>
         </is>
       </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t>['cve: CVE-2023-24998', 'url: https://lists.apache.org/thread/g16kv0xpp272htz107molwbbgdrqrdk1', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.0-M3', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.5', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.71', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.85 url: https://lists.apache.org/thread/4xl4l09mhwg4vgsk7dxqogcjrobrrdoy', 'cert-bund: WID-SEC-2025-0810', 'cert-bund: WID-SEC-2024-1652', 'cert-bund: WID-SEC-2024-1642', 'cert-bund: WID-SEC-2024-1637', 'cert-bund: WID-SEC-2024-1622', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-0890', 'cert-bund: WID-SEC-2024-0888', 'cert-bund: WID-SEC-2024-0794', 'cert-bund: WID-SEC-2024-0124', 'cert-bund: WID-SEC-2024-0117', 'cert-bund: WID-SEC-2024-0054', 'cert-bund: WID-SEC-2023-2688', 'cert-bund: WID-SEC-2023-2675', 'cert-bund: WID-SEC-2023-2674', 'cert-bund: WID-SEC-2023-2625', 'cert-bund: WID-SEC-2023-2309', 'cert-bund: WID-SEC-2023-2031', 'cert-bund: WID-SEC-2023-1817', 'cert-bund: WID-SEC-2023-1815', 'cert-bund: WID-SEC-2023-1813', 'cert-bund: WID-SEC-2023-1812', 'cert-bund: WID-SEC-2023-1811', 'cert-bund: WID-SEC-2023-1809', 'cert-bund: WID-SEC-2023-1808', 'cert-bund: WID-SEC-2023-1807', 'cert-bund: WID-SEC-2023-1794', 'cert-bund: WID-SEC-2023-1792', 'cert-bund: WID-SEC-2023-1791', 'cert-bund: WID-SEC-2023-1784', 'cert-bund: WID-SEC-2023-1783', 'cert-bund: WID-SEC-2023-1782', 'cert-bund: WID-SEC-2023-1424', 'cert-bund: WID-SEC-2023-1142', 'cert-bund: WID-SEC-2023-1021', 'cert-bund: WID-SEC-2023-1017', 'cert-bund: WID-SEC-2023-1016', 'cert-bund: WID-SEC-2023-1012', 'cert-bund: WID-SEC-2023-1007', 'cert-bund: WID-SEC-2023-1005', 'cert-bund: WID-SEC-2023-0609', 'cert-bund: WID-SEC-2023-0433', 'dfn-cert: DFN-CERT-2025-1992', 'dfn-cert: DFN-CERT-2024-2151', 'dfn-cert: DFN-CERT-2024-1865', 'dfn-cert: DFN-CERT-2024-1006 dfn-cert: DFN-CERT-2024-0059', 'dfn-cert: DFN-CERT-2024-0048', 'dfn-cert: DFN-CERT-2023-2778', 'dfn-cert: DFN-CERT-2023-2545', 'dfn-cert: DFN-CERT-2023-2469', 'dfn-cert: DFN-CERT-2023-2054', 'dfn-cert: DFN-CERT-2023-1648', 'dfn-cert: DFN-CERT-2023-1643', 'dfn-cert: DFN-CERT-2023-1642', 'dfn-cert: DFN-CERT-2023-1423', 'dfn-cert: DFN-CERT-2023-1362', 'dfn-cert: DFN-CERT-2023-1109', 'dfn-cert: DFN-CERT-2023-0902', 'dfn-cert: DFN-CERT-2023-0886', 'dfn-cert: DFN-CERT-2023-0884', 'dfn-cert: DFN-CERT-2023-0881', 'dfn-cert: DFN-CERT-2023-0763', 'dfn-cert: DFN-CERT-2023-0574', 'dfn-cert: DFN-CERT-2023-0540', 'dfn-cert: DFN-CERT-2023-0414']</t>
@@ -4714,6 +4895,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
         <v>8081</v>
       </c>
@@ -4757,6 +4939,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4792,6 +4975,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
         <v>8081</v>
       </c>
@@ -4834,6 +5018,7 @@
 Method: Apache Tomcat Detection Consolidation</t>
         </is>
       </c>
+      <c r="P63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4851,6 +5036,7 @@
           <t>Update to version 7.0.108, 8.5.63, 9.0.43, 10.0.2 or later.</t>
         </is>
       </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>['cve: CVE-2021-25329', 'url: https://lists.apache.org/thread.html/rfe62fbf9d4c314f166fe8c668e50e5d9dd882', ',→a99447f26f0367474bf@%3Cannounce.tomcat.apache.org%3E', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.0.2', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.43', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.63', 'url: https://tomcat.apache.org/security-7.html#Fixed_in_Apache_Tomcat_7.0.108', 'cert-bund: WID-SEC-2022-1099', 'cert-bund: WID-SEC-2022-0607', 'cert-bund: CB-K21/0222', 'dfn-cert: DFN-CERT-2024-1926', 'dfn-cert: DFN-CERT-2022-1530', 'dfn-cert: DFN-CERT-2022-0733', 'dfn-cert: DFN-CERT-2021-1904', 'dfn-cert: DFN-CERT-2021-1403', 'dfn-cert: DFN-CERT-2021-0903 dfn-cert: DFN-CERT-2021-0835', 'dfn-cert: DFN-CERT-2021-0807', 'dfn-cert: DFN-CERT-2021-0714', 'dfn-cert: DFN-CERT-2021-0544', 'dfn-cert: DFN-CERT-2021-0445']</t>
@@ -4861,6 +5047,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
         <v>8081</v>
       </c>
@@ -4904,6 +5091,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4921,6 +5109,7 @@
           <t>Update to version 7.0.109, 8.5.66, 9.0.46, 10.0.6 or later.</t>
         </is>
       </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>['cve: CVE-2021-30640', 'url: https://lists.apache.org/thread.html/r59f9ef03929d32120f91f4ea7e6e79edd5688', ',→d75d0a9b65fd26d1fe8%40%3Cannounce.tomcat.apache.org%3E', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.0.6', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.46', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.66', 'url: https://tomcat.apache.org/security-7.html#Fixed_in_Apache_Tomcat_7.0.109', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2022-1116', 'cert-bund: WID-SEC-2022-0623', 'cert-bund: WID-SEC-2022-0615', 'cert-bund: WID-SEC-2022-0607', 'cert-bund: CB-K21/0733', 'dfn-cert: DFN-CERT-2022-1530', 'dfn-cert: DFN-CERT-2022-0826', 'dfn-cert: DFN-CERT-2022-0733', 'dfn-cert: DFN-CERT-2021-2496', 'dfn-cert: DFN-CERT-2021-2438', 'dfn-cert: DFN-CERT-2021-2297', 'dfn-cert: DFN-CERT-2021-2169', 'dfn-cert: DFN-CERT-2021-1728', 'dfn-cert: DFN-CERT-2021-1668', 'dfn-cert: DFN-CERT-2021-1472']</t>
@@ -4931,6 +5120,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
         <v>8040</v>
       </c>
@@ -4975,6 +5165,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4992,6 +5183,7 @@
           <t>Upgrade to Apache Tomcat version 9.0.5, 8.5.28, 8.0.50, 7.0.85 or later.</t>
         </is>
       </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>['cve: CVE-2018-1305', 'cve: CVE-2018-1304', 'url: http://tomcat.apache.org/security-9.html', 'url: http://www.securityfocus.com/bid/103144', 'url: http://www.securityfocus.com/bid/103170', 'url: http://tomcat.apache.org/security-8.html', 'url: http://tomcat.apache.org/security-7.html', 'url: https://lists.apache.org/thread.html/b1d7e2425d6fd2cebed40d318f9365b4454607', ',→7e10949b01b1f8a0fb@%3Cannounce.tomcat.apache.org%3E', 'cert-bund: WID-SEC-2024-1682', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: CB-K19/1121', 'cert-bund: CB-K19/0321', 'cert-bund: CB-K18/1007', 'cert-bund: CB-K18/1006', 'cert-bund: CB-K18/1005', 'cert-bund: CB-K18/0790', 'cert-bund: CB-K18/0420', 'cert-bund: CB-K18/0349', 'dfn-cert: DFN-CERT-2019-1627', 'dfn-cert: DFN-CERT-2019-0772', 'dfn-cert: DFN-CERT-2018-2165', 'dfn-cert: DFN-CERT-2018-2142', 'dfn-cert: DFN-CERT-2018-2125', 'dfn-cert: DFN-CERT-2018-2103', 'dfn-cert: DFN-CERT-2018-1753', 'dfn-cert: DFN-CERT-2018-1407', 'dfn-cert: DFN-CERT-2018-1274', 'dfn-cert: DFN-CERT-2018-1253', 'dfn-cert: DFN-CERT-2018-1038', 'dfn-cert: DFN-CERT-2018-0922', 'dfn-cert: DFN-CERT-2018-0733', 'dfn-cert: DFN-CERT-2018-0455', 'dfn-cert: DFN-CERT-2018-0378']</t>
@@ -5002,6 +5194,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
         <v>8040</v>
       </c>
@@ -5050,6 +5243,7 @@
 Method: Apache Tomcat Detection Consolidation OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5067,6 +5261,7 @@
           <t>Update to version 9.0.96, 10.1.31, 11.0.0 or later.</t>
         </is>
       </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>['cve: CVE-2024-52316 url: https://lists.apache.org/thread/lopzlqh91jj9n334g02om08sbysdb928', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.0', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.31', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.96', 'cert-bund: WID-SEC-2025-0521', 'cert-bund: WID-SEC-2024-3684', 'cert-bund: WID-SEC-2024-3486', 'dfn-cert: DFN-CERT-2025-2285', 'dfn-cert: DFN-CERT-2025-2098', 'dfn-cert: DFN-CERT-2025-0890', 'dfn-cert: DFN-CERT-2025-0146', 'dfn-cert: DFN-CERT-2025-0134', 'dfn-cert: DFN-CERT-2024-3156', 'dfn-cert: DFN-CERT-2024-3077']</t>
@@ -5077,6 +5272,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
         <v>8040</v>
       </c>
@@ -5123,6 +5319,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5140,6 +5337,7 @@
           <t>Update to version 8.5.93, 9.0.80, 10.1.13, 11.0.0-M11 or later.</t>
         </is>
       </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>['cve: CVE-2023-41080', 'url: https://lists.apache.org/thread/71wvwprtx2j2m54fovq9zr7gbm2wow2f', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.0-M1', ',→1', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.13', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.80', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.93', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-0871', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2023-3070', 'cert-bund: WID-SEC-2023-2917', 'cert-bund: WID-SEC-2023-2690', 'cert-bund: WID-SEC-2023-2679', 'cert-bund: WID-SEC-2023-2182', 'dfn-cert: DFN-CERT-2024-3078', 'dfn-cert: DFN-CERT-2024-0723', 'dfn-cert: DFN-CERT-2024-0076', 'dfn-cert: DFN-CERT-2023-3070', 'dfn-cert: DFN-CERT-2023-3061', 'dfn-cert: DFN-CERT-2023-2803', 'dfn-cert: DFN-CERT-2023-2586', 'dfn-cert: DFN-CERT-2023-2568', 'dfn-cert: DFN-CERT-2023-2542', 'dfn-cert: DFN-CERT-2023-2536', 'dfn-cert: DFN-CERT-2023-2469', 'dfn-cert: DFN-CERT-2023-2468', 'dfn-cert: DFN-CERT-2023-1983']</t>
@@ -5150,6 +5348,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
         <v>8040</v>
       </c>
@@ -5166,6 +5365,7 @@
       <c r="K68" t="n">
         <v>6.1</v>
       </c>
+      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
           <t>Installed version: 8.5.23
@@ -5173,6 +5373,7 @@
 Installation path / port: 8040/tcp</t>
         </is>
       </c>
+      <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr">
         <is>
           <t>Product: cpe:/a:apache:tomcat:8.5.23
@@ -5180,6 +5381,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5214,6 +5416,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
         <v>8040</v>
       </c>
@@ -5257,6 +5460,7 @@
 Method: Apache Tomcat Detection Consolidation</t>
         </is>
       </c>
+      <c r="P69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5289,6 +5493,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
         <v>8040</v>
       </c>
@@ -5332,6 +5537,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652</t>
         </is>
       </c>
+      <c r="P70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5349,6 +5555,7 @@
           <t>Update to version 7.0.107, 8.5.60, 9.0.40, 10.0.0-M10 or later.</t>
         </is>
       </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>['cve: CVE-2021-24122', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.0.0-M1', ',→0', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.40', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.60', 'url: https://tomcat.apache.org/security-7.html#Fixed_in_Apache_Tomcat_7.0.107', 'url: https://lists.apache.org/thread.html/rce5ac9a40173651d540babce59f6f3825f12c ,→6d4e886ba00823b11e5%40%3Cannounce.tomcat.apache.org%3E', 'cert-bund: WID-SEC-2023-2465', 'cert-bund: WID-SEC-2022-0607', 'cert-bund: CB-K21/0049', 'dfn-cert: DFN-CERT-2022-1530', 'dfn-cert: DFN-CERT-2021-1904', 'dfn-cert: DFN-CERT-2021-0835', 'dfn-cert: DFN-CERT-2021-0714', 'dfn-cert: DFN-CERT-2021-0544', 'dfn-cert: DFN-CERT-2021-0338', 'dfn-cert: DFN-CERT-2020-2646']</t>
@@ -5359,6 +5566,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
         <v>8040</v>
       </c>
@@ -5402,6 +5610,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5434,6 +5643,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
         <v>8040</v>
       </c>
@@ -5477,6 +5687,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5494,6 +5705,7 @@
           <t>Update to version 8.5.68, 9.0.48, 10.0.7 or later.</t>
         </is>
       </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>['cve: CVE-2021-33037', 'url: https://lists.apache.org/thread.html/r612a79269b0d5e5780c62dfd34286a8037232-&gt;fec0bc6f1a7e60c9381%40%3Cannounce.tomcat.apache.org%3E', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.0.7', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.48', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.68', 'cert-bund: WID-SEC-2024-2180', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2022-1894', 'cert-bund: WID-SEC-2022-1375', 'cert-bund: WID-SEC-2022-1296', 'cert-bund: WID-SEC-2022-1116', 'cert-bund: WID-SEC-2022-0624', 'cert-bund: WID-SEC-2022-0623', 'cert-bund: WID-SEC-2022-0615 cert-bund: WID-SEC-2022-0607 cert-bund: WID-SEC-2022-0094', 'cert-bund: CB-K22/0066', 'cert-bund: CB-K21/1087', 'cert-bund: CB-K21/1084', 'cert-bund: CB-K21/0733', 'dfn-cert: DFN-CERT-2022-1530', 'dfn-cert: DFN-CERT-2022-0872', 'dfn-cert: DFN-CERT-2022-0826', 'dfn-cert: DFN-CERT-2022-0733', 'dfn-cert: DFN-CERT-2021-2496', 'dfn-cert: DFN-CERT-2021-2297', 'dfn-cert: DFN-CERT-2021-2223', 'dfn-cert: DFN-CERT-2021-2193', 'dfn-cert: DFN-CERT-2021-2188', 'dfn-cert: DFN-CERT-2021-1728', 'dfn-cert: DFN-CERT-2021-1668', 'dfn-cert: DFN-CERT-2021-1472']</t>
@@ -5504,6 +5716,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
         <v>8040</v>
       </c>
@@ -5548,6 +5761,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5566,6 +5780,7 @@
           <t>Update to version 8.5.64, 9.0.44 or later.</t>
         </is>
       </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>['cve: CVE-2024-21733', 'url: https://lists.apache.org/thread/h9bjqdd0odj6lhs2o96qgowcc6hb0cfz', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.44', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.64', 'cert-bund: WID-SEC-2024-0769', 'cert-bund: WID-SEC-2024-0163', 'dfn-cert: DFN-CERT-2025-1517', 'dfn-cert: DFN-CERT-2025-0134', 'dfn-cert: DFN-CERT-2024-1404', 'dfn-cert: DFN-CERT-2024-0648']</t>
@@ -5576,6 +5791,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
         <v>8040</v>
       </c>
@@ -5619,6 +5835,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652</t>
         </is>
       </c>
+      <c r="P74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5636,6 +5853,7 @@
           <t>Update to version 8.5.99, 9.0.86, 10.1.19, 11.0.0-M17 or later.</t>
         </is>
       </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>['cve: CVE-2024-23672', 'cve: CVE-2024-24549', 'url: https://lists.apache.org/thread/cmpswfx6tj4s7x0nxxosvfqs11lvdx2f', 'url: https://lists.apache.org/thread/4c50rmomhbbsdgfjsgwlb51xdwfjdcvg', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.0-M1', ',→7', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.19', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.86', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.99', 'url: https://nowotarski.info/http2-continuation-flood/', 'url: https://nowotarski.info/http2-continuation-flood-technical-details/', 'cert-bund: WID-SEC-2024-3663', 'cert-bund: WID-SEC-2024-3508', 'cert-bund: WID-SEC-2024-3377 cert-bund: WID-SEC-2024-3220', 'cert-bund: WID-SEC-2024-3219', 'cert-bund: WID-SEC-2024-3196', 'cert-bund: WID-SEC-2024-3195', 'cert-bund: WID-SEC-2024-3191', 'cert-bund: WID-SEC-2024-1656', 'cert-bund: WID-SEC-2024-1642', 'cert-bund: WID-SEC-2024-1638', 'cert-bund: WID-SEC-2024-1622', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-1214', 'cert-bund: WID-SEC-2024-1210', 'cert-bund: WID-SEC-2024-0769', 'cert-bund: WID-SEC-2024-0630', 'dfn-cert: DFN-CERT-2025-1517', 'dfn-cert: DFN-CERT-2024-3096', 'dfn-cert: DFN-CERT-2024-3078', 'dfn-cert: DFN-CERT-2024-2743', 'dfn-cert: DFN-CERT-2024-1846', 'dfn-cert: DFN-CERT-2024-1372', 'dfn-cert: DFN-CERT-2024-1235', 'dfn-cert: DFN-CERT-2024-1036', 'dfn-cert: DFN-CERT-2024-1011', 'dfn-cert: DFN-CERT-2024-0723', 'dfn-cert: DFN-CERT-2024-0722', 'dfn-cert: DFN-CERT-2024-0697']</t>
@@ -5646,6 +5864,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
         <v>8040</v>
       </c>
@@ -5691,6 +5910,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5703,6 +5923,8 @@
           <t>Apache Tomcat is prone to multiple vulnerabilities.</t>
         </is>
       </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>['cert-bund: WID-SEC-2024-3377', 'cert-bund: WID-SEC-2024-3220', 'cert-bund: WID-SEC-2024-3219', 'cert-bund: WID-SEC-2024-3196', 'cert-bund: WID-SEC-2024-3195', 'cert-bund: WID-SEC-2024-3191', 'cert-bund: WID-SEC-2024-1656', 'cert-bund: WID-SEC-2024-1642', 'cert-bund: WID-SEC-2024-1638', 'cert-bund: WID-SEC-2024-1622', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-1214', 'cert-bund: WID-SEC-2024-1210', 'cert-bund: WID-SEC-2024-0769', 'cert-bund: WID-SEC-2024-0630', 'dfn-cert: DFN-CERT-2025-1517', 'dfn-cert: DFN-CERT-2024-3096', 'dfn-cert: DFN-CERT-2024-3078', 'dfn-cert: DFN-CERT-2024-2743', 'dfn-cert: DFN-CERT-2024-1846', 'dfn-cert: DFN-CERT-2024-1372', 'dfn-cert: DFN-CERT-2024-1235', 'dfn-cert: DFN-CERT-2024-1036', 'dfn-cert: DFN-CERT-2024-1011', 'dfn-cert: DFN-CERT-2024-0723', 'dfn-cert: DFN-CERT-2024-0722', 'dfn-cert: DFN-CERT-2024-0697']</t>
@@ -5713,6 +5935,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
         <v>8040</v>
       </c>
@@ -5792,6 +6015,7 @@
           <t>Update to version 9.0.105, 10.1.41, 11.0.7 or later.</t>
         </is>
       </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>['cve: CVE-2025-46701', 'url: https://lists.apache.org/thread/xhqqk9w5q45srcdqhogdk04lhdscv30j', 'cert-bund: WID-SEC-2025-1850', 'cert-bund: WID-SEC-2025-1365', 'cert-bund: WID-SEC-2025-1165', 'dfn-cert: DFN-CERT-2025-2285', 'dfn-cert: DFN-CERT-2025-2098', 'dfn-cert: DFN-CERT-2025-1991', 'dfn-cert: DFN-CERT-2025-1905', 'dfn-cert: DFN-CERT-2025-1780', 'dfn-cert: DFN-CERT-2025-1384']</t>
@@ -5802,6 +6026,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
         <v>8040</v>
       </c>
@@ -5845,6 +6070,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5862,6 +6088,7 @@
           <t>Update to version 8.5.86, 9.0.72, 10.1.6, 11.0.0-M3 or later.</t>
         </is>
       </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>['cve: CVE-2023-28708', 'url: https://lists.apache.org/thread/hdksc59z3s7tm39x0pp33mtwdrt8qr67', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.0-M3', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.6', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.72', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.86', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2023-2674', 'cert-bund: WID-SEC-2023-1812', 'cert-bund: WID-SEC-2023-1808', 'cert-bund: WID-SEC-2023-1784', 'cert-bund: WID-SEC-2023-1783', 'cert-bund: WID-SEC-2023-1782', 'cert-bund: WID-SEC-2023-1424', 'cert-bund: WID-SEC-2023-1021', 'cert-bund: WID-SEC-2023-1017', 'cert-bund: WID-SEC-2023-0717', 'dfn-cert: DFN-CERT-2025-1517', 'dfn-cert: DFN-CERT-2024-3078', 'dfn-cert: DFN-CERT-2023-2778', 'dfn-cert: DFN-CERT-2023-2545', 'dfn-cert: DFN-CERT-2023-2054', 'dfn-cert: DFN-CERT-2023-0772', 'dfn-cert: DFN-CERT-2023-0763', 'dfn-cert: DFN-CERT-2023-0640']</t>
@@ -5872,6 +6099,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
         <v>8040</v>
       </c>
@@ -5915,6 +6143,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5932,6 +6161,7 @@
           <t>Update to version 8.5.58, 9.0.38, 10.0.0-M8 or later.</t>
         </is>
       </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>['cve: CVE-2020-13943', 'url: https://lists.apache.org/thread.html/r4a390027eb27e4550142fac6c8317cc684b157ae314d31514747f307%40%3Cannounce.tomcat.apache.org%3E', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2023-2467', 'cert-bund: CB-K20/0971', 'dfn-cert: DFN-CERT-2022-0733', 'dfn-cert: DFN-CERT-2021-2620', 'dfn-cert: DFN-CERT-2021-0338', 'dfn-cert: DFN-CERT-2021-0134', 'dfn-cert: DFN-CERT-2021-0034', 'dfn-cert: DFN-CERT-2020-2224']</t>
@@ -5942,6 +6172,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
         <v>8040</v>
       </c>
@@ -5985,6 +6216,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6002,6 +6234,7 @@
           <t>Update to version 7.0.91, 8.5.34, 9.0.12 or later.</t>
         </is>
       </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>['cve: CVE-2018-11784', 'url: http://tomcat.apache.org/security-9.html', 'url: http://tomcat.apache.org/security-8.html', 'url: http://tomcat.apache.org/security-7.html', 'cert-bund: WID-SEC-2025-1212', 'cert-bund: WID-SEC-2024-1682', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2023-0531 cert-bund: WID-SEC-2023-0460', 'cert-bund: CB-K20/0029', 'cert-bund: CB-K19/1121', 'cert-bund: CB-K19/0907', 'cert-bund: CB-K19/0616', 'cert-bund: CB-K19/0320', 'cert-bund: CB-K19/0050', 'cert-bund: CB-K18/0963', 'dfn-cert: DFN-CERT-2019-2710', 'dfn-cert: DFN-CERT-2019-2159', 'dfn-cert: DFN-CERT-2019-1562', 'dfn-cert: DFN-CERT-2019-1237', 'dfn-cert: DFN-CERT-2019-0771', 'dfn-cert: DFN-CERT-2019-0147', 'dfn-cert: DFN-CERT-2019-0104', 'dfn-cert: DFN-CERT-2018-2435', 'dfn-cert: DFN-CERT-2018-2165', 'dfn-cert: DFN-CERT-2018-2142', 'dfn-cert: DFN-CERT-2018-2000']</t>
@@ -6012,6 +6245,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
         <v>8040</v>
       </c>
@@ -6028,6 +6262,7 @@
       <c r="K80" t="n">
         <v>6.5</v>
       </c>
+      <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
           <t>Installed version: 8.5.23
@@ -6050,6 +6285,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6062,11 +6298,8 @@
           <t>Apache Tomcat is prone to an authentication weakness vulnerability in the JNDI Realm.</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Update to version 7.0.91, 8.5.34, 9.0.12 or later.</t>
-        </is>
-      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>['cve: CVE-2021-30640', 'url: https://lists.apache.org/thread.html/r59f9ef03929d32120f91f4ea7e6e79edd5688', ',→d75d0a9b65fd26d1fe8%40%3Cannounce.tomcat.apache.org%3E', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.0.6', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.46', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.66', 'url: https://tomcat.apache.org/security-7.html#Fixed_in_Apache_Tomcat_7.0.109', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2022-1116', 'cert-bund: WID-SEC-2022-0623', 'cert-bund: WID-SEC-2022-0615', 'cert-bund: WID-SEC-2022-0607', 'cert-bund: CB-K21/0733', 'dfn-cert: DFN-CERT-2022-1530', 'dfn-cert: DFN-CERT-2022-0826', 'dfn-cert: DFN-CERT-2022-0733', 'dfn-cert: DFN-CERT-2021-2496', 'dfn-cert: DFN-CERT-2021-2438 dfn-cert: DFN-CERT-2021-2297', 'dfn-cert: DFN-CERT-2021-2169', 'dfn-cert: DFN-CERT-2021-1728', 'dfn-cert: DFN-CERT-2021-1668', 'dfn-cert: DFN-CERT-2021-1472']</t>
@@ -6077,6 +6310,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
         <v>8081</v>
       </c>
@@ -6093,6 +6327,7 @@
       <c r="K81" t="n">
         <v>6.5</v>
       </c>
+      <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
           <t>Installed version: 8.5.23
@@ -6116,6 +6351,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6149,6 +6385,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
         <v>8081</v>
       </c>
@@ -6194,6 +6431,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652</t>
         </is>
       </c>
+      <c r="P82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6212,6 +6450,7 @@
           <t>Update to version 9.0.96, 10.1.31, 11.0.0 or later.</t>
         </is>
       </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>['cve: CVE-2024-52316', 'url: https://lists.apache.org/thread/lopzlqh91jj9n334g02om08sbysdb928', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.0', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.31', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.96', 'cert-bund: WID-SEC-2025-0521', 'cert-bund: WID-SEC-2024-3684', 'cert-bund: WID-SEC-2024-3486', 'dfn-cert: DFN-CERT-2025-2285', 'dfn-cert: DFN-CERT-2025-2098', 'dfn-cert: DFN-CERT-2025-0890', 'dfn-cert: DFN-CERT-2025-0146', 'dfn-cert: DFN-CERT-2025-0134', 'dfn-cert: DFN-CERT-2024-3156', 'dfn-cert: DFN-CERT-2024-3077']</t>
@@ -6222,6 +6461,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
         <v>8081</v>
       </c>
@@ -6267,6 +6507,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6284,6 +6525,7 @@
           <t>Update to version 7.0.94, 8.5.40, 9.0.18 or later.</t>
         </is>
       </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>['cve: CVE-2019-0221', 'url: https://seclists.org/fulldisclosure/2019/May/50', 'url: https://lists.apache.org/thread.html/6e6e9eacf7b28fd63d249711e9d3ccd4e0a83f556e324aee37be5a8c@%3Cannounce.tomcat.apache.org%3E', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2023-1994', 'cert-bund: CB-K20/0029', 'cert-bund: CB-K19/0434', 'dfn-cert: DFN-CERT-2024-1926', 'dfn-cert: DFN-CERT-2021-0819', 'dfn-cert: DFN-CERT-2020-1129', 'dfn-cert: DFN-CERT-2020-1094', 'dfn-cert: DFN-CERT-2020-0557', 'dfn-cert: DFN-CERT-2019-2710', 'dfn-cert: DFN-CERT-2019-2457', 'dfn-cert: DFN-CERT-2019-1895', 'dfn-cert: DFN-CERT-2019-1704', 'dfn-cert: DFN-CERT-2019-1472', 'dfn-cert: DFN-CERT-2019-1231 dfn-cert: DFN-CERT-2019-1092']</t>
@@ -6294,6 +6536,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
         <v>8081</v>
       </c>
@@ -6337,6 +6580,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6355,6 +6599,7 @@
           <t>Update to version 8.5.93, 9.0.80, 10.1.13, 11.0.0-M11 or later.</t>
         </is>
       </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>['cve: CVE-2023-41080', 'url: https://lists.apache.org/thread/71wvwprtx2j2m54fovq9zr7gbm2wow2f', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.0-M1', ',→1', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.13', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.80', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.93', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-0871', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2023-3070', 'cert-bund: WID-SEC-2023-2917', 'cert-bund: WID-SEC-2023-2690', 'cert-bund: WID-SEC-2023-2679', 'cert-bund: WID-SEC-2023-2182', 'dfn-cert: DFN-CERT-2024-3078', 'dfn-cert: DFN-CERT-2024-0723', 'dfn-cert: DFN-CERT-2024-0076', 'dfn-cert: DFN-CERT-2023-3070', 'dfn-cert: DFN-CERT-2023-3061', 'dfn-cert: DFN-CERT-2023-2803', 'dfn-cert: DFN-CERT-2023-2586', 'dfn-cert: DFN-CERT-2023-2568', 'dfn-cert: DFN-CERT-2023-2542', 'dfn-cert: DFN-CERT-2023-2536', 'dfn-cert: DFN-CERT-2023-2469', 'dfn-cert: DFN-CERT-2023-2468', 'dfn-cert: DFN-CERT-2023-1983']</t>
@@ -6365,6 +6610,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
         <v>8081</v>
       </c>
@@ -6406,6 +6652,7 @@
 Method: Apache Tomcat Detection Consolidation OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6438,6 +6685,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
         <v>8081</v>
       </c>
@@ -6481,6 +6729,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6499,6 +6748,7 @@
           <t>Update to version 7.0.107, 8.5.60, 9.0.40, 10.0.0-M10 or later.</t>
         </is>
       </c>
+      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>['cve: CVE-2021-24122', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.0.0-M1', ',→0', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.40', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.60', 'url: https://tomcat.apache.org/security-7.html#Fixed_in_Apache_Tomcat_7.0.107', 'url: https://lists.apache.org/thread.html/rce5ac9a40173651d540babce59f6f3825f12c', ',→6d4e886ba00823b11e5%40%3Cannounce.tomcat.apache.org%3E', 'cert-bund: WID-SEC-2023-2465', 'cert-bund: WID-SEC-2022-0607', 'cert-bund: CB-K21/0049', 'dfn-cert: DFN-CERT-2022-1530', 'dfn-cert: DFN-CERT-2021-1904', 'dfn-cert: DFN-CERT-2021-0835', 'dfn-cert: DFN-CERT-2021-0714', 'dfn-cert: DFN-CERT-2021-0544', 'dfn-cert: DFN-CERT-2021-0338', 'dfn-cert: DFN-CERT-2020-2646']</t>
@@ -6509,6 +6759,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
         <v>8081</v>
       </c>
@@ -6552,6 +6803,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6564,6 +6816,8 @@
           <t>Apache Tomcat is prone to an HTTP request smuggling vulnerability.</t>
         </is>
       </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>['cve: CVE-2021-33037', 'url: https://lists.apache.org/thread.html/r612a79269b0d5e5780c62dfd34286a8037232', ',→fec0bc6f1a7e60c9381%40%3Cannounce.tomcat.apache.org%3E', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.0.7', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.48', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.68', 'cert-bund: WID-SEC-2024-2180', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2022-1894', 'cert-bund: WID-SEC-2022-1375', 'cert-bund: WID-SEC-2022-1296', 'cert-bund: WID-SEC-2022-1116', 'cert-bund: WID-SEC-2022-0624', 'cert-bund: WID-SEC-2022-0623', 'cert-bund: WID-SEC-2022-0615', 'cert-bund: WID-SEC-2022-0607', 'cert-bund: WID-SEC-2022-0094', 'cert-bund: CB-K22/0066 cert-bund: CB-K21/1087', 'cert-bund: CB-K21/1084', 'cert-bund: CB-K21/0733', 'dfn-cert: DFN-CERT-2022-1530', 'dfn-cert: DFN-CERT-2022-0872', 'dfn-cert: DFN-CERT-2022-0826', 'dfn-cert: DFN-CERT-2022-0733', 'dfn-cert: DFN-CERT-2021-2496', 'dfn-cert: DFN-CERT-2021-2297', 'dfn-cert: DFN-CERT-2021-2223', 'dfn-cert: DFN-CERT-2021-2193', 'dfn-cert: DFN-CERT-2021-2188', 'dfn-cert: DFN-CERT-2021-1728', 'dfn-cert: DFN-CERT-2021-1668', 'dfn-cert: DFN-CERT-2021-1472']</t>
@@ -6574,6 +6828,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
         <v>8081</v>
       </c>
@@ -6590,6 +6845,7 @@
       <c r="K88" t="n">
         <v>5.3</v>
       </c>
+      <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
           <t>Installed version: 8.5.23
@@ -6612,6 +6868,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6630,6 +6887,7 @@
           <t>Update to version 8.5.64, 9.0.44 or later.</t>
         </is>
       </c>
+      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
           <t>['cve: CVE-2024-21733', 'url: https://lists.apache.org/thread/h9bjqdd0odj6lhs2o96qgowcc6hb0cfz', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.44', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.64', 'cert-bund: WID-SEC-2024-0769', 'cert-bund: WID-SEC-2024-0163', 'dfn-cert: DFN-CERT-2025-1517', 'dfn-cert: DFN-CERT-2025-0134', 'dfn-cert: DFN-CERT-2024-1404', 'dfn-cert: DFN-CERT-2024-0648']</t>
@@ -6640,6 +6898,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
         <v>8081</v>
       </c>
@@ -6683,6 +6942,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6700,6 +6960,7 @@
           <t>Update to version 7.0.84, 8.0.48, 8.5.24, 9.0.2 or later.</t>
         </is>
       </c>
+      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>['cve: CVE-2017-15706', 'url: http://tomcat.apache.org/security-9.html', 'url: http://tomcat.apache.org/security-8.html', 'url: http://tomcat.apache.org/security-7.html', 'url: https://lists.apache.org/thread/jocvjoxftkq59c4z8sdp12oskkvm56dy', 'cert-bund: CB-K18/0199', 'dfn-cert: DFN-CERT-2018-2165', 'dfn-cert: DFN-CERT-2018-2142', 'dfn-cert: DFN-CERT-2018-1038', 'dfn-cert: DFN-CERT-2018-0733', 'dfn-cert: DFN-CERT-2018-0217']</t>
@@ -6710,6 +6971,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
         <v>8081</v>
       </c>
@@ -6754,6 +7016,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6781,6 +7044,7 @@
 problematic cache have been removed)</t>
         </is>
       </c>
+      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>['cve: CVE-2024-50379', 'cve: CVE-2024-54677', 'cve: CVE-2024-56337', 'url: https://lists.apache.org/thread/y6lj6q1xnp822g6ro70tn19sgtjmr80r', 'url: https://lists.apache.org/thread/tdtbbxpg5trdwc2wnopcth9ccvdftq2n', 'url: https://lists.apache.org/thread/b2b9qrgjrz1kvo4ym8y2wkfdvwoq6qbp', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.2', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.34', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.98', 'cert-bund: WID-SEC-2025-0823', 'cert-bund: WID-SEC-2025-0819', 'cert-bund: WID-SEC-2025-0818', 'cert-bund: WID-SEC-2025-0808', 'cert-bund: WID-SEC-2025-0719', 'cert-bund: WID-SEC-2025-0148', 'cert-bund: WID-SEC-2024-3744', 'cert-bund: WID-SEC-2024-3722', 'dfn-cert: DFN-CERT-2025-2285', 'dfn-cert: DFN-CERT-2025-2098', 'dfn-cert: DFN-CERT-2025-1991', 'dfn-cert: DFN-CERT-2025-1923', 'dfn-cert: DFN-CERT-2025-1181', 'dfn-cert: DFN-CERT-2025-0974', 'dfn-cert: DFN-CERT-2025-0890', 'dfn-cert: DFN-CERT-2025-0888', 'dfn-cert: DFN-CERT-2025-0766', 'dfn-cert: DFN-CERT-2025-0528', 'dfn-cert: DFN-CERT-2025-0509', 'dfn-cert: DFN-CERT-2025-0444', 'dfn-cert: DFN-CERT-2025-0146', 'dfn-cert: DFN-CERT-2025-0138', 'dfn-cert: DFN-CERT-2025-0134', 'dfn-cert: DFN-CERT-2025-0036', 'dfn-cert: DFN-CERT-2024-3364']</t>
@@ -6791,6 +7055,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
         <v>8081</v>
       </c>
@@ -6838,6 +7103,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6855,6 +7121,7 @@
           <t>Update to version 9.0.105, 10.1.41, 11.0.7 or later.</t>
         </is>
       </c>
+      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t>['cve: CVE-2025-46701', 'url: https://lists.apache.org/thread/xhqqk9w5q45srcdqhogdk04lhdscv30j', 'cert-bund: WID-SEC-2025-1850', 'cert-bund: WID-SEC-2025-1365', 'cert-bund: WID-SEC-2025-1165', 'dfn-cert: DFN-CERT-2025-2285', 'dfn-cert: DFN-CERT-2025-2098', 'dfn-cert: DFN-CERT-2025-1991', 'dfn-cert: DFN-CERT-2025-1905', 'dfn-cert: DFN-CERT-2025-1780', 'dfn-cert: DFN-CERT-2025-1384']</t>
@@ -6865,6 +7132,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
         <v>8081</v>
       </c>
@@ -6909,6 +7177,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6926,6 +7195,7 @@
           <t>Update to version 8.5.99, 9.0.86, 10.1.19, 11.0.0-M17 or later.</t>
         </is>
       </c>
+      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
           <t>['cve: CVE-2024-23672', 'cve: CVE-2024-24549', 'url: https://lists.apache.org/thread/cmpswfx6tj4s7x0nxxosvfqs11lvdx2f', 'url: https://lists.apache.org/thread/4c50rmomhbbsdgfjsgwlb51xdwfjdcvg', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.0-M1', ',→7', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.19', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.86', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.99', 'url: https://nowotarski.info/http2-continuation-flood/', 'url: https://nowotarski.info/http2-continuation-flood-technical-details/', 'cert-bund: WID-SEC-2024-3663', 'cert-bund: WID-SEC-2024-3508', 'cert-bund: WID-SEC-2024-3377', 'cert-bund: WID-SEC-2024-3220', 'cert-bund: WID-SEC-2024-3219', 'cert-bund: WID-SEC-2024-3196', 'cert-bund: WID-SEC-2024-3195', 'cert-bund: WID-SEC-2024-3191', 'cert-bund: WID-SEC-2024-1656', 'cert-bund: WID-SEC-2024-1642', 'cert-bund: WID-SEC-2024-1638', 'cert-bund: WID-SEC-2024-1622', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-1214', 'cert-bund: WID-SEC-2024-1210', 'cert-bund: WID-SEC-2024-0769', 'cert-bund: WID-SEC-2024-0630 dfn-cert: DFN-CERT-2025-1517', 'dfn-cert: DFN-CERT-2024-3096', 'dfn-cert: DFN-CERT-2024-3078', 'dfn-cert: DFN-CERT-2024-2743', 'dfn-cert: DFN-CERT-2024-1846', 'dfn-cert: DFN-CERT-2024-1372', 'dfn-cert: DFN-CERT-2024-1235', 'dfn-cert: DFN-CERT-2024-1036', 'dfn-cert: DFN-CERT-2024-1011', 'dfn-cert: DFN-CERT-2024-0723', 'dfn-cert: DFN-CERT-2024-0722', 'dfn-cert: DFN-CERT-2024-0697']</t>
@@ -6936,6 +7206,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
         <v>8081</v>
       </c>
@@ -6982,6 +7253,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7000,6 +7272,7 @@
           <t>Update to version 8.5.86, 9.0.72, 10.1.6, 11.0.0-M3 or later.</t>
         </is>
       </c>
+      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
           <t>['cve: CVE-2023-28708', 'url: https://lists.apache.org/thread/hdksc59z3s7tm39x0pp33mtwdrt8qr67', 'url: https://tomcat.apache.org/security-11.html#Fixed_in_Apache_Tomcat_11.0.0-M3', 'url: https://tomcat.apache.org/security-10.html#Fixed_in_Apache_Tomcat_10.1.6', 'url: https://tomcat.apache.org/security-9.html#Fixed_in_Apache_Tomcat_9.0.72', 'url: https://tomcat.apache.org/security-8.html#Fixed_in_Apache_Tomcat_8.5.86', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2023-2674', 'cert-bund: WID-SEC-2023-1812', 'cert-bund: WID-SEC-2023-1808', 'cert-bund: WID-SEC-2023-1784', 'cert-bund: WID-SEC-2023-1783', 'cert-bund: WID-SEC-2023-1782', 'cert-bund: WID-SEC-2023-1424', 'cert-bund: WID-SEC-2023-1021', 'cert-bund: WID-SEC-2023-1017', 'cert-bund: WID-SEC-2023-0717', 'dfn-cert: DFN-CERT-2025-1517', 'dfn-cert: DFN-CERT-2024-3078', 'dfn-cert: DFN-CERT-2023-2778', 'dfn-cert: DFN-CERT-2023-2545', 'dfn-cert: DFN-CERT-2023-2054', 'dfn-cert: DFN-CERT-2023-0772', 'dfn-cert: DFN-CERT-2023-0763', 'dfn-cert: DFN-CERT-2023-0640']</t>
@@ -7010,6 +7283,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
         <v>8081</v>
       </c>
@@ -7053,6 +7327,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7070,6 +7345,7 @@
           <t>Update to version 7.0.91, 8.5.34, 9.0.12 or later.</t>
         </is>
       </c>
+      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
           <t>['cve: CVE-2018-11784', 'url: http://tomcat.apache.org/security-9.html', 'url: http://tomcat.apache.org/security-8.html', 'url: http://tomcat.apache.org/security-7.html', 'cert-bund: WID-SEC-2025-1212 cert-bund: WID-SEC-2024-1682', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2023-0531', 'cert-bund: WID-SEC-2023-0460', 'cert-bund: CB-K20/0029', 'cert-bund: CB-K19/1121', 'cert-bund: CB-K19/0907', 'cert-bund: CB-K19/0616', 'cert-bund: CB-K19/0320', 'cert-bund: CB-K19/0050', 'cert-bund: CB-K18/0963', 'dfn-cert: DFN-CERT-2019-2710', 'dfn-cert: DFN-CERT-2019-2159', 'dfn-cert: DFN-CERT-2019-1562', 'dfn-cert: DFN-CERT-2019-1237', 'dfn-cert: DFN-CERT-2019-0771', 'dfn-cert: DFN-CERT-2019-0147', 'dfn-cert: DFN-CERT-2019-0104', 'dfn-cert: DFN-CERT-2018-2435', 'dfn-cert: DFN-CERT-2018-2165', 'dfn-cert: DFN-CERT-2018-2142', 'dfn-cert: DFN-CERT-2018-2000']</t>
@@ -7080,6 +7356,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
         <v>8081</v>
       </c>
@@ -7096,6 +7373,7 @@
       <c r="K95" t="n">
         <v>4.3</v>
       </c>
+      <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
           <t>Installed version: 8.5.23
@@ -7118,6 +7396,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -7135,6 +7414,7 @@
           <t>Update to version 8.5.58, 9.0.38, 10.0.0-M8 or later.</t>
         </is>
       </c>
+      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
           <t>['cve: CVE-2020-13943', 'url: https://lists.apache.org/thread.html/r4a390027eb27e4550142fac6c8317cc684b15', ',→7ae314d31514747f307%40%3Cannounce.tomcat.apache.org%3E', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2023-2467', 'cert-bund: CB-K20/0971', 'dfn-cert: DFN-CERT-2022-0733', 'dfn-cert: DFN-CERT-2021-2620', 'dfn-cert: DFN-CERT-2021-0338', 'dfn-cert: DFN-CERT-2021-0134', 'dfn-cert: DFN-CERT-2021-0034', 'dfn-cert: DFN-CERT-2020-2224']</t>
@@ -7145,6 +7425,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
         <v>8081</v>
       </c>
@@ -7161,6 +7442,7 @@
       <c r="K96" t="n">
         <v>4.3</v>
       </c>
+      <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
           <t>Installed version: 8.5.23
@@ -7183,6 +7465,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7217,6 +7500,7 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
           <t>general</t>
@@ -7257,6 +7541,8 @@
 Version used: 2025-01-21T05:37:33Z</t>
         </is>
       </c>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -7274,6 +7560,7 @@
           <t>Update to version 8.5.78, 9.0.62, 10.0.20, 10.1.0-M14 or later.</t>
         </is>
       </c>
+      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
           <t>['cve: CVE-2021-43980', 'url: https://lists.apache.org/thread/3jjqbsp6j88b198x5rmg99b1qr8ht3g3', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2022-1558', 'dfn-cert: DFN-CERT-2022-2684', 'dfn-cert: DFN-CERT-2022-2605', 'dfn-cert: DFN-CERT-2022-2392']</t>
@@ -7284,6 +7571,7 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
         <v>8040</v>
       </c>
@@ -7328,6 +7616,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -7363,6 +7652,7 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
         <v>8040</v>
       </c>
@@ -7379,12 +7669,7 @@
       <c r="K99" t="n">
         <v>2.6</v>
       </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>The simplified implementation of blocking reads and writes introduced in Tomcat 10 and backported to Tomcat 9.0.47 onwards exposed a long standing (but extremely hard to trigger) concurrency bug that could cause client connections to share an Http11Processor instance resulting
-in responses, or part responses, to be received by the wrong client.</t>
-        </is>
-      </c>
+      <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
           <t>It was detected that the host implements RFC1323/RFC7323.
@@ -7402,6 +7687,8 @@
 Version used: 2023-12-15T16:10:08Z</t>
         </is>
       </c>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -7419,6 +7706,7 @@
           <t>Update to version 8.5.78, 9.0.62, 10.0.20, 10.1.0-M14 or later.</t>
         </is>
       </c>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
           <t>['cve: CVE-2021-43980', 'url: https://lists.apache.org/thread/3jjqbsp6j88b198x5rmg99b1qr8ht3g3', 'cert-bund: WID-SEC-2024-1238', 'cert-bund: WID-SEC-2024-0528', 'cert-bund: WID-SEC-2022-1558', 'dfn-cert: DFN-CERT-2022-2684', 'dfn-cert: DFN-CERT-2022-2605', 'dfn-cert: DFN-CERT-2022-2392']</t>
@@ -7429,6 +7717,7 @@
           <t>LOG</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
         <v>8081</v>
       </c>
@@ -7472,6 +7761,7 @@
 OID: 1.3.6.1.4.1.25623.1.0.107652)</t>
         </is>
       </c>
+      <c r="P100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7485,6 +7775,8 @@
 </t>
         </is>
       </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>['url: https://tomcat.apache.org/connectors-doc/ajp/ajpv13a.html']</t>
@@ -7495,6 +7787,7 @@
           <t>LOG</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
           <t>general</t>
@@ -7523,13 +7816,8 @@
           <t>A service supporting the Apache JServ Protocol (AJP) v1.3 seems to be running on this port.</t>
         </is>
       </c>
-      <c r="O101" t="inlineStr">
-        <is>
-          <t>172.31.1.54|cpe:/a:apache:tomcat:8.5.23
-172.31.1.54|cpe:/a:jfrog:artifactory:5.11.0
-172.31.1.54|cpe:/o:linux:kernel</t>
-        </is>
-      </c>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Details: Apache JServ Protocol (AJP) v1.3 Detection (TCP)
@@ -7554,6 +7842,8 @@
 the older CPE.</t>
         </is>
       </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
           <t>['https://nvd.nist.gov/products/cpe']</t>
@@ -7564,6 +7854,7 @@
           <t>LOG</t>
         </is>
       </c>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
           <t>general</t>
@@ -7582,6 +7873,7 @@
       <c r="K102" t="n">
         <v>0</v>
       </c>
+      <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
           <t>172.31.1.54|cpe:/a:apache:tomcat:8.5.23
@@ -7589,6 +7881,8 @@
 172.31.1.54|cpe:/o:linux:kernel</t>
         </is>
       </c>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Details: CPE Inventory
@@ -7608,11 +7902,15 @@
           <t>This plugin performs service detection.</t>
         </is>
       </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
           <t>LOG</t>
         </is>
       </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
         <v>8040</v>
       </c>
@@ -7641,6 +7939,8 @@
           <t>A web server is running on this port</t>
         </is>
       </c>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Details: Services
@@ -7660,6 +7960,8 @@
           <t>Enumerates which HTTP methods are allowed.</t>
         </is>
       </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
           <t>['https://nvd.nist.gov/products/cpe']</t>
@@ -7670,6 +7972,7 @@
           <t>LOG</t>
         </is>
       </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
         <v>8040</v>
       </c>
@@ -7699,6 +8002,8 @@
           <t>The following list contains the URLs and corresponding supported HTTP methods.</t>
         </is>
       </c>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Sends multiple HTTP requests and checks the responses.
@@ -7727,11 +8032,15 @@
 (including its value and if it is deprecated) or is missing on the target.</t>
         </is>
       </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
           <t>LOG</t>
         </is>
       </c>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
         <v>8040</v>
       </c>
@@ -7748,11 +8057,7 @@
       <c r="K105" t="n">
         <v>0</v>
       </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>MKREDIRECTREF, MKWORKSPACE, MOVE, ORDERPATCH, PATCH, PRI, PROPFIND,</t>
-        </is>
-      </c>
+      <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
           <t>Missing Headers | More Information
@@ -7765,11 +8070,9 @@
 ,→e: This is an upcoming header</t>
         </is>
       </c>
-      <c r="P105" t="inlineStr">
-        <is>
-          <t>rudimentary information about the possible enabled methods</t>
-        </is>
-      </c>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -7788,6 +8091,7 @@
           <t>Solution:</t>
         </is>
       </c>
+      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>['url: https://owasp.org/www-project-secure-headers/', 'url: https://owasp.org/www-project-secure-headers/#div-headers', 'url: https://securityheaders.com/']</t>
@@ -7798,6 +8102,7 @@
           <t>LOG</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
         <v>8040</v>
       </c>
@@ -7814,11 +8119,7 @@
       <c r="K106" t="n">
         <v>0</v>
       </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>PROPPATCH, REBIND, REPORT, SEARCH, UNBIND, UNCHECKOUT, UNLINK, UN-</t>
-        </is>
-      </c>
+      <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">Missing Headers | More Information
@@ -7848,6 +8149,7 @@
 Version used: 2025-03-21T15:40:43Z</t>
         </is>
       </c>
+      <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Details: HTTP Security Headers Detection
@@ -7868,6 +8170,8 @@
 Quality of Detection (QoD): 80%</t>
         </is>
       </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
           <t>['url: https://jfrog.com/artifactory/']</t>
@@ -7878,6 +8182,7 @@
           <t>LOG</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
         <v>8040</v>
       </c>
@@ -7894,11 +8199,7 @@
       <c r="K107" t="n">
         <v>0</v>
       </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>LOCK, UPDATE, UPDATEREDIRECTREF, VERSION-CONTROL</t>
-        </is>
-      </c>
+      <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
           <t>Detected JFrog Artifactory
@@ -7909,6 +8210,8 @@
 Concluded from version/product identification location: http://artifactory5.trabalho_vulnnet:8040/artifactory/ui/auth/screen/footer</t>
         </is>
       </c>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Details: JFrog Artifactory Detection (HTTP)
@@ -7939,6 +8242,8 @@
 If you think any of this information is wrong please report it to the referenced community forum.</t>
         </is>
       </c>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
           <t>['url: https://forum.greenbone.net/c/vulnerability-tests/7']</t>
@@ -7949,6 +8254,7 @@
           <t>LOG</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
         <v>8040</v>
       </c>
@@ -7965,6 +8271,7 @@
       <c r="K108" t="n">
         <v>0</v>
       </c>
+      <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
           <t>The Hostname/IP "artifactory5.trabalho_vulnnet" was used to access the remote ho
@@ -7989,6 +8296,8 @@
 ,→s</t>
         </is>
       </c>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Details: Web Application Scanning Consolidation / Info Reporting
@@ -8008,11 +8317,15 @@
           <t>The script reports information on how the hostname of the target was determined.</t>
         </is>
       </c>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
           <t>LOG</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
         <v>8040</v>
       </c>
@@ -8029,13 +8342,54 @@
       <c r="K109" t="n">
         <v>0</v>
       </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>For internal networks, the distances are usually small, often less than 4 hosts between scanner
-and target. For public targets the distance is greater and might be 10 hosts or more.</t>
-        </is>
-      </c>
-      <c r="M109" t="inlineStr">
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Traceroute</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Collect information about the network route and network distance between the scanner host and the target host.</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="n">
+        <v>8040</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>OPENVAS</t>
+        </is>
+      </c>
+      <c r="K110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>For internal networks, the distances are usually small, often less than 4 hosts between scanner and target. For public targets the distance is greater and might be 10 hosts or more.</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
         <is>
           <t>Network route from scanner (172.30.0.2) to target (172.31.1.54):
 172.30.0.2
@@ -8043,7 +8397,9 @@
 Network distance between scanner and target: 2</t>
         </is>
       </c>
-      <c r="P109" t="inlineStr">
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
         <is>
           <t>A combination of the protocols ICMP and TCP is used to determine the route. This method is
 applicable for IPv4 only and it is also known as 'traceroute'.
@@ -8053,61 +8409,6 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Traceroute</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Collect information about the network route and network distance between the scanner host and the target host.</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>LOG</t>
-        </is>
-      </c>
-      <c r="H110" t="n">
-        <v>8040</v>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>tcp</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>OPENVAS</t>
-        </is>
-      </c>
-      <c r="K110" t="n">
-        <v>0</v>
-      </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>For internal networks, the distances are usually small, often less than 4 hosts between scanner and target. For public targets the distance is greater and might be 10 hosts or more.</t>
-        </is>
-      </c>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>Network route from scanner (172.30.0.2) to target (172.31.1.54):
-172.30.0.2
-172.31.1.54
-Network distance between scanner and target: 2</t>
-        </is>
-      </c>
-      <c r="P110" t="inlineStr">
-        <is>
-          <t>A combination of the protocols ICMP and TCP is used to determine the route. This method is
-applicable for IPv4 only and it is also known as 'traceroute'.
-Details: Traceroute
-OID:1.3.6.1.4.1.25623.1.0.51662
-Version used: 2022-10-17T11:13:19Z</t>
-        </is>
-      </c>
-    </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
@@ -8119,6 +8420,8 @@
           <t>Checks if the remote host has IP forwarding enabled.</t>
         </is>
       </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
           <t>['cve: CVE-1999-0511']</t>
@@ -8129,6 +8432,7 @@
           <t>LOG</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
         <v>8040</v>
       </c>
@@ -8145,6 +8449,7 @@
       <c r="K111" t="n">
         <v>0</v>
       </c>
+      <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
           <t>It was possible to route a TCP packet through the target host and received an answer which means IP forwarding is enabled.</t>
@@ -8155,13 +8460,8 @@
           <t>Sends a crafted Local Link Layer (LLL) frame and checks the response.</t>
         </is>
       </c>
-      <c r="P111" t="inlineStr">
-        <is>
-          <t>Details: OS Detection Consolidation and Reporting
-OID:1.3.6.1.4.1.25623.1.0.105937
-Version used: 2026-01-21T05:50:46Z</t>
-        </is>
-      </c>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -8175,6 +8475,8 @@
 Furthermore it reports all previously collected information leading to this best matching OS.</t>
         </is>
       </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
           <t>['https://forum.greenbone.net/c/vulnerability-tests/7']</t>
@@ -8185,6 +8487,7 @@
           <t>LOG</t>
         </is>
       </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
         <v>8040</v>
       </c>
@@ -8201,6 +8504,7 @@
       <c r="K112" t="n">
         <v>0</v>
       </c>
+      <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
           <t>Best matching OS: Linux Kernel
@@ -8213,6 +8517,7 @@
 Concluded from ICMP based OS fingerprint</t>
         </is>
       </c>
+      <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Log Method
@@ -8233,6 +8538,8 @@
           <t>Consolidation of Apache Tomcat detections.</t>
         </is>
       </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
           <t>['http://tomcat.apache.org/']</t>
@@ -8243,6 +8550,7 @@
           <t>LOG</t>
         </is>
       </c>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
         <v>8040</v>
       </c>
@@ -8259,6 +8567,7 @@
       <c r="K113" t="n">
         <v>0</v>
       </c>
+      <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
           <t>Detected Apache Tomcat
@@ -8267,6 +8576,7 @@
 CPE: cpe:/a:apache:tomcat:8.5.23</t>
         </is>
       </c>
+      <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr">
         <is>
           <t>Detected Apache Tomcat
@@ -8318,6 +8628,8 @@
 If you think any of this information is wrong please report it to the referenced community forum.)</t>
         </is>
       </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
           <t>['url: https://forum.greenbone.net/c/vulnerability-tests/7']</t>
@@ -8328,6 +8640,7 @@
           <t>LOG</t>
         </is>
       </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
         <v>8040</v>
       </c>
@@ -8344,6 +8657,7 @@
       <c r="K114" t="n">
         <v>0</v>
       </c>
+      <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
           <t>The Hostname/IP "artifactory5.trabalho_vulnnet" was used to access the remote ho
@@ -8368,6 +8682,8 @@
 ,→s</t>
         </is>
       </c>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Details: Web Application Scanning Consolidation / Info Reporting
@@ -8387,11 +8703,15 @@
           <t>Enumerates which HTTP methods are allowed.</t>
         </is>
       </c>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
           <t>LOG</t>
         </is>
       </c>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
         <v>8040</v>
       </c>
@@ -8424,13 +8744,9 @@
 ,→NS (obtained via HTTP OPTIONS method)</t>
         </is>
       </c>
-      <c r="P115" t="inlineStr">
-        <is>
-          <t>Details: Web Application Scanning Consolidation / Info Reporting
-OID:1.3.6.1.4.1.25623.1.0.111038
-Version used: 2026-01-13T05:47:36Z</t>
-        </is>
-      </c>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -8443,11 +8759,15 @@
           <t>This plugin performs service detection.</t>
         </is>
       </c>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
           <t>LOG</t>
         </is>
       </c>
+      <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
         <v>8040</v>
       </c>
@@ -8471,11 +8791,13 @@
 information available for other check routines.</t>
         </is>
       </c>
+      <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr">
         <is>
           <t>This plugin attempts to guess which service is running on the remote port(s).</t>
         </is>
       </c>
+      <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Details: Services
@@ -8496,6 +8818,8 @@
 Quality of Detection (QoD): 80%</t>
         </is>
       </c>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
           <t>['https://jfrog.com/artifactory/']</t>
@@ -8506,6 +8830,7 @@
           <t>LOG</t>
         </is>
       </c>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
         <v>8081</v>
       </c>
@@ -8522,6 +8847,7 @@
       <c r="K117" t="n">
         <v>8</v>
       </c>
+      <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
           <t>Detected JFrog Artifactory
@@ -8532,6 +8858,8 @@
 Concluded from version/product identification location: http://artifactory5.trabalho_vulnnet:8081/artifactory/ui/auth/screen/footer</t>
         </is>
       </c>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Details: JFrog Artifactory Detection (HTTP)
